--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -7837,7 +7837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -9225,51 +9225,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>The realised vessel sale — direct evidence on carrying values</t>
-        </is>
-      </c>
-      <c r="B112" s="14" t="n"/>
-      <c r="C112" s="14" t="n"/>
-      <c r="D112" s="14" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="14" t="n"/>
-      <c r="G112" s="14" t="n"/>
-      <c r="H112" s="14" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>Carrying value of the very large crude carrier sold (USD 000)</t>
-        </is>
-      </c>
-      <c r="C113" s="27" t="n">
-        <v>83000</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Realised sale price, January 2026 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C114" s="27" t="n">
-        <v>111000</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Capital gain recognised on the sale, as disclosed (USD 000)</t>
-        </is>
-      </c>
-      <c r="C115" s="27" t="n">
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Every figure on this sheet is an input. Nothing here is computed; everything computed from these cells lives on the sheets that follow.</t>
         </is>
@@ -12796,9 +12752,8 @@
           <t>Carrying value of the very large crude carrier sold (USD 000)</t>
         </is>
       </c>
-      <c r="C56" s="18">
-        <f>Assumptions!$C$113</f>
-        <v/>
+      <c r="C56" s="27" t="n">
+        <v>83000</v>
       </c>
     </row>
     <row r="57">
@@ -12807,9 +12762,8 @@
           <t>Realised sale price, January 2026 (USD 000)</t>
         </is>
       </c>
-      <c r="C57" s="18">
-        <f>Assumptions!$C$114</f>
-        <v/>
+      <c r="C57" s="27" t="n">
+        <v>111000</v>
       </c>
     </row>
     <row r="58">
@@ -12829,9 +12783,8 @@
           <t>Capital gain recognised on the sale, as disclosed (USD 000)</t>
         </is>
       </c>
-      <c r="C59" s="18">
-        <f>Assumptions!$C$115</f>
-        <v/>
+      <c r="C59" s="27" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="60">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="114" customWidth="1" min="1" max="1"/>
@@ -732,159 +732,167 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      beta and a different capital-expenditure path) and the three expert-panel legs.</t>
+          <t xml:space="preserve">      beta — the two ends of the regression's own confidence interval — and a different capital-expenditure</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MONTE CARLO AND SENSITIVITY GRIDS DO NOT REDRAW WHEN A DRIVER IS CHANGED. Changing a blue cell</t>
+          <t xml:space="preserve">      path) and the three expert-panel legs.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reprices the whole valuation chain, but those grids are engine outputs and stay as they were run.</t>
+          <t xml:space="preserve">  THE MONTE CARLO AND SENSITIVITY GRIDS DO NOT REDRAW WHEN A DRIVER IS CHANGED. Changing a blue cell</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  reprices the whole valuation chain, but those grids are engine outputs and stay as they were run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Anything else pasted is a defect.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>How revenue is built. Not as one growth rate. The tanker fleet is built vessel by vessel: fifty-three owned</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>vessels split into those trading at spot rates and those on charters out at rates already fixed and</t>
+          <t>How revenue is built. Not as one growth rate. The tanker fleet is built vessel by vessel: fifty-three owned</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>disclosed, each class earning its own time-charter equivalent per day over 365 days, less an all-in running</t>
+          <t>vessels split into those trading at spot rates and those on charters out at rates already fixed and</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>cost per vessel per day escalated on a services-and-wage escalator. The gas carriers are built from</t>
+          <t>disclosed, each class earning its own time-charter equivalent per day over 365 days, less an all-in running</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>contracted vessel-years times an implied day rate. The five remaining units are grown on their own revenue</t>
+          <t>cost per vessel per day escalated on a services-and-wage escalator. The gas carriers are built from</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>contracted vessel-years times an implied day rate. The five remaining units are grown on their own revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
           <t>and margin drivers, anchored on what each actually earned in the first quarter of 2026.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS. The stock's own weekly regression against its local index</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>gives a beta of 0.705, which passes the usability gate and is the primary reading. An asset-risk</t>
+          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS — HOW THE MARKET IS MEASURED. The same weekly regression of the</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>beta of 1.00 — what a listed fleet owner might be expected to carry — gives a materially different cost of</t>
+          <t>stock's own returns is run against two different measures of its market, and the answer moves a long way</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>equity. BOTH are carried through the model in full, side by side, on the Summary and Fundamental Valuation</t>
+          <t>between them. Against the published index of the exchange the share is listed on — the index the method</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>sheets. They are NOT averaged into one number.</t>
+          <t>asks for, and the primary reading — the beta is 1.085. Against an equal-weight composite of that same</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>exchange's names, which gives its smallest listings the same say as its largest, the beta is</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges and distributions.</t>
+          <t>company belongs to; the composite is not. That single difference in construction, and nothing about the</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>company, moves the cost of equity and the cash-flow value materially. BOTH are carried through the model in</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
+          <t>full, side by side, on the Summary, Fundamental Valuation and DCF sheets. They are NOT averaged into one</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+          <t>number. The regression's own 90% confidence interval on the primary estimate runs 0.758 to 1.412, and</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
+          <t>those two bounds — not round numbers chosen by hand — are the betas used in the bear and bull cases, so the</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>is listed with its value, source and date in the companion bibliography document.</t>
+          <t>published range is the range the estimate itself supports.</t>
         </is>
       </c>
     </row>
@@ -894,33 +902,81 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+          <t>shown as ranges and distributions.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
-        </is>
-      </c>
+      <c r="A56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>is listed with its value, source and date in the companion bibliography document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Sensitivity · Per-Share &amp; Ratios · Peer &amp; Sector.</t>
         </is>
@@ -1113,23 +1169,23 @@
         <v>19434</v>
       </c>
       <c r="E7" s="18">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="F7" s="18">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="G7" s="18">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
       <c r="I7" s="18">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$101</f>
         <v/>
       </c>
     </row>
@@ -1149,23 +1205,23 @@
         <v>51368</v>
       </c>
       <c r="E8" s="18">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="F8" s="18">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="I8" s="18">
-        <f>Assumptions!$C$99</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
     </row>
@@ -1226,23 +1282,23 @@
         <v>577769</v>
       </c>
       <c r="E10" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="G10" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -1334,23 +1390,23 @@
         <v>337794</v>
       </c>
       <c r="E13" s="18">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>Assumptions!$C$97</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -1558,23 +1614,23 @@
         <v>1978619</v>
       </c>
       <c r="E19" s="18">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="G19" s="18">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="I19" s="18">
-        <f>Assumptions!$C$91</f>
+        <f>Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -1594,23 +1650,23 @@
         <v>264512</v>
       </c>
       <c r="E20" s="18">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="F20" s="18">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="G20" s="18">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="I20" s="18">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -1907,7 +1963,7 @@
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>'Income Statement'!E28/((Assumptions!$C$96+E21)/2)</f>
+        <f>'Income Statement'!E28/((Assumptions!$C$99+E21)/2)</f>
         <v/>
       </c>
       <c r="F28" s="10">
@@ -1993,23 +2049,23 @@
         </is>
       </c>
       <c r="B32" s="18">
-        <f>Assumptions!$B$68</f>
+        <f>Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="C32" s="18">
-        <f>Assumptions!$C$68</f>
+        <f>Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="D32" s="18">
-        <f>Assumptions!$D$68</f>
+        <f>Assumptions!$D$71</f>
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>Assumptions!$E$68</f>
+        <f>Assumptions!$E$71</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>Assumptions!$F$68</f>
+        <f>Assumptions!$F$71</f>
         <v/>
       </c>
     </row>
@@ -2020,23 +2076,23 @@
         </is>
       </c>
       <c r="B33" s="19">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="C33" s="19">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="D33" s="19">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="E33" s="19">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
       <c r="F33" s="19">
-        <f>Assumptions!$C$69</f>
+        <f>Assumptions!$C$72</f>
         <v/>
       </c>
     </row>
@@ -2128,23 +2184,23 @@
         </is>
       </c>
       <c r="B37" s="31">
-        <f>Assumptions!$C$70*(1+Assumptions!$C$46)^1</f>
+        <f>Assumptions!$C$73*(1+Assumptions!$C$49)^1</f>
         <v/>
       </c>
       <c r="C37" s="31">
-        <f>Assumptions!$C$70*(1+Assumptions!$C$46)^2</f>
+        <f>Assumptions!$C$73*(1+Assumptions!$C$49)^2</f>
         <v/>
       </c>
       <c r="D37" s="31">
-        <f>Assumptions!$C$70*(1+Assumptions!$C$46)^3</f>
+        <f>Assumptions!$C$73*(1+Assumptions!$C$49)^3</f>
         <v/>
       </c>
       <c r="E37" s="31">
-        <f>Assumptions!$C$70*(1+Assumptions!$C$46)^4</f>
+        <f>Assumptions!$C$73*(1+Assumptions!$C$49)^4</f>
         <v/>
       </c>
       <c r="F37" s="31">
-        <f>Assumptions!$C$70*(1+Assumptions!$C$46)^5</f>
+        <f>Assumptions!$C$73*(1+Assumptions!$C$49)^5</f>
         <v/>
       </c>
     </row>
@@ -2268,23 +2324,23 @@
         </is>
       </c>
       <c r="B43" s="17">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
       <c r="F43" s="17">
-        <f>Assumptions!$C$71</f>
+        <f>Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -2295,23 +2351,23 @@
         </is>
       </c>
       <c r="B44" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="E44" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
       <c r="F44" s="17">
-        <f>Assumptions!$C$72</f>
+        <f>Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -2322,23 +2378,23 @@
         </is>
       </c>
       <c r="B45" s="17">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="C45" s="17">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
       <c r="F45" s="17">
-        <f>Assumptions!$C$73</f>
+        <f>Assumptions!$C$76</f>
         <v/>
       </c>
     </row>
@@ -2457,7 +2513,7 @@
         </is>
       </c>
       <c r="B50" s="36">
-        <f>B49-Assumptions!$C$74</f>
+        <f>B49-Assumptions!$C$77</f>
         <v/>
       </c>
       <c r="C50" s="36">
@@ -2516,7 +2572,7 @@
         </is>
       </c>
       <c r="B53" s="18">
-        <f>Assumptions!$C$89+Assumptions!$C$90</f>
+        <f>Assumptions!$C$92+Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="C53" s="31">
@@ -2543,23 +2599,23 @@
         </is>
       </c>
       <c r="B54" s="31">
-        <f>B53+Assumptions!$C$97</f>
+        <f>B53+Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="C54" s="31">
-        <f>C53+Assumptions!$C$97</f>
+        <f>C53+Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="D54" s="31">
-        <f>D53+Assumptions!$C$97</f>
+        <f>D53+Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="E54" s="31">
-        <f>E53+Assumptions!$C$97</f>
+        <f>E53+Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="F54" s="31">
-        <f>F53+Assumptions!$C$97</f>
+        <f>F53+Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -2624,23 +2680,23 @@
         </is>
       </c>
       <c r="B57" s="31">
-        <f>-B55*(1-Assumptions!$C$18)</f>
+        <f>-B55*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="C57" s="31">
-        <f>-C55*(1-Assumptions!$C$18)</f>
+        <f>-C55*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="D57" s="31">
-        <f>-D55*(1-Assumptions!$C$18)</f>
+        <f>-D55*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="E57" s="31">
-        <f>-E55*(1-Assumptions!$C$18)</f>
+        <f>-E55*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="F57" s="31">
-        <f>-F55*(1-Assumptions!$C$18)</f>
+        <f>-F55*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -2651,23 +2707,23 @@
         </is>
       </c>
       <c r="B58" s="31">
-        <f>Assumptions!$C$21*Assumptions!$C$97*(1-Assumptions!$C$18)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="C58" s="31">
-        <f>Assumptions!$C$21*Assumptions!$C$97*(1-Assumptions!$C$18)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="D58" s="31">
-        <f>Assumptions!$C$21*Assumptions!$C$97*(1-Assumptions!$C$18)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="E58" s="31">
-        <f>Assumptions!$C$21*Assumptions!$C$97*(1-Assumptions!$C$18)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="F58" s="31">
-        <f>Assumptions!$C$21*Assumptions!$C$97*(1-Assumptions!$C$18)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -2678,23 +2734,23 @@
         </is>
       </c>
       <c r="B59" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="C59" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="D59" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="E59" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F59" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
     </row>
@@ -2732,23 +2788,23 @@
         </is>
       </c>
       <c r="B61" s="31">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$101)^0</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$104)^0</f>
         <v/>
       </c>
       <c r="C61" s="31">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$101)^1</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$104)^1</f>
         <v/>
       </c>
       <c r="D61" s="31">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$101)^2</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$104)^2</f>
         <v/>
       </c>
       <c r="E61" s="31">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$101)^3</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$104)^3</f>
         <v/>
       </c>
       <c r="F61" s="31">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$101)^4</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$104)^4</f>
         <v/>
       </c>
     </row>
@@ -2818,7 +2874,7 @@
         </is>
       </c>
       <c r="B65" s="18">
-        <f>Assumptions!$C$96</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
       <c r="C65" s="31">
@@ -5034,96 +5090,103 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>9.390453571720622</v>
+        <v>7.545680996606645</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>10.06513198559633</v>
+        <v>7.931348061513757</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>10.92227220457735</v>
+        <v>8.398472715396702</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>12.05037562092223</v>
+        <v>8.977536366227794</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.900</t>
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>7.545680996606645</v>
+        <v>6.283565631675469</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>7.931348061513757</v>
+        <v>6.519104656680824</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>8.398472715396702</v>
+        <v>6.795132335801774</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>8.977536366227794</v>
+        <v>7.124094206639689</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>0.900</t>
+          <t>1.085</t>
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6.283565631675469</v>
+        <v>5.369137616541499</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>6.519104656680824</v>
+        <v>5.518897207717134</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>6.795132335801774</v>
+        <v>5.690033756953623</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>7.124094206639689</v>
+        <v>5.888166311203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>5.761673686091052</v>
+        <v>4.714750523785993</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>5.945943414850556</v>
+        <v>4.814547320478896</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>6.158857038790813</v>
+        <v>4.926333903107382</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>6.408480618830459</v>
+        <v>5.05290125339436</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.412</t>
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>4.899787897206465</v>
+        <v>4.181085324391071</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>5.01276476812066</v>
+        <v>4.24697992822436</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>5.14006717064332</v>
+        <v>4.319377618424721</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>5.285149575002541</v>
+        <v>4.399639302029021</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.085 is the adopted regression against the exchange's published index, and 1.412 is the top of that regression's own 90% confidence interval (its bottom, 0.758, sits just above the composite reading). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.085 row is the published cash-flow value.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -5175,19 +5238,19 @@
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>7.18254744398532</v>
+        <v>4.839888773483615</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>7.790510079691012</v>
+        <v>5.264961265218619</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>8.398472715396702</v>
+        <v>5.690033756953623</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>9.006435351102384</v>
+        <v>6.115106248688621</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>9.614397986808076</v>
+        <v>6.540178740423624</v>
       </c>
     </row>
     <row r="15">
@@ -5245,16 +5308,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>8.883254479344194</v>
+        <v>6.080954150614569</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>8.398472715396702</v>
+        <v>5.690033756953623</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>7.91369095144921</v>
+        <v>5.299113363292675</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>7.428909187501718</v>
+        <v>4.908192969631731</v>
       </c>
     </row>
     <row r="20">
@@ -5307,13 +5370,13 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>8.369572255284547</v>
+        <v>5.664303093467798</v>
       </c>
       <c r="C24" s="21" t="n">
-        <v>7.850087452844138</v>
+        <v>5.282629999295614</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>7.07086024918353</v>
+        <v>4.710120358037337</v>
       </c>
     </row>
     <row r="25">
@@ -6734,7 +6797,7 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>Assumptions!$C$105</f>
+        <f>Assumptions!$C$108</f>
         <v/>
       </c>
     </row>
@@ -6871,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6966,7 +7029,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$107</f>
+        <f>Assumptions!$C$110</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -7001,7 +7064,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$108</f>
+        <f>Assumptions!$C$111</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -7032,7 +7095,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$109</f>
+        <f>Assumptions!$C$112</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -7063,7 +7126,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$110</f>
+        <f>Assumptions!$C$113</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -7121,7 +7184,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (asset-risk beta of 1.00)</t>
+          <t>Discounted cash flow (composite-index beta of 0.705)</t>
         </is>
       </c>
       <c r="B12" s="9">
@@ -7129,7 +7192,7 @@
         <v/>
       </c>
       <c r="C12" s="7">
-        <f>DCF!$C$121</f>
+        <f>DCF!$C$130</f>
         <v/>
       </c>
       <c r="D12" s="9">
@@ -7149,14 +7212,14 @@
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>DCF!$C$118</f>
+        <f>DCF!$C$127</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Weighted central on the asset-risk beta</t>
+          <t>Weighted central on the composite-index beta</t>
         </is>
       </c>
       <c r="B13" s="14" t="n"/>
@@ -7180,7 +7243,7 @@
         </is>
       </c>
       <c r="C15" s="7">
-        <f>'Fundamental Valuation'!$C$32</f>
+        <f>'Fundamental Valuation'!$C$34</f>
         <v/>
       </c>
       <c r="G15" s="10">
@@ -7297,7 +7360,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity — regressed beta</t>
+          <t>Cost of equity — published-index beta (primary)</t>
         </is>
       </c>
       <c r="C26" s="19">
@@ -7308,7 +7371,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity — asset-risk beta</t>
+          <t>Cost of equity — composite-index beta (alternative)</t>
         </is>
       </c>
       <c r="C27" s="19">
@@ -7319,60 +7382,82 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt — the three constructions averaged</t>
+          <t>Cost of equity at the lower 90% confidence bound on the primary beta</t>
         </is>
       </c>
       <c r="C28" s="19">
-        <f>DCF!$C$88</f>
+        <f>DCF!$C$114</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window</t>
+          <t>Cost of equity at the upper 90% confidence bound on the primary beta</t>
         </is>
       </c>
       <c r="C29" s="19">
-        <f>DCF!$C$97</f>
+        <f>DCF!$C$115</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — terminal</t>
+          <t>Cost of debt — the three constructions averaged</t>
         </is>
       </c>
       <c r="C30" s="19">
-        <f>DCF!$C$102</f>
+        <f>DCF!$C$88</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C31" s="8">
-        <f>DCF!$C$39</f>
+          <t>Cost of capital — explicit window</t>
+        </is>
+      </c>
+      <c r="C31" s="19">
+        <f>DCF!$C$97</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>Cost of capital — terminal</t>
+        </is>
+      </c>
+      <c r="C32" s="19">
+        <f>DCF!$C$102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C33" s="8">
+        <f>DCF!$C$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
           <t>Sum-of-the-parts cross-check (AED per share)</t>
         </is>
       </c>
-      <c r="C32" s="7">
+      <c r="C34" s="7">
         <f>'SOTP Bridge'!$C$40</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>The terminal value share beside the discounted-cash-flow row is a live formula — the present value of the terminal value over the enterprise value of operations — and it is shown again in the equity bridge on the SOTP Bridge sheet. It is high, as it is for any long-lived asset owner whose fleet outlives the forecast window, and it is the reason the terminal cost of capital and the terminal growth rate carry more of this valuation than any single trading year.</t>
         </is>
@@ -7389,7 +7474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -7453,11 +7538,11 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>beta 1.10, rate anchor 0.85x, capital expenditure 1.10x — a whole-model re-run</t>
+          <t>beta 1.412 — the TOP of the regression's own 90% confidence interval, not a round number picked by hand — with the rate anchor at 0.85x and capital expenditure at 1.10x. A whole-model re-run</t>
         </is>
       </c>
       <c r="C6" s="21" t="n">
-        <v>4.595125455307053</v>
+        <v>3.47772190260892</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -7468,11 +7553,11 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>beta 0.55, rate anchor 1.15x, capital expenditure 0.95x — a whole-model re-run</t>
+          <t>beta 0.758 — the BOTTOM of the same interval — with the rate anchor at 1.15x and capital expenditure at 0.95x. Taking both bounds from the interval means the published range is the range the estimate itself supports. A whole-model re-run</t>
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>11.56265014945073</v>
+        <v>9.000150484360782</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -7538,7 +7623,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>THE CONTESTED JUDGEMENT — TWO BETAS, BOTH CARRIED THROUGH IN FULL</t>
+          <t>THE CONTESTED JUDGEMENT — TWO INDEX CONSTRUCTIONS, BOTH CARRIED THROUGH IN FULL</t>
         </is>
       </c>
       <c r="B14" s="14" t="n"/>
@@ -7547,12 +7632,12 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Beta — own-stock weekly regression</t>
+          <t>Beta — weekly regression against the published index of its own exchange (primary)</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>163 weekly observations, R-squared 17.2%, standard error 0.122 — the usability gate is passed</t>
+          <t>161 weekly observations, R-squared 15.8%, standard error 0.199, 90% confidence interval 0.758 to 1.412 — the usability gate is passed, and this is the index the method asks for</t>
         </is>
       </c>
       <c r="C15" s="23">
@@ -7563,7 +7648,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity on the regressed beta</t>
+          <t>Cost of equity on the published-index beta</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -7579,7 +7664,7 @@
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital on the regressed beta</t>
+          <t>Cost of capital on the published-index beta</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -7595,7 +7680,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share — regressed beta (AED)</t>
+          <t>Fair value per share — published-index beta (AED)</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
@@ -7611,7 +7696,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Weighted central — regressed beta (AED)</t>
+          <t>Weighted central — published-index beta (AED)</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -7627,12 +7712,12 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Asset-risk beta</t>
+          <t>Beta — the same regression against an equal-weight composite of the same exchange's names (alternative)</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>what a listed fleet owner might be expected to carry; the sector prior for a spot tanker owner is 0.9 to 1.4</t>
+          <t>the published index is weighted by size and is dominated by the same large-capitalisation group this company belongs to; the composite gives the exchange's smallest names the same say as its largest. Only the measure of the market changes</t>
         </is>
       </c>
       <c r="C20" s="23">
@@ -7643,12 +7728,12 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity on the asset-risk beta</t>
+          <t>Cost of equity on the composite-index beta</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>the same construction at a beta of 1.00</t>
+          <t>the same construction, the same premium, the composite beta</t>
         </is>
       </c>
       <c r="C21" s="19">
@@ -7659,7 +7744,7 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital on the asset-risk beta</t>
+          <t>Cost of capital on the composite-index beta</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
@@ -7675,7 +7760,7 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share — asset-risk beta (AED)</t>
+          <t>Fair value per share — composite-index beta (AED)</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -7684,14 +7769,14 @@
         </is>
       </c>
       <c r="C23" s="7">
-        <f>DCF!$C$121</f>
+        <f>DCF!$C$130</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Weighted central — asset-risk beta (AED)</t>
+          <t>Weighted central — composite-index beta (AED)</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
@@ -7704,127 +7789,159 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>These two readings are published side by side and are never averaged into a single number. The regression passes its usability gate on the stock's own history, but that history is only three years long and the beta's own confidence interval spans more than half the point estimate, so the asset-risk reading is not a stress case — it is a second legitimate answer to the same question.</t>
-        </is>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Beta — lower bound of the 90% confidence interval on the primary regression</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>the bull-case beta; the bear and bull cases take the two ends of this interval rather than round numbers picked by hand</t>
+        </is>
+      </c>
+      <c r="C25" s="23">
+        <f>Assumptions!$C$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Beta — upper bound of the 90% confidence interval on the primary regression</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>the bear-case beta; the published range is therefore the range the estimate itself supports</t>
+        </is>
+      </c>
+      <c r="C26" s="23">
+        <f>Assumptions!$C$17</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>These two readings are published side by side and are never averaged into a single number. They are the same regression of the same weekly returns; what differs is how the market itself is measured. The published index of the exchange is what the beta method asks for and is the primary reading. The equal-weight composite is what an earlier construction of this study used, and it is kept in view because a difference of this size is a property of index construction rather than a fact about the company. The regression passes its usability gate, but the history is only three years long and the 90% interval shown above spans more than half the point estimate, so the alternative is not a stress case — it is a second legitimate answer to the same question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>EXPERT PANEL — THREE METHODS, WORKED INDEPENDENTLY</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Expert</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Base (AED per share)</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Expert 1</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>mid-cycle earnings power</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>6.051858331225449</v>
-      </c>
-      <c r="D29" s="21" t="n">
-        <v>4.538893748419087</v>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>7.564822914031812</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Expert 2</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>owner cash earnings</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>6.229801223504354</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <v>4.2732615454651</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>8.113775108868071</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>Expert 1</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>mid-cycle earnings power</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>6.051858331225449</v>
+      </c>
+      <c r="D31" s="21" t="n">
+        <v>4.538893748419087</v>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>7.564822914031812</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Expert 2</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>owner cash earnings</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>4.659955276266538</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>3.410372734655293</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>6.548699942289825</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
           <t>Expert 3</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>cash returns against the cost of capital</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
-        <v>7.295828966094767</v>
-      </c>
-      <c r="D31" s="21" t="n">
-        <v>4.997558751749976</v>
-      </c>
-      <c r="E31" s="21" t="n">
-        <v>9.110401132774284</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="C33" s="21" t="n">
+        <v>4.792142453207098</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>3.709183272309684</v>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>5.641772237728</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Panel average</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="12">
-        <f>AVERAGE(C29:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
+      <c r="B34" s="14" t="n"/>
+      <c r="C34" s="12">
+        <f>AVERAGE(C31:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7837,7 +7954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -7972,376 +8089,340 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Beta — own-stock weekly regression against its local index</t>
+          <t>Beta — own-stock weekly regression against the published index of its own exchange</t>
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>0.705</v>
+        <v>1.085</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Asset-risk beta — the contested alternative</t>
+          <t>Beta — the same regression against an equal-weight composite of that exchange's names (the disclosed alternative)</t>
         </is>
       </c>
       <c r="C15" s="29" t="n">
-        <v>1</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium (mature premium plus country risk)</t>
-        </is>
-      </c>
-      <c r="C16" s="28" t="n">
-        <v>0.0487</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>No sovereign credit-default-swap entry exists for the United Arab Emirates in the country risk file, so the alternative rating-versus-swap premium basis cannot be built for this country; one basis is published rather than two.</t>
-        </is>
+          <t>Beta — lower bound of the regression's 90% confidence interval (the bull-case beta)</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>0.758</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="n">
-        <v>0.0325</v>
+          <t>Beta — upper bound of the regression's 90% confidence interval (the bear-case beta)</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>1.412</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Statutory corporate tax rate</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>0.09</v>
+          <t>Beta — lead-lag sum beta from the same series, one lead and two lags</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>1.164</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Equity risk premium (mature premium plus country risk)</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>No sovereign credit-default-swap entry exists for the United Arab Emirates in the country risk file, so the alternative rating-versus-swap premium basis cannot be built for this country; one basis is published rather than two.</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Cost of debt — the evidence behind the three constructions</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>0.0325</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Secured overnight financing rate</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>The Central Bank base rate of 3.65% was maintained at the 29 July 2026 decision; the last change was a 25 basis point cut from 3.90% on 10 December 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Parent revolving credit facility margin</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="n">
-        <v>0.008</v>
+          <t>Statutory corporate tax rate</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Third-party bank loans — low end of the disclosed range</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="n">
-        <v>0.0711</v>
-      </c>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Cost of debt — the evidence behind the three constructions</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="n"/>
+      <c r="H23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Third-party bank loans — high end of the disclosed range</t>
+          <t>Secured overnight financing rate</t>
         </is>
       </c>
       <c r="C24" s="28" t="n">
-        <v>0.0755</v>
+        <v>0.0365</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>The Central Bank base rate of 3.65% was maintained at the 29 July 2026 decision; the last change was a 25 basis point cut from 3.90% on 10 December 2025.</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Other third-party borrowings — low end of the disclosed range</t>
+          <t>Parent revolving credit facility margin</t>
         </is>
       </c>
       <c r="C25" s="28" t="n">
-        <v>0.0436</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Other third-party borrowings — high end of the disclosed range</t>
+          <t>Third-party bank loans — low end of the disclosed range</t>
         </is>
       </c>
       <c r="C26" s="28" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Lease interest charged in 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C27" s="27" t="n">
-        <v>12719</v>
+          <t>Third-party bank loans — high end of the disclosed range</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n">
+        <v>0.0755</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, opening balance 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C28" s="27" t="n">
-        <v>170274</v>
+          <t>Other third-party borrowings — low end of the disclosed range</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>0.0436</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, closing balance 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="n">
-        <v>223153</v>
+          <t>Other third-party borrowings — high end of the disclosed range</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="n">
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Shareholder loan at 31 March 2026 (USD 000)</t>
+          <t>Lease interest charged in 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C30" s="27" t="n">
-        <v>500000</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Third-party borrowings at 31 March 2026 (USD 000)</t>
+          <t>Lease liabilities, opening balance 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C31" s="27" t="n">
-        <v>402763</v>
+        <v>170274</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities at 31 March 2026 (USD 000)</t>
+          <t>Lease liabilities, closing balance 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C32" s="27" t="n">
-        <v>212449</v>
+        <v>223153</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Shareholder loan at 31 March 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Tanker fleet — vessel counts and day rates by class</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Handysize</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>Medium range</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Long range 1</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>Long range 2</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>Very large crude carrier</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="n"/>
-      <c r="H34" s="14" t="n"/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Third-party borrowings at 31 March 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>402763</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Vessels owned</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>2</v>
+          <t>Lease liabilities at 31 March 2026 (USD 000)</t>
+        </is>
       </c>
       <c r="C35" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="E35" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="F35" s="27" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Vessels trading at spot rates</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="D36" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F36" s="27" t="n">
-        <v>7</v>
+        <v>212449</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Fixed charter-out rate (USD per day)</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="27" t="n">
-        <v>19750</v>
-      </c>
-      <c r="E37" s="27" t="n">
-        <v>35943</v>
-      </c>
-      <c r="F37" s="27" t="n">
-        <v>60942</v>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>The smallest two classes have no vessels on charters out, so no fixed rate applies to them.</t>
-        </is>
-      </c>
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Tanker fleet — vessel counts and day rates by class</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Handysize</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Medium range</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Long range 1</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Long range 2</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Very large crude carrier</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2025 average time-charter equivalent (USD per day)</t>
+          <t>Vessels owned</t>
         </is>
       </c>
       <c r="B38" s="27" t="n">
-        <v>24139.5</v>
+        <v>2</v>
       </c>
       <c r="C38" s="27" t="n">
-        <v>24139.5</v>
+        <v>16</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>24199.25</v>
+        <v>9</v>
       </c>
       <c r="E38" s="27" t="n">
-        <v>35737.25</v>
+        <v>17</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>52466</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>First-quarter 2026 time-charter equivalent (USD per day)</t>
+          <t>Vessels trading at spot rates</t>
         </is>
       </c>
       <c r="B39" s="27" t="n">
-        <v>30000</v>
+        <v>2</v>
       </c>
       <c r="C39" s="27" t="n">
-        <v>30000</v>
+        <v>16</v>
       </c>
       <c r="D39" s="27" t="n">
-        <v>36000</v>
+        <v>7</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>58000</v>
+        <v>13</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>145000</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Second-quarter 2026 time-charter equivalent (USD per day)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>44000</v>
-      </c>
-      <c r="C40" s="27" t="n">
-        <v>44000</v>
+          <t>Fixed charter-out rate (USD per day)</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D40" s="27" t="n">
-        <v>55000</v>
+        <v>19750</v>
       </c>
       <c r="E40" s="27" t="n">
-        <v>95000</v>
+        <v>35943</v>
       </c>
       <c r="F40" s="27" t="n">
-        <v>260000</v>
+        <v>60942</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>The smallest two classes have no vessels on charters out, so no fixed rate applies to them.</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle rate anchor (USD per day)</t>
+          <t>2025 average time-charter equivalent (USD per day)</t>
         </is>
       </c>
       <c r="B41" s="27" t="n">
@@ -8351,881 +8432,947 @@
         <v>24139.5</v>
       </c>
       <c r="D41" s="27" t="n">
-        <v>32177.125</v>
+        <v>24199.25</v>
       </c>
       <c r="E41" s="27" t="n">
-        <v>41874</v>
+        <v>35737.25</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>47923.625</v>
+        <v>52466</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>First-quarter 2026 time-charter equivalent (USD per day)</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D42" s="27" t="n">
+        <v>36000</v>
+      </c>
+      <c r="E42" s="27" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F42" s="27" t="n">
+        <v>145000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Tanker fleet — rate path and running cost</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="n"/>
-      <c r="C43" s="14" t="n"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="14" t="n"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Second-quarter 2026 time-charter equivalent (USD per day)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>44000</v>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>44000</v>
+      </c>
+      <c r="D43" s="27" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F43" s="27" t="n">
+        <v>260000</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Weight on the 2025 average rate in setting the second half of 2026</t>
-        </is>
-      </c>
-      <c r="C44" s="30" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>All-in running cost per vessel per day (USD)</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="n">
-        <v>9354.949470147329</v>
+          <t>Mid-cycle rate anchor (USD per day)</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n">
+        <v>24139.5</v>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>24139.5</v>
+      </c>
+      <c r="D44" s="27" t="n">
+        <v>32177.125</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>41874</v>
+      </c>
+      <c r="F44" s="27" t="n">
+        <v>47923.625</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Running-cost escalation (services and wages)</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Tanker fleet — rate path and running cost</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="n"/>
+      <c r="G46" s="14" t="n"/>
+      <c r="H46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Gross-up from time-charter-equivalent revenue to reported revenue</t>
-        </is>
-      </c>
-      <c r="C47" s="26" t="n">
-        <v>1.6</v>
+          <t>Weight on the 2025 average rate in setting the second half of 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>All-in running cost per vessel per day (USD)</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>9354.949470147329</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Tanker charter-out roll-off and gas-carrier contracts</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="n"/>
-      <c r="H49" s="14" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Running-cost escalation (services and wages)</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Charter-out contracts still running (share of the year)</t>
-        </is>
-      </c>
-      <c r="B50" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Gas carriers — contracted vessel-years</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="C51" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="D51" s="24" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="E51" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="F51" s="24" t="n">
-        <v>25</v>
+          <t>Gross-up from time-charter-equivalent revenue to reported revenue</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="n">
-        <v>61573.28767123288</v>
-      </c>
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Tanker charter-out roll-off and gas-carrier contracts</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="n"/>
+      <c r="H52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Gas carriers — earnings margin</t>
-        </is>
+          <t>Charter-out contracts still running (share of the year)</t>
+        </is>
+      </c>
+      <c r="B53" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="C53" s="30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Gas carriers — contracted vessel-years</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="C54" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" s="24" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="E54" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="F54" s="24" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>The remaining five units — revenue and margin drivers</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="n"/>
-      <c r="H55" s="14" t="n"/>
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="n">
+        <v>61573.28767123288</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B56" s="27" t="n">
-        <v>1248192</v>
-      </c>
-      <c r="C56" s="27" t="n">
-        <v>1298120</v>
-      </c>
-      <c r="D56" s="27" t="n">
-        <v>1350044</v>
-      </c>
-      <c r="E56" s="27" t="n">
-        <v>1404046</v>
-      </c>
-      <c r="F56" s="27" t="n">
-        <v>1460208</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Contracting — earnings margin</t>
-        </is>
-      </c>
-      <c r="B57" s="30" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E57" s="30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F57" s="30" t="n">
-        <v>0.43</v>
+          <t>Gas carriers — earnings margin</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Services — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B58" s="27" t="n">
-        <v>662856</v>
-      </c>
-      <c r="C58" s="27" t="n">
-        <v>696000</v>
-      </c>
-      <c r="D58" s="27" t="n">
-        <v>730800</v>
-      </c>
-      <c r="E58" s="27" t="n">
-        <v>767340</v>
-      </c>
-      <c r="F58" s="27" t="n">
-        <v>805707</v>
-      </c>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>The remaining five units — revenue and margin drivers</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="n"/>
+      <c r="H58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — earnings margin</t>
-        </is>
-      </c>
-      <c r="B59" s="30" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="C59" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D59" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E59" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F59" s="30" t="n">
-        <v>0.29</v>
+          <t>Offshore Contracting — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="n">
+        <v>1248192</v>
+      </c>
+      <c r="C59" s="27" t="n">
+        <v>1298120</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>1350044</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>1404046</v>
+      </c>
+      <c r="F59" s="27" t="n">
+        <v>1460208</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B60" s="27" t="n">
-        <v>125000</v>
-      </c>
-      <c r="C60" s="27" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D60" s="27" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E60" s="27" t="n">
-        <v>275000</v>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>300000</v>
+          <t>Offshore Contracting — earnings margin</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="D60" s="30" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E60" s="30" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — earnings margin</t>
-        </is>
-      </c>
-      <c r="B61" s="30" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="C61" s="30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D61" s="30" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E61" s="30" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F61" s="30" t="n">
-        <v>0.065</v>
+          <t>Offshore Services — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="n">
+        <v>662856</v>
+      </c>
+      <c r="C61" s="27" t="n">
+        <v>696000</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>730800</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>767340</v>
+      </c>
+      <c r="F61" s="27" t="n">
+        <v>805707</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B62" s="27" t="n">
-        <v>197164</v>
-      </c>
-      <c r="C62" s="27" t="n">
-        <v>201107</v>
-      </c>
-      <c r="D62" s="27" t="n">
-        <v>205129</v>
-      </c>
-      <c r="E62" s="27" t="n">
-        <v>209232</v>
-      </c>
-      <c r="F62" s="27" t="n">
-        <v>213417</v>
+          <t>Offshore Services — earnings margin</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="C62" s="30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="D62" s="30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E62" s="30" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F62" s="30" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — earnings margin</t>
-        </is>
-      </c>
-      <c r="B63" s="30" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="C63" s="30" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="D63" s="30" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="E63" s="30" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="F63" s="30" t="n">
-        <v>0.184</v>
+          <t>Offshore Projects — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C63" s="27" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F63" s="27" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Services — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B64" s="27" t="n">
-        <v>355372</v>
-      </c>
-      <c r="C64" s="27" t="n">
-        <v>369587</v>
-      </c>
-      <c r="D64" s="27" t="n">
-        <v>384370</v>
-      </c>
-      <c r="E64" s="27" t="n">
-        <v>399745</v>
-      </c>
-      <c r="F64" s="27" t="n">
-        <v>415735</v>
+          <t>Offshore Projects — earnings margin</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="C64" s="30" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D64" s="30" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E64" s="30" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F64" s="30" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Services — earnings margin</t>
-        </is>
-      </c>
-      <c r="B65" s="30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C65" s="30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D65" s="30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E65" s="30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F65" s="30" t="n">
-        <v>0.2</v>
+          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="n">
+        <v>197164</v>
+      </c>
+      <c r="C65" s="27" t="n">
+        <v>201107</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>205129</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>209232</v>
+      </c>
+      <c r="F65" s="27" t="n">
+        <v>213417</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — earnings margin</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="C66" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="D66" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="E66" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="F66" s="30" t="n">
+        <v>0.184</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>Capital expenditure, depreciation and working capital</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="n"/>
-      <c r="H67" s="14" t="n"/>
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Services — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="n">
+        <v>355372</v>
+      </c>
+      <c r="C67" s="27" t="n">
+        <v>369587</v>
+      </c>
+      <c r="D67" s="27" t="n">
+        <v>384370</v>
+      </c>
+      <c r="E67" s="27" t="n">
+        <v>399745</v>
+      </c>
+      <c r="F67" s="27" t="n">
+        <v>415735</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure (USD 000)</t>
-        </is>
-      </c>
-      <c r="B68" s="27" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="C68" s="27" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="D68" s="27" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="E68" s="27" t="n">
-        <v>700000</v>
-      </c>
-      <c r="F68" s="27" t="n">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation rate on property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="n">
-        <v>0.058</v>
+          <t>Services — earnings margin</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C68" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D68" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E68" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F68" s="30" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
-        </is>
-      </c>
-      <c r="C70" s="27" t="n">
-        <v>109836</v>
-      </c>
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>Capital expenditure, depreciation and working capital</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="n"/>
+      <c r="H70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Days sales outstanding</t>
-        </is>
-      </c>
-      <c r="C71" s="24" t="n">
-        <v>108.3964672240173</v>
+          <t>Capital expenditure (USD 000)</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="C71" s="27" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="D71" s="27" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="E71" s="27" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F71" s="27" t="n">
+        <v>650000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Days inventory outstanding</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="n">
-        <v>14.10679115477453</v>
+          <t>Depreciation rate on property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="n">
+        <v>0.058</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Days payable outstanding</t>
-        </is>
-      </c>
-      <c r="C73" s="24" t="n">
-        <v>131.7339996916174</v>
+          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="n">
+        <v>109836</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Net working capital at 31 December 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C74" s="27" t="n">
-        <v>346415</v>
+          <t>Days sales outstanding</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="n">
+        <v>108.3964672240173</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Days inventory outstanding</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="n">
+        <v>14.10679115477453</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>Tax by business unit and the 2025 depreciation allocation basis</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="n"/>
-      <c r="C76" s="14" t="n"/>
-      <c r="D76" s="14" t="n"/>
-      <c r="E76" s="14" t="n"/>
-      <c r="F76" s="14" t="n"/>
-      <c r="G76" s="14" t="n"/>
-      <c r="H76" s="14" t="n"/>
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Days payable outstanding</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="n">
+        <v>131.7339996916174</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Integrated Logistics — income tax rate</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Shipping — income tax rate</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="n">
-        <v>0.01</v>
+          <t>Net working capital at 31 December 2025 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="n">
+        <v>346415</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Services — income tax rate</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Tax by business unit and the 2025 depreciation allocation basis</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="14" t="n"/>
+      <c r="E79" s="14" t="n"/>
+      <c r="F79" s="14" t="n"/>
+      <c r="G79" s="14" t="n"/>
+      <c r="H79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C80" s="27" t="n">
-        <v>151367</v>
+          <t>Integrated Logistics — income tax rate</t>
+        </is>
+      </c>
+      <c r="C80" s="30" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C81" s="27" t="n">
-        <v>62963</v>
+          <t>Shipping — income tax rate</t>
+        </is>
+      </c>
+      <c r="C81" s="30" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C82" s="27" t="n">
-        <v>8860</v>
+          <t>Services — income tax rate</t>
+        </is>
+      </c>
+      <c r="C82" s="30" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C83" s="27" t="n">
-        <v>195374</v>
+        <v>151367</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C84" s="27" t="n">
-        <v>50526</v>
+        <v>62963</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C85" s="27" t="n">
-        <v>25225</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>Services — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C86" s="27" t="n">
-        <v>30297</v>
+        <v>195374</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="n">
+        <v>50526</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>Funding, distributions and the bridge</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="n"/>
-      <c r="C88" s="14" t="n"/>
-      <c r="D88" s="14" t="n"/>
-      <c r="E88" s="14" t="n"/>
-      <c r="F88" s="14" t="n"/>
-      <c r="G88" s="14" t="n"/>
-      <c r="H88" s="14" t="n"/>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C88" s="27" t="n">
+        <v>25225</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>Net debt at 31 March 2026, company basis (USD 000)</t>
+          <t>Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C89" s="27" t="n">
-        <v>419867</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Deferred consideration on acquisitions (USD 000)</t>
-        </is>
-      </c>
-      <c r="C90" s="27" t="n">
-        <v>301462</v>
+        <v>30297</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Perpetual capital securities at carrying value (USD 000)</t>
-        </is>
-      </c>
-      <c r="C91" s="27" t="n">
-        <v>1978619</v>
-      </c>
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>Funding, distributions and the bridge</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="n"/>
+      <c r="C91" s="14" t="n"/>
+      <c r="D91" s="14" t="n"/>
+      <c r="E91" s="14" t="n"/>
+      <c r="F91" s="14" t="n"/>
+      <c r="G91" s="14" t="n"/>
+      <c r="H91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Perpetual capital securities margin over the overnight rate</t>
-        </is>
-      </c>
-      <c r="C92" s="28" t="n">
-        <v>0.0125</v>
+          <t>Net debt at 31 March 2026, company basis (USD 000)</t>
+        </is>
+      </c>
+      <c r="C92" s="27" t="n">
+        <v>419867</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests at carrying value (USD 000)</t>
+          <t>Deferred consideration on acquisitions (USD 000)</t>
         </is>
       </c>
       <c r="C93" s="27" t="n">
-        <v>272134</v>
+        <v>301462</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests' share of profit</t>
-        </is>
-      </c>
-      <c r="C94" s="30" t="n">
-        <v>0.08799999999999999</v>
+          <t>Perpetual capital securities at carrying value (USD 000)</t>
+        </is>
+      </c>
+      <c r="C94" s="27" t="n">
+        <v>1978619</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Joint ventures and associates at carrying value (USD 000)</t>
-        </is>
-      </c>
-      <c r="C95" s="27" t="n">
-        <v>493120</v>
+          <t>Perpetual capital securities margin over the overnight rate</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="n">
+        <v>0.0125</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
+          <t>Non-controlling interests at carrying value (USD 000)</t>
         </is>
       </c>
       <c r="C96" s="27" t="n">
-        <v>5073902</v>
+        <v>272134</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents held (USD 000)</t>
-        </is>
-      </c>
-      <c r="C97" s="27" t="n">
-        <v>695345</v>
+          <t>Non-controlling interests' share of profit</t>
+        </is>
+      </c>
+      <c r="C97" s="30" t="n">
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (USD 000)</t>
+          <t>Joint ventures and associates at carrying value (USD 000)</t>
         </is>
       </c>
       <c r="C98" s="27" t="n">
-        <v>19434</v>
+        <v>493120</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>Goodwill (USD 000)</t>
+          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C99" s="27" t="n">
-        <v>51368</v>
+        <v>5073902</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+          <t>Cash and cash equivalents held (USD 000)</t>
         </is>
       </c>
       <c r="C100" s="27" t="n">
-        <v>341000</v>
+        <v>695345</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend growth</t>
-        </is>
-      </c>
-      <c r="C101" s="30" t="n">
-        <v>0.05</v>
+          <t>Intangible assets (USD 000)</t>
+        </is>
+      </c>
+      <c r="C101" s="27" t="n">
+        <v>19434</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C102" s="30" t="n">
-        <v>0.02</v>
+          <t>Goodwill (USD 000)</t>
+        </is>
+      </c>
+      <c r="C102" s="27" t="n">
+        <v>51368</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="n">
+        <v>341000</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>Lens weights and the multiple blend</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="n"/>
-      <c r="C104" s="14" t="n"/>
-      <c r="D104" s="14" t="n"/>
-      <c r="E104" s="14" t="n"/>
-      <c r="F104" s="14" t="n"/>
-      <c r="G104" s="14" t="n"/>
-      <c r="H104" s="14" t="n"/>
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividend growth</t>
+        </is>
+      </c>
+      <c r="C104" s="30" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Share of 2026 earnings exposed to spot rates</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="C105" s="30" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>Weight on the enterprise multiple within the relative lens</t>
-        </is>
-      </c>
-      <c r="C106" s="30" t="n">
-        <v>0.7</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C107" s="30" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Lens weights and the multiple blend</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="n"/>
+      <c r="C107" s="14" t="n"/>
+      <c r="D107" s="14" t="n"/>
+      <c r="E107" s="14" t="n"/>
+      <c r="F107" s="14" t="n"/>
+      <c r="G107" s="14" t="n"/>
+      <c r="H107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative multiples</t>
+          <t>Share of 2026 earnings exposed to spot rates</t>
         </is>
       </c>
       <c r="C108" s="30" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings power</t>
+          <t>Weight on the enterprise multiple within the relative lens</t>
         </is>
       </c>
       <c r="C109" s="30" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C110" s="30" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative multiples</t>
+        </is>
+      </c>
+      <c r="C111" s="30" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised earnings power</t>
+        </is>
+      </c>
+      <c r="C112" s="30" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
           <t>Weight — book value and sustainable return</t>
         </is>
       </c>
-      <c r="C110" s="30" t="n">
+      <c r="C113" s="30" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>Every figure on this sheet is an input. Nothing here is computed; everything computed from these cells lives on the sheets that follow.</t>
         </is>
@@ -9354,7 +9501,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
       <c r="D9" s="9">
@@ -9385,7 +9532,7 @@
         </is>
       </c>
       <c r="C11" s="18">
-        <f>-Assumptions!$C$89</f>
+        <f>-Assumptions!$C$92</f>
         <v/>
       </c>
       <c r="D11" s="9">
@@ -9400,7 +9547,7 @@
         </is>
       </c>
       <c r="C12" s="18">
-        <f>-Assumptions!$C$90</f>
+        <f>-Assumptions!$C$93</f>
         <v/>
       </c>
       <c r="D12" s="9">
@@ -9415,7 +9562,7 @@
         </is>
       </c>
       <c r="C13" s="18">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$94</f>
         <v/>
       </c>
       <c r="D13" s="9">
@@ -9430,7 +9577,7 @@
         </is>
       </c>
       <c r="C14" s="18">
-        <f>-Assumptions!$C$93</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
       <c r="D14" s="9">
@@ -9634,7 +9781,7 @@
         </is>
       </c>
       <c r="C28" s="8">
-        <f>Assumptions!$C$105</f>
+        <f>Assumptions!$C$108</f>
         <v/>
       </c>
     </row>
@@ -9679,7 +9826,7 @@
         </is>
       </c>
       <c r="C33" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -9701,7 +9848,7 @@
         </is>
       </c>
       <c r="C35" s="18">
-        <f>-Assumptions!$C$89</f>
+        <f>-Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -9712,7 +9859,7 @@
         </is>
       </c>
       <c r="C36" s="18">
-        <f>-Assumptions!$C$90</f>
+        <f>-Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -9723,7 +9870,7 @@
         </is>
       </c>
       <c r="C37" s="18">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -9734,7 +9881,7 @@
         </is>
       </c>
       <c r="C38" s="18">
-        <f>-Assumptions!$C$93</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -10189,23 +10336,23 @@
         </is>
       </c>
       <c r="B26" s="18">
-        <f>Assumptions!$B$35</f>
+        <f>Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="C26" s="18">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
       <c r="D26" s="18">
-        <f>Assumptions!$D$35</f>
+        <f>Assumptions!$D$38</f>
         <v/>
       </c>
       <c r="E26" s="18">
-        <f>Assumptions!$E$35</f>
+        <f>Assumptions!$E$38</f>
         <v/>
       </c>
       <c r="F26" s="18">
-        <f>Assumptions!$F$35</f>
+        <f>Assumptions!$F$38</f>
         <v/>
       </c>
     </row>
@@ -10216,23 +10363,23 @@
         </is>
       </c>
       <c r="B27" s="18">
-        <f>Assumptions!$B$36</f>
+        <f>Assumptions!$B$39</f>
         <v/>
       </c>
       <c r="C27" s="18">
-        <f>Assumptions!$C$36</f>
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
       <c r="D27" s="18">
-        <f>Assumptions!$D$36</f>
+        <f>Assumptions!$D$39</f>
         <v/>
       </c>
       <c r="E27" s="18">
-        <f>Assumptions!$E$36</f>
+        <f>Assumptions!$E$39</f>
         <v/>
       </c>
       <c r="F27" s="18">
-        <f>Assumptions!$F$36</f>
+        <f>Assumptions!$F$39</f>
         <v/>
       </c>
     </row>
@@ -10270,23 +10417,23 @@
         </is>
       </c>
       <c r="B29" s="18">
-        <f>Assumptions!$B$37</f>
+        <f>Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="C29" s="18">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
       <c r="D29" s="18">
-        <f>Assumptions!$D$37</f>
+        <f>Assumptions!$D$40</f>
         <v/>
       </c>
       <c r="E29" s="18">
-        <f>Assumptions!$E$37</f>
+        <f>Assumptions!$E$40</f>
         <v/>
       </c>
       <c r="F29" s="18">
-        <f>Assumptions!$F$37</f>
+        <f>Assumptions!$F$40</f>
         <v/>
       </c>
     </row>
@@ -10297,23 +10444,23 @@
         </is>
       </c>
       <c r="B30" s="18">
-        <f>Assumptions!$B$38</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="C30" s="18">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
       <c r="D30" s="18">
-        <f>Assumptions!$D$38</f>
+        <f>Assumptions!$D$41</f>
         <v/>
       </c>
       <c r="E30" s="18">
-        <f>Assumptions!$E$38</f>
+        <f>Assumptions!$E$41</f>
         <v/>
       </c>
       <c r="F30" s="18">
-        <f>Assumptions!$F$38</f>
+        <f>Assumptions!$F$41</f>
         <v/>
       </c>
     </row>
@@ -10324,23 +10471,23 @@
         </is>
       </c>
       <c r="B31" s="18">
-        <f>Assumptions!$B$39</f>
+        <f>Assumptions!$B$42</f>
         <v/>
       </c>
       <c r="C31" s="18">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$42</f>
         <v/>
       </c>
       <c r="D31" s="18">
-        <f>Assumptions!$D$39</f>
+        <f>Assumptions!$D$42</f>
         <v/>
       </c>
       <c r="E31" s="18">
-        <f>Assumptions!$E$39</f>
+        <f>Assumptions!$E$42</f>
         <v/>
       </c>
       <c r="F31" s="18">
-        <f>Assumptions!$F$39</f>
+        <f>Assumptions!$F$42</f>
         <v/>
       </c>
     </row>
@@ -10351,23 +10498,23 @@
         </is>
       </c>
       <c r="B32" s="18">
-        <f>Assumptions!$B$40</f>
+        <f>Assumptions!$B$43</f>
         <v/>
       </c>
       <c r="C32" s="18">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="D32" s="18">
-        <f>Assumptions!$D$40</f>
+        <f>Assumptions!$D$43</f>
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>Assumptions!$E$40</f>
+        <f>Assumptions!$E$43</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>Assumptions!$F$40</f>
+        <f>Assumptions!$F$43</f>
         <v/>
       </c>
     </row>
@@ -10378,23 +10525,23 @@
         </is>
       </c>
       <c r="B33" s="31">
-        <f>B31*(1-Assumptions!$C$44)+B30*Assumptions!$C$44</f>
+        <f>B31*(1-Assumptions!$C$47)+B30*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="C33" s="31">
-        <f>C31*(1-Assumptions!$C$44)+C30*Assumptions!$C$44</f>
+        <f>C31*(1-Assumptions!$C$47)+C30*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D33" s="31">
-        <f>D31*(1-Assumptions!$C$44)+D30*Assumptions!$C$44</f>
+        <f>D31*(1-Assumptions!$C$47)+D30*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="E33" s="31">
-        <f>E31*(1-Assumptions!$C$44)+E30*Assumptions!$C$44</f>
+        <f>E31*(1-Assumptions!$C$47)+E30*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="F33" s="31">
-        <f>F31*(1-Assumptions!$C$44)+F30*Assumptions!$C$44</f>
+        <f>F31*(1-Assumptions!$C$47)+F30*Assumptions!$C$47</f>
         <v/>
       </c>
     </row>
@@ -10432,23 +10579,23 @@
         </is>
       </c>
       <c r="B35" s="18">
-        <f>Assumptions!$B$41</f>
+        <f>Assumptions!$B$44</f>
         <v/>
       </c>
       <c r="C35" s="18">
-        <f>Assumptions!$C$41</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="D35" s="18">
-        <f>Assumptions!$D$41</f>
+        <f>Assumptions!$D$44</f>
         <v/>
       </c>
       <c r="E35" s="18">
-        <f>Assumptions!$E$41</f>
+        <f>Assumptions!$E$44</f>
         <v/>
       </c>
       <c r="F35" s="18">
-        <f>Assumptions!$F$41</f>
+        <f>Assumptions!$F$44</f>
         <v/>
       </c>
     </row>
@@ -10685,23 +10832,23 @@
         </is>
       </c>
       <c r="B46" s="31">
-        <f>($B$28*($B$29*Assumptions!$B$50+B38*(1-Assumptions!$B$50))+$C$28*($C$29*Assumptions!$B$50+B39*(1-Assumptions!$B$50))+$D$28*($D$29*Assumptions!$B$50+B40*(1-Assumptions!$B$50))+$E$28*($E$29*Assumptions!$B$50+B41*(1-Assumptions!$B$50))+$F$28*($F$29*Assumptions!$B$50+B42*(1-Assumptions!$B$50)))*365/1000</f>
+        <f>($B$28*($B$29*Assumptions!$B$53+B38*(1-Assumptions!$B$53))+$C$28*($C$29*Assumptions!$B$53+B39*(1-Assumptions!$B$53))+$D$28*($D$29*Assumptions!$B$53+B40*(1-Assumptions!$B$53))+$E$28*($E$29*Assumptions!$B$53+B41*(1-Assumptions!$B$53))+$F$28*($F$29*Assumptions!$B$53+B42*(1-Assumptions!$B$53)))*365/1000</f>
         <v/>
       </c>
       <c r="C46" s="31">
-        <f>($B$28*($B$29*Assumptions!$C$50+C38*(1-Assumptions!$C$50))+$C$28*($C$29*Assumptions!$C$50+C39*(1-Assumptions!$C$50))+$D$28*($D$29*Assumptions!$C$50+C40*(1-Assumptions!$C$50))+$E$28*($E$29*Assumptions!$C$50+C41*(1-Assumptions!$C$50))+$F$28*($F$29*Assumptions!$C$50+C42*(1-Assumptions!$C$50)))*365/1000</f>
+        <f>($B$28*($B$29*Assumptions!$C$53+C38*(1-Assumptions!$C$53))+$C$28*($C$29*Assumptions!$C$53+C39*(1-Assumptions!$C$53))+$D$28*($D$29*Assumptions!$C$53+C40*(1-Assumptions!$C$53))+$E$28*($E$29*Assumptions!$C$53+C41*(1-Assumptions!$C$53))+$F$28*($F$29*Assumptions!$C$53+C42*(1-Assumptions!$C$53)))*365/1000</f>
         <v/>
       </c>
       <c r="D46" s="31">
-        <f>($B$28*($B$29*Assumptions!$D$50+D38*(1-Assumptions!$D$50))+$C$28*($C$29*Assumptions!$D$50+D39*(1-Assumptions!$D$50))+$D$28*($D$29*Assumptions!$D$50+D40*(1-Assumptions!$D$50))+$E$28*($E$29*Assumptions!$D$50+D41*(1-Assumptions!$D$50))+$F$28*($F$29*Assumptions!$D$50+D42*(1-Assumptions!$D$50)))*365/1000</f>
+        <f>($B$28*($B$29*Assumptions!$D$53+D38*(1-Assumptions!$D$53))+$C$28*($C$29*Assumptions!$D$53+D39*(1-Assumptions!$D$53))+$D$28*($D$29*Assumptions!$D$53+D40*(1-Assumptions!$D$53))+$E$28*($E$29*Assumptions!$D$53+D41*(1-Assumptions!$D$53))+$F$28*($F$29*Assumptions!$D$53+D42*(1-Assumptions!$D$53)))*365/1000</f>
         <v/>
       </c>
       <c r="E46" s="31">
-        <f>($B$28*($B$29*Assumptions!$E$50+E38*(1-Assumptions!$E$50))+$C$28*($C$29*Assumptions!$E$50+E39*(1-Assumptions!$E$50))+$D$28*($D$29*Assumptions!$E$50+E40*(1-Assumptions!$E$50))+$E$28*($E$29*Assumptions!$E$50+E41*(1-Assumptions!$E$50))+$F$28*($F$29*Assumptions!$E$50+E42*(1-Assumptions!$E$50)))*365/1000</f>
+        <f>($B$28*($B$29*Assumptions!$E$53+E38*(1-Assumptions!$E$53))+$C$28*($C$29*Assumptions!$E$53+E39*(1-Assumptions!$E$53))+$D$28*($D$29*Assumptions!$E$53+E40*(1-Assumptions!$E$53))+$E$28*($E$29*Assumptions!$E$53+E41*(1-Assumptions!$E$53))+$F$28*($F$29*Assumptions!$E$53+E42*(1-Assumptions!$E$53)))*365/1000</f>
         <v/>
       </c>
       <c r="F46" s="31">
-        <f>($B$28*($B$29*Assumptions!$F$50+F38*(1-Assumptions!$F$50))+$C$28*($C$29*Assumptions!$F$50+F39*(1-Assumptions!$F$50))+$D$28*($D$29*Assumptions!$F$50+F40*(1-Assumptions!$F$50))+$E$28*($E$29*Assumptions!$F$50+F41*(1-Assumptions!$F$50))+$F$28*($F$29*Assumptions!$F$50+F42*(1-Assumptions!$F$50)))*365/1000</f>
+        <f>($B$28*($B$29*Assumptions!$F$53+F38*(1-Assumptions!$F$53))+$C$28*($C$29*Assumptions!$F$53+F39*(1-Assumptions!$F$53))+$D$28*($D$29*Assumptions!$F$53+F40*(1-Assumptions!$F$53))+$E$28*($E$29*Assumptions!$F$53+F41*(1-Assumptions!$F$53))+$F$28*($F$29*Assumptions!$F$53+F42*(1-Assumptions!$F$53)))*365/1000</f>
         <v/>
       </c>
     </row>
@@ -10750,23 +10897,23 @@
         </is>
       </c>
       <c r="B49" s="38">
-        <f>Assumptions!$C$45*(1+Assumptions!$C$46)^1</f>
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^1</f>
         <v/>
       </c>
       <c r="C49" s="38">
-        <f>Assumptions!$C$45*(1+Assumptions!$C$46)^2</f>
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^2</f>
         <v/>
       </c>
       <c r="D49" s="38">
-        <f>Assumptions!$C$45*(1+Assumptions!$C$46)^3</f>
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^3</f>
         <v/>
       </c>
       <c r="E49" s="38">
-        <f>Assumptions!$C$45*(1+Assumptions!$C$46)^4</f>
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^4</f>
         <v/>
       </c>
       <c r="F49" s="38">
-        <f>Assumptions!$C$45*(1+Assumptions!$C$46)^5</f>
+        <f>Assumptions!$C$48*(1+Assumptions!$C$49)^5</f>
         <v/>
       </c>
     </row>
@@ -10831,23 +10978,23 @@
         </is>
       </c>
       <c r="B52" s="39">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="C52" s="39">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="D52" s="39">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="E52" s="39">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="F52" s="39">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
     </row>
@@ -10917,23 +11064,23 @@
         </is>
       </c>
       <c r="B56" s="17">
-        <f>Assumptions!$B$51</f>
+        <f>Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="C56" s="17">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D56" s="17">
-        <f>Assumptions!$D$51</f>
+        <f>Assumptions!$D$54</f>
         <v/>
       </c>
       <c r="E56" s="17">
-        <f>Assumptions!$E$51</f>
+        <f>Assumptions!$E$54</f>
         <v/>
       </c>
       <c r="F56" s="17">
-        <f>Assumptions!$F$51</f>
+        <f>Assumptions!$F$54</f>
         <v/>
       </c>
     </row>
@@ -10944,23 +11091,23 @@
         </is>
       </c>
       <c r="B57" s="31">
-        <f>Assumptions!$C$52*(1+Assumptions!$C$46)^1</f>
+        <f>Assumptions!$C$55*(1+Assumptions!$C$49)^1</f>
         <v/>
       </c>
       <c r="C57" s="31">
-        <f>Assumptions!$C$52*(1+Assumptions!$C$46)^2</f>
+        <f>Assumptions!$C$55*(1+Assumptions!$C$49)^2</f>
         <v/>
       </c>
       <c r="D57" s="31">
-        <f>Assumptions!$C$52*(1+Assumptions!$C$46)^3</f>
+        <f>Assumptions!$C$55*(1+Assumptions!$C$49)^3</f>
         <v/>
       </c>
       <c r="E57" s="31">
-        <f>Assumptions!$C$52*(1+Assumptions!$C$46)^4</f>
+        <f>Assumptions!$C$55*(1+Assumptions!$C$49)^4</f>
         <v/>
       </c>
       <c r="F57" s="31">
-        <f>Assumptions!$C$52*(1+Assumptions!$C$46)^5</f>
+        <f>Assumptions!$C$55*(1+Assumptions!$C$49)^5</f>
         <v/>
       </c>
     </row>
@@ -10998,23 +11145,23 @@
         </is>
       </c>
       <c r="B59" s="8">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="C59" s="8">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="D59" s="8">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="E59" s="8">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="F59" s="8">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
     </row>
@@ -11084,23 +11231,23 @@
         </is>
       </c>
       <c r="B63" s="18">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$59</f>
         <v/>
       </c>
       <c r="C63" s="18">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
       <c r="D63" s="18">
-        <f>Assumptions!$D$56</f>
+        <f>Assumptions!$D$59</f>
         <v/>
       </c>
       <c r="E63" s="18">
-        <f>Assumptions!$E$56</f>
+        <f>Assumptions!$E$59</f>
         <v/>
       </c>
       <c r="F63" s="18">
-        <f>Assumptions!$F$56</f>
+        <f>Assumptions!$F$59</f>
         <v/>
       </c>
     </row>
@@ -11111,23 +11258,23 @@
         </is>
       </c>
       <c r="B64" s="31">
-        <f>B63*Assumptions!$B$57</f>
+        <f>B63*Assumptions!$B$60</f>
         <v/>
       </c>
       <c r="C64" s="31">
-        <f>C63*Assumptions!$C$57</f>
+        <f>C63*Assumptions!$C$60</f>
         <v/>
       </c>
       <c r="D64" s="31">
-        <f>D63*Assumptions!$D$57</f>
+        <f>D63*Assumptions!$D$60</f>
         <v/>
       </c>
       <c r="E64" s="31">
-        <f>E63*Assumptions!$E$57</f>
+        <f>E63*Assumptions!$E$60</f>
         <v/>
       </c>
       <c r="F64" s="31">
-        <f>F63*Assumptions!$F$57</f>
+        <f>F63*Assumptions!$F$60</f>
         <v/>
       </c>
     </row>
@@ -11138,23 +11285,23 @@
         </is>
       </c>
       <c r="B65" s="18">
-        <f>Assumptions!$B$58</f>
+        <f>Assumptions!$B$61</f>
         <v/>
       </c>
       <c r="C65" s="18">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$61</f>
         <v/>
       </c>
       <c r="D65" s="18">
-        <f>Assumptions!$D$58</f>
+        <f>Assumptions!$D$61</f>
         <v/>
       </c>
       <c r="E65" s="18">
-        <f>Assumptions!$E$58</f>
+        <f>Assumptions!$E$61</f>
         <v/>
       </c>
       <c r="F65" s="18">
-        <f>Assumptions!$F$58</f>
+        <f>Assumptions!$F$61</f>
         <v/>
       </c>
     </row>
@@ -11165,23 +11312,23 @@
         </is>
       </c>
       <c r="B66" s="31">
-        <f>B65*Assumptions!$B$59</f>
+        <f>B65*Assumptions!$B$62</f>
         <v/>
       </c>
       <c r="C66" s="31">
-        <f>C65*Assumptions!$C$59</f>
+        <f>C65*Assumptions!$C$62</f>
         <v/>
       </c>
       <c r="D66" s="31">
-        <f>D65*Assumptions!$D$59</f>
+        <f>D65*Assumptions!$D$62</f>
         <v/>
       </c>
       <c r="E66" s="31">
-        <f>E65*Assumptions!$E$59</f>
+        <f>E65*Assumptions!$E$62</f>
         <v/>
       </c>
       <c r="F66" s="31">
-        <f>F65*Assumptions!$F$59</f>
+        <f>F65*Assumptions!$F$62</f>
         <v/>
       </c>
     </row>
@@ -11192,23 +11339,23 @@
         </is>
       </c>
       <c r="B67" s="18">
-        <f>Assumptions!$B$60</f>
+        <f>Assumptions!$B$63</f>
         <v/>
       </c>
       <c r="C67" s="18">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="D67" s="18">
-        <f>Assumptions!$D$60</f>
+        <f>Assumptions!$D$63</f>
         <v/>
       </c>
       <c r="E67" s="18">
-        <f>Assumptions!$E$60</f>
+        <f>Assumptions!$E$63</f>
         <v/>
       </c>
       <c r="F67" s="18">
-        <f>Assumptions!$F$60</f>
+        <f>Assumptions!$F$63</f>
         <v/>
       </c>
     </row>
@@ -11219,23 +11366,23 @@
         </is>
       </c>
       <c r="B68" s="31">
-        <f>B67*Assumptions!$B$61</f>
+        <f>B67*Assumptions!$B$64</f>
         <v/>
       </c>
       <c r="C68" s="31">
-        <f>C67*Assumptions!$C$61</f>
+        <f>C67*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="D68" s="31">
-        <f>D67*Assumptions!$D$61</f>
+        <f>D67*Assumptions!$D$64</f>
         <v/>
       </c>
       <c r="E68" s="31">
-        <f>E67*Assumptions!$E$61</f>
+        <f>E67*Assumptions!$E$64</f>
         <v/>
       </c>
       <c r="F68" s="31">
-        <f>F67*Assumptions!$F$61</f>
+        <f>F67*Assumptions!$F$64</f>
         <v/>
       </c>
     </row>
@@ -11246,23 +11393,23 @@
         </is>
       </c>
       <c r="B69" s="18">
-        <f>Assumptions!$B$62</f>
+        <f>Assumptions!$B$65</f>
         <v/>
       </c>
       <c r="C69" s="18">
-        <f>Assumptions!$C$62</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="D69" s="18">
-        <f>Assumptions!$D$62</f>
+        <f>Assumptions!$D$65</f>
         <v/>
       </c>
       <c r="E69" s="18">
-        <f>Assumptions!$E$62</f>
+        <f>Assumptions!$E$65</f>
         <v/>
       </c>
       <c r="F69" s="18">
-        <f>Assumptions!$F$62</f>
+        <f>Assumptions!$F$65</f>
         <v/>
       </c>
     </row>
@@ -11273,23 +11420,23 @@
         </is>
       </c>
       <c r="B70" s="31">
-        <f>B69*Assumptions!$B$63</f>
+        <f>B69*Assumptions!$B$66</f>
         <v/>
       </c>
       <c r="C70" s="31">
-        <f>C69*Assumptions!$C$63</f>
+        <f>C69*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="D70" s="31">
-        <f>D69*Assumptions!$D$63</f>
+        <f>D69*Assumptions!$D$66</f>
         <v/>
       </c>
       <c r="E70" s="31">
-        <f>E69*Assumptions!$E$63</f>
+        <f>E69*Assumptions!$E$66</f>
         <v/>
       </c>
       <c r="F70" s="31">
-        <f>F69*Assumptions!$F$63</f>
+        <f>F69*Assumptions!$F$66</f>
         <v/>
       </c>
     </row>
@@ -11300,23 +11447,23 @@
         </is>
       </c>
       <c r="B71" s="18">
-        <f>Assumptions!$B$64</f>
+        <f>Assumptions!$B$67</f>
         <v/>
       </c>
       <c r="C71" s="18">
-        <f>Assumptions!$C$64</f>
+        <f>Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="D71" s="18">
-        <f>Assumptions!$D$64</f>
+        <f>Assumptions!$D$67</f>
         <v/>
       </c>
       <c r="E71" s="18">
-        <f>Assumptions!$E$64</f>
+        <f>Assumptions!$E$67</f>
         <v/>
       </c>
       <c r="F71" s="18">
-        <f>Assumptions!$F$64</f>
+        <f>Assumptions!$F$67</f>
         <v/>
       </c>
     </row>
@@ -11327,23 +11474,23 @@
         </is>
       </c>
       <c r="B72" s="31">
-        <f>B71*Assumptions!$B$65</f>
+        <f>B71*Assumptions!$B$68</f>
         <v/>
       </c>
       <c r="C72" s="31">
-        <f>C71*Assumptions!$C$65</f>
+        <f>C71*Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="D72" s="31">
-        <f>D71*Assumptions!$D$65</f>
+        <f>D71*Assumptions!$D$68</f>
         <v/>
       </c>
       <c r="E72" s="31">
-        <f>E71*Assumptions!$E$65</f>
+        <f>E71*Assumptions!$E$68</f>
         <v/>
       </c>
       <c r="F72" s="31">
-        <f>F71*Assumptions!$F$65</f>
+        <f>F71*Assumptions!$F$68</f>
         <v/>
       </c>
     </row>
@@ -12244,7 +12391,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -12255,7 +12402,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>-Assumptions!$C$89</f>
+        <f>-Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -12266,7 +12413,7 @@
         </is>
       </c>
       <c r="C10" s="18">
-        <f>-Assumptions!$C$90</f>
+        <f>-Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -12277,7 +12424,7 @@
         </is>
       </c>
       <c r="C11" s="18">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -12288,7 +12435,7 @@
         </is>
       </c>
       <c r="C12" s="18">
-        <f>-Assumptions!$C$93</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -12354,7 +12501,7 @@
         </is>
       </c>
       <c r="C18" s="8">
-        <f>Assumptions!$C$106</f>
+        <f>Assumptions!$C$109</f>
         <v/>
       </c>
     </row>
@@ -12379,11 +12526,11 @@
         </is>
       </c>
       <c r="C20" s="9">
-        <f>(C5*'Peer &amp; Sector'!$C$11+Assumptions!$C$95-Assumptions!$C$89-Assumptions!$C$90-Assumptions!$C$91-Assumptions!$C$93)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
+        <f>(C5*'Peer &amp; Sector'!$C$11+Assumptions!$C$98-Assumptions!$C$92-Assumptions!$C$93-Assumptions!$C$94-Assumptions!$C$96)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
         <v/>
       </c>
       <c r="D20" s="9">
-        <f>(C5*'Peer &amp; Sector'!$C$10+Assumptions!$C$95-Assumptions!$C$89-Assumptions!$C$90-Assumptions!$C$91-Assumptions!$C$93)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
+        <f>(C5*'Peer &amp; Sector'!$C$10+Assumptions!$C$98-Assumptions!$C$92-Assumptions!$C$93-Assumptions!$C$94-Assumptions!$C$96)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
@@ -12427,7 +12574,7 @@
         </is>
       </c>
       <c r="C25" s="18">
-        <f>Assumptions!$C$89+Assumptions!$C$90</f>
+        <f>Assumptions!$C$92+Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -12482,7 +12629,7 @@
         </is>
       </c>
       <c r="C30" s="33">
-        <f>C24/(Assumptions!$C$96+Assumptions!$C$91)</f>
+        <f>C24/(Assumptions!$C$99+Assumptions!$C$94)</f>
         <v/>
       </c>
     </row>
@@ -12493,7 +12640,7 @@
         </is>
       </c>
       <c r="C31" s="8">
-        <f>Assumptions!$C$100/C24</f>
+        <f>Assumptions!$C$103/C24</f>
         <v/>
       </c>
     </row>
@@ -12539,7 +12686,7 @@
         </is>
       </c>
       <c r="C36" s="31">
-        <f>C35+Assumptions!$C$95-Assumptions!$C$89-Assumptions!$C$90-Assumptions!$C$91-Assumptions!$C$93</f>
+        <f>C35+Assumptions!$C$98-Assumptions!$C$92-Assumptions!$C$93-Assumptions!$C$94-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -12608,11 +12755,11 @@
         </is>
       </c>
       <c r="C42" s="9">
-        <f>(C34*'Peer &amp; Sector'!$C$11+Assumptions!$C$95-Assumptions!$C$89-Assumptions!$C$90-Assumptions!$C$91-Assumptions!$C$93)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
+        <f>(C34*'Peer &amp; Sector'!$C$11+Assumptions!$C$98-Assumptions!$C$92-Assumptions!$C$93-Assumptions!$C$94-Assumptions!$C$96)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
         <v/>
       </c>
       <c r="D42" s="9">
-        <f>(C34*'Peer &amp; Sector'!$C$10+Assumptions!$C$95-Assumptions!$C$89-Assumptions!$C$90-Assumptions!$C$91-Assumptions!$C$93)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
+        <f>(C34*'Peer &amp; Sector'!$C$10+Assumptions!$C$98-Assumptions!$C$92-Assumptions!$C$93-Assumptions!$C$94-Assumptions!$C$96)/Assumptions!$C$6/1000*Assumptions!$C$7</f>
         <v/>
       </c>
     </row>
@@ -12636,7 +12783,7 @@
         </is>
       </c>
       <c r="C45" s="18">
-        <f>Assumptions!$C$96</f>
+        <f>Assumptions!$C$99</f>
         <v/>
       </c>
     </row>
@@ -12691,7 +12838,7 @@
         </is>
       </c>
       <c r="C50" s="8">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$105</f>
         <v/>
       </c>
     </row>
@@ -12723,15 +12870,15 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Bear — return 15% lower against the asset-risk cost of equity (C) / bull — return 15% higher against a lower premium (D)</t>
+          <t>Bear — return 15% lower, discounted at the cost of equity built on the TOP of the beta's 90% confidence interval (C) / bull — return 15% higher, discounted at the cost of equity built on the BOTTOM of the same interval (D)</t>
         </is>
       </c>
       <c r="C53" s="9">
-        <f>(C48*0.85-C50)/(DCF!$C$106-C50)*C47</f>
+        <f>(C48*0.85-C50)/(DCF!$C$115-C50)*C47</f>
         <v/>
       </c>
       <c r="D53" s="9">
-        <f>(C48*1.15-C50)/((DCF!$C$62+0.55*Assumptions!$C$16)-C50)*C47</f>
+        <f>(C48*1.15-C50)/(DCF!$C$114-C50)*C47</f>
         <v/>
       </c>
     </row>
@@ -12805,7 +12952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -13090,23 +13237,23 @@
         </is>
       </c>
       <c r="B13" s="18">
-        <f>-Assumptions!$B$68</f>
+        <f>-Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="C13" s="18">
-        <f>-Assumptions!$C$68</f>
+        <f>-Assumptions!$C$71</f>
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>-Assumptions!$D$68</f>
+        <f>-Assumptions!$D$71</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>-Assumptions!$E$68</f>
+        <f>-Assumptions!$E$71</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>-Assumptions!$F$68</f>
+        <f>-Assumptions!$F$71</f>
         <v/>
       </c>
     </row>
@@ -13423,23 +13570,23 @@
         </is>
       </c>
       <c r="B26" s="31">
-        <f>-B8*(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-B8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="C26" s="31">
-        <f>-C8*(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-C8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="D26" s="31">
-        <f>-D8*(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-D8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="E26" s="31">
-        <f>-E8*(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-E8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="F26" s="31">
-        <f>-F8*(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-F8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
     </row>
@@ -13450,23 +13597,23 @@
         </is>
       </c>
       <c r="B27" s="31">
-        <f>-B8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-B8*(Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="C27" s="31">
-        <f>-C8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-C8*(Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="D27" s="31">
-        <f>-D8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-D8*(Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="E27" s="31">
-        <f>-E8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-E8*(Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="F27" s="31">
-        <f>-F8*(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-F8*(Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
     </row>
@@ -13477,23 +13624,23 @@
         </is>
       </c>
       <c r="B28" s="31">
-        <f>-B8*(Assumptions!$C$86)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-B8*(Assumptions!$C$89)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="C28" s="31">
-        <f>-C8*(Assumptions!$C$86)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-C8*(Assumptions!$C$89)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="D28" s="31">
-        <f>-D8*(Assumptions!$C$86)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-D8*(Assumptions!$C$89)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="E28" s="31">
-        <f>-E8*(Assumptions!$C$86)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-E8*(Assumptions!$C$89)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="F28" s="31">
-        <f>-F8*(Assumptions!$C$86)/(Assumptions!$C$80+Assumptions!$C$81+Assumptions!$C$82+Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86)</f>
+        <f>-F8*(Assumptions!$C$89)/(Assumptions!$C$83+Assumptions!$C$84+Assumptions!$C$85+Assumptions!$C$86+Assumptions!$C$87+Assumptions!$C$88+Assumptions!$C$89)</f>
         <v/>
       </c>
     </row>
@@ -13585,23 +13732,23 @@
         </is>
       </c>
       <c r="B32" s="31">
-        <f>B29*Assumptions!$C$77</f>
+        <f>B29*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="C32" s="31">
-        <f>C29*Assumptions!$C$77</f>
+        <f>C29*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="D32" s="31">
-        <f>D29*Assumptions!$C$77</f>
+        <f>D29*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="E32" s="31">
-        <f>E29*Assumptions!$C$77</f>
+        <f>E29*Assumptions!$C$80</f>
         <v/>
       </c>
       <c r="F32" s="31">
-        <f>F29*Assumptions!$C$77</f>
+        <f>F29*Assumptions!$C$80</f>
         <v/>
       </c>
     </row>
@@ -13612,23 +13759,23 @@
         </is>
       </c>
       <c r="B33" s="31">
-        <f>B30*Assumptions!$C$78</f>
+        <f>B30*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="C33" s="31">
-        <f>C30*Assumptions!$C$78</f>
+        <f>C30*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="D33" s="31">
-        <f>D30*Assumptions!$C$78</f>
+        <f>D30*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="E33" s="31">
-        <f>E30*Assumptions!$C$78</f>
+        <f>E30*Assumptions!$C$81</f>
         <v/>
       </c>
       <c r="F33" s="31">
-        <f>F30*Assumptions!$C$78</f>
+        <f>F30*Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -13639,23 +13786,23 @@
         </is>
       </c>
       <c r="B34" s="31">
-        <f>B31*Assumptions!$C$79</f>
+        <f>B31*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C34" s="31">
-        <f>C31*Assumptions!$C$79</f>
+        <f>C31*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="D34" s="31">
-        <f>D31*Assumptions!$C$79</f>
+        <f>D31*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="E34" s="31">
-        <f>E31*Assumptions!$C$79</f>
+        <f>E31*Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="F34" s="31">
-        <f>F31*Assumptions!$C$79</f>
+        <f>F31*Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -13732,7 +13879,7 @@
         </is>
       </c>
       <c r="C39" s="8">
-        <f>Assumptions!$C$102</f>
+        <f>Assumptions!$C$105</f>
         <v/>
       </c>
     </row>
@@ -13842,7 +13989,7 @@
         </is>
       </c>
       <c r="C49" s="18">
-        <f>Assumptions!$C$95</f>
+        <f>Assumptions!$C$98</f>
         <v/>
       </c>
     </row>
@@ -13864,7 +14011,7 @@
         </is>
       </c>
       <c r="C51" s="18">
-        <f>-Assumptions!$C$89</f>
+        <f>-Assumptions!$C$92</f>
         <v/>
       </c>
     </row>
@@ -13875,7 +14022,7 @@
         </is>
       </c>
       <c r="C52" s="18">
-        <f>-Assumptions!$C$90</f>
+        <f>-Assumptions!$C$93</f>
         <v/>
       </c>
     </row>
@@ -13886,7 +14033,7 @@
         </is>
       </c>
       <c r="C53" s="18">
-        <f>-Assumptions!$C$91</f>
+        <f>-Assumptions!$C$94</f>
         <v/>
       </c>
     </row>
@@ -13897,7 +14044,7 @@
         </is>
       </c>
       <c r="C54" s="18">
-        <f>-Assumptions!$C$93</f>
+        <f>-Assumptions!$C$96</f>
         <v/>
       </c>
     </row>
@@ -14001,7 +14148,7 @@
         </is>
       </c>
       <c r="C64" s="19">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$19</f>
         <v/>
       </c>
     </row>
@@ -14037,7 +14184,7 @@
         </is>
       </c>
       <c r="C68" s="19">
-        <f>Assumptions!$C$21</f>
+        <f>Assumptions!$C$24</f>
         <v/>
       </c>
     </row>
@@ -14048,7 +14195,7 @@
         </is>
       </c>
       <c r="C69" s="19">
-        <f>Assumptions!$C$22</f>
+        <f>Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -14070,7 +14217,7 @@
         </is>
       </c>
       <c r="C71" s="19">
-        <f>Assumptions!$C$23</f>
+        <f>Assumptions!$C$26</f>
         <v/>
       </c>
     </row>
@@ -14081,7 +14228,7 @@
         </is>
       </c>
       <c r="C72" s="19">
-        <f>Assumptions!$C$24</f>
+        <f>Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -14103,7 +14250,7 @@
         </is>
       </c>
       <c r="C74" s="19">
-        <f>Assumptions!$C$25</f>
+        <f>Assumptions!$C$28</f>
         <v/>
       </c>
     </row>
@@ -14114,7 +14261,7 @@
         </is>
       </c>
       <c r="C75" s="19">
-        <f>Assumptions!$C$26</f>
+        <f>Assumptions!$C$29</f>
         <v/>
       </c>
     </row>
@@ -14147,7 +14294,7 @@
         </is>
       </c>
       <c r="C78" s="18">
-        <f>Assumptions!$C$27</f>
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
@@ -14158,7 +14305,7 @@
         </is>
       </c>
       <c r="C79" s="18">
-        <f>Assumptions!$C$28</f>
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -14169,7 +14316,7 @@
         </is>
       </c>
       <c r="C80" s="18">
-        <f>Assumptions!$C$29</f>
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
@@ -14191,7 +14338,7 @@
         </is>
       </c>
       <c r="C82" s="18">
-        <f>Assumptions!$C$30</f>
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -14202,7 +14349,7 @@
         </is>
       </c>
       <c r="C83" s="18">
-        <f>Assumptions!$C$31</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -14213,7 +14360,7 @@
         </is>
       </c>
       <c r="C84" s="18">
-        <f>Assumptions!$C$32</f>
+        <f>Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
@@ -14270,7 +14417,7 @@
         </is>
       </c>
       <c r="C89" s="8">
-        <f>Assumptions!$C$18</f>
+        <f>Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -14361,7 +14508,7 @@
         </is>
       </c>
       <c r="C98" s="19">
-        <f>Assumptions!$C$17</f>
+        <f>Assumptions!$C$20</f>
         <v/>
       </c>
     </row>
@@ -14414,7 +14561,7 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>THE CONTESTED JUDGEMENT — THE SAME MODEL ON AN ASSET-RISK BETA OF 1.00</t>
+          <t>THE CONTESTED JUDGEMENT — THE SAME MODEL ON THE COMPOSITE-INDEX BETA</t>
         </is>
       </c>
       <c r="B104" s="14" t="n"/>
@@ -14426,7 +14573,7 @@
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>Asset-risk beta</t>
+          <t>Beta against an equal-weight composite of the exchange's names — the disclosed alternative construction</t>
         </is>
       </c>
       <c r="C105" s="23">
@@ -14437,7 +14584,7 @@
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity on the asset-risk beta</t>
+          <t>Cost of equity on the composite-index beta</t>
         </is>
       </c>
       <c r="C106" s="42">
@@ -14448,7 +14595,7 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of equity on the asset-risk beta</t>
+          <t>Terminal cost of equity on the composite-index beta</t>
         </is>
       </c>
       <c r="C107" s="42">
@@ -14459,7 +14606,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window, asset-risk beta</t>
+          <t>Cost of capital — explicit window, composite-index beta</t>
         </is>
       </c>
       <c r="C108" s="42">
@@ -14470,7 +14617,7 @@
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of capital, asset-risk beta</t>
+          <t>Terminal cost of capital, composite-index beta</t>
         </is>
       </c>
       <c r="C109" s="42">
@@ -14478,213 +14625,291 @@
         <v/>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>The same cash flows, discounted at the asset-risk cost of capital</t>
-        </is>
-      </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>Forward cost of capital — the glide</t>
-        </is>
-      </c>
-      <c r="B111" s="42">
-        <f>$C$108+($C$109-$C$108)*1/5</f>
-        <v/>
-      </c>
-      <c r="C111" s="42">
-        <f>$C$108+($C$109-$C$108)*2/5</f>
-        <v/>
-      </c>
-      <c r="D111" s="42">
-        <f>$C$108+($C$109-$C$108)*3/5</f>
-        <v/>
-      </c>
-      <c r="E111" s="42">
-        <f>$C$108+($C$109-$C$108)*4/5</f>
-        <v/>
-      </c>
-      <c r="F111" s="42">
-        <f>$C$108+($C$109-$C$108)*5/5</f>
-        <v/>
-      </c>
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>HOW PRECISE THE PRIMARY BETA IS — THE INTERVAL AROUND IT, PRICED</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="n"/>
+      <c r="C111" s="14" t="n"/>
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="B112" s="43">
-        <f>1/(1+B111)^Assumptions!$C$8</f>
-        <v/>
-      </c>
-      <c r="C112" s="43">
-        <f>B112/(1+C111)</f>
-        <v/>
-      </c>
-      <c r="D112" s="43">
-        <f>C112/(1+D111)</f>
-        <v/>
-      </c>
-      <c r="E112" s="43">
-        <f>D112/(1+E111)</f>
-        <v/>
-      </c>
-      <c r="F112" s="43">
-        <f>E112/(1+F111)</f>
+          <t>Beta — lower bound of the 90% confidence interval on the primary regression</t>
+        </is>
+      </c>
+      <c r="C112" s="23">
+        <f>Assumptions!$C$16</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Present value of free cash flow</t>
-        </is>
-      </c>
-      <c r="B113" s="31">
-        <f>B17*B112</f>
-        <v/>
-      </c>
-      <c r="C113" s="31">
-        <f>C17*C112</f>
-        <v/>
-      </c>
-      <c r="D113" s="31">
-        <f>D17*D112</f>
-        <v/>
-      </c>
-      <c r="E113" s="31">
-        <f>E17*E112</f>
-        <v/>
-      </c>
-      <c r="F113" s="31">
-        <f>F17*F112</f>
+          <t>Beta — upper bound of the 90% confidence interval on the primary regression</t>
+        </is>
+      </c>
+      <c r="C113" s="23">
+        <f>Assumptions!$C$17</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Present value of the five forecast years</t>
-        </is>
-      </c>
-      <c r="C114" s="31">
-        <f>SUM(B113:F113)</f>
+          <t>Cost of equity at the lower confidence bound — the bull-case discount rate</t>
+        </is>
+      </c>
+      <c r="C114" s="42">
+        <f>C62+C112*C64</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Terminal value</t>
-        </is>
-      </c>
-      <c r="C115" s="31">
-        <f>C43*(1-C42)/(C109-C39)</f>
+          <t>Cost of equity at the upper confidence bound — the bear-case discount rate</t>
+        </is>
+      </c>
+      <c r="C115" s="42">
+        <f>C62+C113*C64</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Present value of the terminal value</t>
-        </is>
-      </c>
-      <c r="C116" s="31">
-        <f>C115*F112</f>
+          <t>Beta — lead-lag sum beta, one lead and two lags</t>
+        </is>
+      </c>
+      <c r="C116" s="23">
+        <f>Assumptions!$C$18</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value of operations</t>
-        </is>
-      </c>
-      <c r="C117" s="31">
-        <f>C114+C116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Terminal value as a share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C118" s="10">
-        <f>C116/C117</f>
+          <t>Cost of equity on the lead-lag sum beta</t>
+        </is>
+      </c>
+      <c r="C117" s="42">
+        <f>C62+C116*C64</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="C119" s="31">
-        <f>C117+C49</f>
-        <v/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>The same cash flows, discounted at the composite-index cost of capital</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
+          <t>Forward cost of capital — the glide</t>
+        </is>
+      </c>
+      <c r="B120" s="42">
+        <f>$C$108+($C$109-$C$108)*1/5</f>
+        <v/>
+      </c>
+      <c r="C120" s="42">
+        <f>$C$108+($C$109-$C$108)*2/5</f>
+        <v/>
+      </c>
+      <c r="D120" s="42">
+        <f>$C$108+($C$109-$C$108)*3/5</f>
+        <v/>
+      </c>
+      <c r="E120" s="42">
+        <f>$C$108+($C$109-$C$108)*4/5</f>
+        <v/>
+      </c>
+      <c r="F120" s="42">
+        <f>$C$108+($C$109-$C$108)*5/5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="B121" s="43">
+        <f>1/(1+B120)^Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="C121" s="43">
+        <f>B121/(1+C120)</f>
+        <v/>
+      </c>
+      <c r="D121" s="43">
+        <f>C121/(1+D120)</f>
+        <v/>
+      </c>
+      <c r="E121" s="43">
+        <f>D121/(1+E120)</f>
+        <v/>
+      </c>
+      <c r="F121" s="43">
+        <f>E121/(1+F120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Present value of free cash flow</t>
+        </is>
+      </c>
+      <c r="B122" s="31">
+        <f>B17*B121</f>
+        <v/>
+      </c>
+      <c r="C122" s="31">
+        <f>C17*C121</f>
+        <v/>
+      </c>
+      <c r="D122" s="31">
+        <f>D17*D121</f>
+        <v/>
+      </c>
+      <c r="E122" s="31">
+        <f>E17*E121</f>
+        <v/>
+      </c>
+      <c r="F122" s="31">
+        <f>F17*F121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Present value of the five forecast years</t>
+        </is>
+      </c>
+      <c r="C123" s="31">
+        <f>SUM(B122:F122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value</t>
+        </is>
+      </c>
+      <c r="C124" s="31">
+        <f>C43*(1-C42)/(C109-C39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Present value of the terminal value</t>
+        </is>
+      </c>
+      <c r="C125" s="31">
+        <f>C124*F121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise value of operations</t>
+        </is>
+      </c>
+      <c r="C126" s="31">
+        <f>C123+C125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value as a share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C127" s="10">
+        <f>C125/C126</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C128" s="31">
+        <f>C126+C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
           <t>Equity attributable to ordinary shareholders</t>
         </is>
       </c>
-      <c r="C120" s="31">
-        <f>C119+C51+C52+C53+C54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="14" t="inlineStr">
-        <is>
-          <t>Fair value per share (AED) — asset-risk beta</t>
-        </is>
-      </c>
-      <c r="B121" s="14" t="n"/>
-      <c r="C121" s="15">
-        <f>C120/Assumptions!$C$6/1000*Assumptions!$C$7</f>
-        <v/>
-      </c>
-      <c r="D121" s="14" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>The two readings above are carried side by side and are never averaged. The regressed beta is the primary reading because it passes the usability gate on the stock's own history; the asset-risk beta is what a listed fleet owner might instead be expected to carry, and the gap between the two is the single most consequential judgement in this study.</t>
+      <c r="C129" s="31">
+        <f>C128+C51+C52+C53+C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>Fair value per share (AED) — composite-index beta</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="n"/>
+      <c r="C130" s="15">
+        <f>C129/Assumptions!$C$6/1000*Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D130" s="14" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>The two readings above are carried side by side and are never averaged. They are the SAME regression of the same weekly returns; only the measure of the market differs. The published index of the exchange is what the method asks for and is the primary reading — it is weighted by size, and is therefore dominated by the same large-capitalisation group this company belongs to. The equal-weight composite gives the exchange's smallest names the same say as its largest and is the construction an earlier version of this study used; it is published beside the primary reading because a gap of this size is a fact about how the index is built, not about the company, and the reader is entitled to see it. The gap between the two is the single most consequential judgement in this study.</t>
         </is>
       </c>
     </row>
@@ -15478,23 +15703,23 @@
         <v>18959</v>
       </c>
       <c r="E22" s="18">
-        <f>Assumptions!$C$21*Assumptions!$C$97</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="F22" s="18">
-        <f>Assumptions!$C$21*Assumptions!$C$97</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="G22" s="18">
-        <f>Assumptions!$C$21*Assumptions!$C$97</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="H22" s="18">
-        <f>Assumptions!$C$21*Assumptions!$C$97</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100</f>
         <v/>
       </c>
       <c r="I22" s="18">
-        <f>Assumptions!$C$21*Assumptions!$C$97</f>
+        <f>Assumptions!$C$24*Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -15664,23 +15889,23 @@
         <v>-24306</v>
       </c>
       <c r="E27" s="31">
-        <f>-E26*Assumptions!$C$94</f>
+        <f>-E26*Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="F27" s="31">
-        <f>-F26*Assumptions!$C$94</f>
+        <f>-F26*Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="G27" s="31">
-        <f>-G26*Assumptions!$C$94</f>
+        <f>-G26*Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="H27" s="31">
-        <f>-H26*Assumptions!$C$94</f>
+        <f>-H26*Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="I27" s="31">
-        <f>-I26*Assumptions!$C$94</f>
+        <f>-I26*Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -15739,23 +15964,23 @@
         <v>-61333</v>
       </c>
       <c r="E29" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F29" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="G29" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="H29" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="I29" s="31">
-        <f>-Assumptions!$C$91*(Assumptions!$C$21+Assumptions!$C$92)</f>
+        <f>-Assumptions!$C$94*(Assumptions!$C$24+Assumptions!$C$95)</f>
         <v/>
       </c>
     </row>

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -5101,16 +5101,16 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>8.821143313217801</v>
+        <v>7.684059821165052</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>9.403767556239309</v>
+        <v>8.089468651542681</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>10.13964211125459</v>
+        <v>8.585870670520746</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>11.10110240007209</v>
+        <v>9.209641660332705</v>
       </c>
     </row>
     <row r="7">
@@ -5120,16 +5120,16 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>7.377139043473286</v>
+        <v>6.521904241629056</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>7.739575354063446</v>
+        <v>6.779643881894967</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>8.17954270903156</v>
+        <v>7.085238719949822</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>8.726572606786965</v>
+        <v>7.454596803798754</v>
       </c>
     </row>
     <row r="8">
@@ -5139,16 +5139,16 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6.336732732190536</v>
+        <v>5.661976211130093</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>6.573581007511788</v>
+        <v>5.831947183128495</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>6.852892465948203</v>
+        <v>6.028543766541673</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>7.188337826923521</v>
+        <v>6.259397237851367</v>
       </c>
     </row>
     <row r="9">
@@ -5158,16 +5158,16 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>5.594985790205619</v>
+        <v>5.036939713504717</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>5.758498704864779</v>
+        <v>5.154177217420941</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>5.947214608798108</v>
+        <v>5.287160500641522</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>6.168263183774388</v>
+        <v>5.439908589636779</v>
       </c>
     </row>
     <row r="10">
@@ -5177,22 +5177,22 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>4.991669767894912</v>
+        <v>4.52102003401324</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>5.105151875101628</v>
+        <v>4.601537559133286</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>5.23366042288852</v>
+        <v>4.691207672798638</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>5.380993860983772</v>
+        <v>4.792139844400095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.085 is the adopted regression against the exchange's published index, and 1.412 is the top of that regression's own 90% confidence interval (its bottom, 0.758, sits just above the composite reading). READ THIS GRID AS A SHAPE, NOT AS A LEVEL. Every cell is a complete re-run of the model discounted at a rate built from the equity and the debt alone. The rate the valuation itself uses also carries the perpetual capital securities at their own coupon, which makes it dearer — 8.49% against 7.86% over the forecast years and 7.73% against 7.16% in the terminal — so every cell here sits above the published figure. At the 1.085 row and the 2.0% column the grid reads AED 6.85 against the published AED 6.03, a gap of 13.7%. What the grid is for is the slope: how much the answer moves for a given move in the beta or in terminal growth.</t>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.085 is the adopted regression against the exchange's published index, and 1.412 is the top of that regression's own 90% confidence interval (its bottom, 0.758, sits just above the composite reading). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.085 row is the published cash-flow value of AED 6.03 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>5.185674797723733</v>
+        <v>5.121306811301282</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>5.644016771814515</v>
+        <v>5.574925288921477</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>6.102358745905295</v>
+        <v>6.028543766541673</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>6.560700719996079</v>
+        <v>6.482162244161869</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>7.019042694086861</v>
+        <v>6.935780721782064</v>
       </c>
     </row>
     <row r="15">
@@ -5274,7 +5274,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>The same caution applies to this row and the one below it: each is a re-run discounted over the forecast years at 7.86%, the rate the equity and the debt alone imply, rather than at the 8.49% the valuation uses. At 1.00x it reads AED 6.10 against the published AED 6.03, 1.2% above it. The swing across the row is what it is for.</t>
+          <t>This row and the one below it are re-runs of the whole model at the same 8.49% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 6.03 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
         </is>
       </c>
     </row>
@@ -5322,16 +5322,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6.515320858093369</v>
+        <v>6.437907235122407</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6.102358745905295</v>
+        <v>6.028543766541673</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>5.689396633717223</v>
+        <v>5.619180297960939</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>5.276434521529151</v>
+        <v>5.209816829380204</v>
       </c>
     </row>
     <row r="20">
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="C6" s="21" t="n">
-        <v>3.840998691014435</v>
+        <v>3.790471085198643</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>9.379477215384453</v>
+        <v>9.270835477800441</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -18332,11 +18332,11 @@
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital — explicit window, composite-index beta. The contested change is the cost of EQUITY, so the alternative reprices the equity leg over the explicit window and leaves the perpetual leg to the terminal, where its cost has normalised</t>
+          <t>Cost of capital — explicit window, composite-index beta. Only the cost of EQUITY changes: the same three tranches of capital are carried, because how the market is measured does not change what the company is financed with</t>
         </is>
       </c>
       <c r="C117" s="49">
-        <f>C101*C115+C102*C94</f>
+        <f>C101*C115+C102*C94+C103*C104</f>
         <v/>
       </c>
     </row>

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="114" customWidth="1" min="1" max="1"/>
@@ -683,307 +683,488 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing exactly which.</t>
+          <t>FOUR THINGS ARE PASTED VALUES, and it is worth knowing exactly which.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (1) AUDITED AND DISCLOSED HISTORY — the primary record, not a calculation. Where a line is both disclosed</t>
+          <t xml:space="preserve">  (1) THE INDEPENDENT INPUTS ON THE ASSUMPTIONS SHEET — the blue cells: disclosed vessel counts, published</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      and arithmetically derivable, the DISCLOSED figure is carried, because the filing is the record.</t>
+          <t xml:space="preserve">      day rates, the twelve charter fixtures and their dates, the balance-sheet anchors, the tax rates and</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2) THE OUTPUT OF A UNIT BUILD that would be unreadable flattened into a grid — the historical segment</t>
+          <t xml:space="preserve">      the study judgements. Anything on that sheet that is itself DERIVED from other inputs is a GREEN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      revenue and earnings table, which the operating-segments note gives directly.</t>
+          <t xml:space="preserve">      formula pointing at the build that produces it — the running cost per vessel-day, the gas-carrier day</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (3) WHOLE-MODEL RE-RUNS, where each figure is a complete revaluation of the entire model and so cannot be</t>
+          <t xml:space="preserve">      rate, the three days ratios and the opening working capital are all solved elsewhere and only shown</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      a single formula: the Monte Carlo price map, the two sensitivity grids, the discounted-cash-flow</t>
+          <t xml:space="preserve">      there, so a reader can never mistake an output for an assumption.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      bear and bull bounds (each of which re-runs the fleet build at a different rate anchor, a different</t>
+          <t xml:space="preserve">  (2) AUDITED AND DISCLOSED HISTORY — the primary record, not a calculation. Where a line is both disclosed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      beta — the two ends of the regression's own confidence interval — and a different capital-expenditure</t>
+          <t xml:space="preserve">      and arithmetically derivable, the DISCLOSED figure is carried, because the filing is the record.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">      path) and the three expert-panel legs.</t>
+          <t xml:space="preserve">  (3) THE OUTPUT OF A UNIT BUILD that would be unreadable flattened into a grid — the historical segment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MONTE CARLO AND SENSITIVITY GRIDS DO NOT REDRAW WHEN A DRIVER IS CHANGED. Changing a blue cell</t>
+          <t xml:space="preserve">      revenue and earnings table, which the operating-segments note gives directly.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reprices the whole valuation chain, but those grids are engine outputs and stay as they were run.</t>
+          <t xml:space="preserve">  (4) WHOLE-MODEL RE-RUNS, where each figure is a complete revaluation of the entire model and so cannot be</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Anything else pasted is a defect.</t>
+          <t xml:space="preserve">      a single formula: the Monte Carlo price map, the two sensitivity grids, the discounted-cash-flow</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      bear and bull bounds (each of which re-runs the fleet build at a different rate anchor, a different</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. The tanker fleet is built vessel by vessel: fifty-three owned</t>
+          <t xml:space="preserve">      beta — the two ends of the regression's own confidence interval — and a different capital-expenditure</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>vessels split into those trading at spot rates and those on charters out at rates already fixed and</t>
+          <t xml:space="preserve">      path) and the three expert-panel legs.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>disclosed, each class earning its own time-charter equivalent per day over 365 days, less an all-in running</t>
+          <t xml:space="preserve">  THE MONTE CARLO AND SENSITIVITY GRIDS DO NOT REDRAW WHEN A DRIVER IS CHANGED. Changing a blue cell</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>cost per vessel per day escalated on a services-and-wage escalator. The gas carriers are built from</t>
+          <t xml:space="preserve">  reprices the whole valuation chain, but those grids are engine outputs and stay as they were run.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>contracted vessel-years times an implied day rate. The five remaining units are grown on their own revenue</t>
+          <t xml:space="preserve">  Anything else pasted is a defect.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>and margin drivers, anchored on what each actually earned in the first quarter of 2026.</t>
-        </is>
-      </c>
+      <c r="A39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>How revenue is built. Not as one growth rate, and not off the published rate either. The company gives one</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS — HOW THE MARKET IS MEASURED. The same weekly regression of the</t>
+          <t>rate per vessel class each quarter, and its own chief financial officer said on the first-quarter call that</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>stock's own returns is run against two different measures of its market, and the answer moves a long way</t>
+          <t>this rate is a BLEND across the whole class, the vessels on charters out included. So the SPOT rate is not</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>between them. Against the published index of the exchange the share is listed on — the index the method</t>
+          <t>read off that disclosure — it is SOLVED out of it, window by window: the published blend times the class</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>asks for, and the primary reading — the beta is 1.085. Against an equal-weight composite of that same</t>
+          <t>vessel-days, less the revenue the twelve disclosed fixtures earn over exactly the days their own contracts</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>exchange's names, which gives its smallest listings the same say as its largest, the beta is</t>
+          <t>run, divided by the vessel-days that actually traded spot. Every step of that derivation is on the Segments</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
+          <t>sheet, cell by cell. The forecast then prices each vessel on its own terms — chartered vessels at their</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>company belongs to; the composite is not. That single difference in construction, and nothing about the</t>
+          <t>contracted rate for their contracted days, everything else at the implied spot rate — less an all-in running</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>company, moves the cost of equity and the cash-flow value materially. BOTH are carried through the model in</t>
+          <t>cost per vessel-day that is itself solved so the same construction reproduces the tanker earnings the company</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>full, side by side, on the Summary, Fundamental Valuation and DCF sheets. They are NOT averaged into one</t>
+          <t>reported for 2025. The gas carriers are contracted vessel-years times a day rate solved the same way. The</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>number. The regression's own 90% confidence interval on the primary estimate runs 0.758 to 1.412, and</t>
+          <t>five remaining units are grown on their own revenue and margin drivers, anchored on what each actually</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>those two bounds — not round numbers chosen by hand — are the betas used in the bear and bull cases, so the</t>
+          <t>earned in the first quarter of 2026.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>published range is the range the estimate itself supports.</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>THE COST OF CAPITAL CARRIES THREE TRANCHES, NOT TWO: equity, debt, and the perpetual capital securities at</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>their own coupon. Those securities rank ahead of the ordinary shares and are deducted in the equity bridge,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges and distributions.</t>
+          <t>and a claim that is deducted from enterprise value has to be weighted in the rate as well — the two are</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>halves of one treatment. The coupon is an equity distribution rather than interest, so it is not taxed down.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
+          <t>Every construction in the workbook carries the same three tranches, including the sensitivity re-runs, so</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+          <t>the sensitivity grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
-        </is>
-      </c>
+      <c r="A59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>is listed with its value, source and date in the companion bibliography document.</t>
+          <t>THE BOOK LENS IS A RESIDUAL INCOME BUILD. A single-stage justified price-to-book assumes a steady state this</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>company is not in: it pays out about a third of its earnings and compounds its book above its own cost of</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+          <t>equity, where that formula is undefined rather than merely wrong. The lens is instead the book the company</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+          <t>already has, plus the present value of earning more than the cost of equity on it for five years, plus a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
+          <t>remainder in which that excess fades. The whole ladder is live on the Relative &amp; Normalized sheet, three</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+          <t>times over — base, bear and bull — and the return it is struck on is what the ORDINARY holders earn, after</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>the perpetual coupon that ranks ahead of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS — HOW THE MARKET IS MEASURED. The same weekly regression of the</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>stock's own returns is run against two different measures of its market, and the answer moves a long way</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>between them. Against the published index of the exchange the share is listed on — the index the method</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>asks for, and the primary reading — the beta is 1.085. Against an equal-weight composite of that same</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>exchange's names, which gives its smallest listings the same say as its largest, the beta is</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>company belongs to; the composite is not. That single difference in construction, and nothing about the</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>company, moves the cost of equity and the cash-flow value materially. BOTH are carried through the model in</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>full, side by side, on the Summary, Fundamental Valuation and DCF sheets. They are NOT averaged into one</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>number. The regression's own 90% confidence interval on the primary estimate runs 0.758 to 1.412, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>those two bounds — not round numbers chosen by hand — are the betas used in the bear and bull cases, so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>published range is the range the estimate itself supports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>shown as ranges and distributions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>is listed with its value, source and date in the companion bibliography document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Sensitivity · Per-Share &amp; Ratios · Peer &amp; Sector.</t>
         </is>
@@ -7615,7 +7796,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>justified price-to-book on the sustainable return on equity</t>
+          <t>the book the company already has, plus the present value of earning more than the cost of equity on it while that lasts, plus a fading remainder — a residual income build, not a justified multiple</t>
         </is>
       </c>
       <c r="C10" s="7">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="114" customWidth="1" min="1" max="1"/>
@@ -970,352 +970,425 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate, and not off the published rate either. The company gives one</t>
+          <t>AND THE BETA HAS BEEN RE-MEASURED. It is now produced by the same standard routine used for every share</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>rate per vessel class each quarter, and its own chief financial officer said on the first-quarter call that</t>
+          <t>covered on this desk: the market series is resolved from the exchange the share is listed on rather than</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>this rate is a BLEND across the whole class, the vessels on charters out included. So the SPOT rate is not</t>
+          <t>chosen, both series are screened for data quality before they are paired, and the weekly returns are</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>read off that disclosure — it is SOLVED out of it, window by window: the published blend times the class</t>
+          <t>measured on that exchange's own trading week. The series it resolved is the one this study already used, so</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>vessel-days, less the revenue the twelve disclosed fixtures earn over exactly the days their own contracts</t>
+          <t>WHICH market the share is measured against has not changed — but the grid and the screening do move the</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>run, divided by the vessel-days that actually traded spot. Every step of that derivation is on the Segments</t>
+          <t>figure: the slope is now 1.1032 on 159 weekly observations, and its 90% confidence interval</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>sheet, cell by cell. The forecast then prices each vessel on its own terms — chartered vessels at their</t>
+          <t>runs 0.586 to 1.621, materially WIDER than the interval the previous edition</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>contracted rate for their contracted days, everything else at the implied spot rate — less an all-in running</t>
+          <t>published. The bear and bull cases take those two bounds directly, so the published range widens with it.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>cost per vessel-day that is itself solved so the same construction reproduces the tanker earnings the company</t>
+          <t>A range that widens on re-measurement is information about how much a three-year price history can settle,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>reported for 2025. The gas carriers are contracted vessel-years times a day rate solved the same way. The</t>
+          <t>not an embarrassment to be smoothed away.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>five remaining units are grown on their own revenue and margin drivers, anchored on what each actually</t>
-        </is>
-      </c>
+      <c r="A72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>earned in the first quarter of 2026.</t>
+          <t>How revenue is built. Not as one growth rate, and not off the published rate either. The company gives one</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>rate per vessel class each quarter, and its own chief financial officer said on the first-quarter call that</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>THE COST OF CAPITAL CARRIES THREE TRANCHES, NOT TWO: equity, debt, and the perpetual capital securities at</t>
+          <t>this rate is a BLEND across the whole class, the vessels on charters out included. So the SPOT rate is not</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>their own coupon. Those securities rank ahead of the ordinary shares and are deducted in the equity bridge,</t>
+          <t>read off that disclosure — it is SOLVED out of it, window by window: the published blend times the class</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>and a claim that is deducted from enterprise value has to be weighted in the rate as well — the two are</t>
+          <t>vessel-days, less the revenue the twelve disclosed fixtures earn over exactly the days their own contracts</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>halves of one treatment. The coupon is an equity distribution rather than interest, so it is not taxed down.</t>
+          <t>run, divided by the vessel-days that actually traded spot. Every step of that derivation is on the Segments</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Every construction in the workbook carries the same three tranches, including the sensitivity re-runs, so</t>
+          <t>sheet, cell by cell. The forecast then prices each vessel on its own terms — chartered vessels at their</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>the sensitivity grid is centred on the figure it brackets.</t>
+          <t>contracted rate for their contracted days, everything else at the implied spot rate — less an all-in running</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>cost per vessel-day that is itself solved so the same construction reproduces the tanker earnings the company</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>THE BOOK LENS IS A RESIDUAL INCOME BUILD. A single-stage justified price-to-book assumes a steady state this</t>
+          <t>reported for 2025. The gas carriers are contracted vessel-years times a day rate solved the same way. The</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>company is not in: it pays out about a third of its earnings and compounds its book above its own cost of</t>
+          <t>five remaining units are grown on their own revenue and margin drivers, anchored on what each actually</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>equity, where that formula is undefined rather than merely wrong. The lens is instead the book the company</t>
+          <t>earned in the first quarter of 2026.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>already has, plus the present value of earning more than the cost of equity on it for five years, plus a</t>
-        </is>
-      </c>
+      <c r="A85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>remainder in which that excess fades. The whole ladder is live on the Relative &amp; Normalized sheet, three</t>
+          <t>THE COST OF CAPITAL CARRIES THREE TRANCHES, NOT TWO: equity, debt, and the perpetual capital securities at</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>times over — base, bear and bull — and the return it is struck on is what the ORDINARY holders earn, after</t>
+          <t>their own coupon. Those securities rank ahead of the ordinary shares and are deducted in the equity bridge,</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>the perpetual coupon that ranks ahead of them.</t>
+          <t>and a claim that is deducted from enterprise value has to be weighted in the rate as well — the two are</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr"/>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>halves of one treatment. The coupon is an equity distribution rather than interest, so it is not taxed down.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS — HOW THE MARKET IS MEASURED. The same weekly regression of the</t>
+          <t>Every construction in the workbook carries the same three tranches, including the sensitivity re-runs, so</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>stock's own returns is run against two different measures of its market, and the answer moves a long way</t>
+          <t>the sensitivity grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>between them. Against the published index of the exchange the share is listed on — the index the method</t>
-        </is>
-      </c>
+      <c r="A92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>asks for, and the primary reading — the beta is 1.085. Against an equal-weight composite of that same</t>
+          <t>THE BOOK LENS IS A RESIDUAL INCOME BUILD. A single-stage justified price-to-book assumes a steady state this</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>exchange's names, which gives its smallest listings the same say as its largest, the beta is</t>
+          <t>company is not in: it pays out about a third of its earnings and compounds its book above its own cost of</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
+          <t>equity, where that formula is undefined rather than merely wrong. The lens is instead the book the company</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>company belongs to; the composite is not. That single difference in construction, and nothing about the</t>
+          <t>already has, plus the present value of earning more than the cost of equity on it for five years, plus a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>company, moves the cost of equity and the cash-flow value materially. BOTH are carried through the model in</t>
+          <t>remainder in which that excess fades. The whole ladder is live on the Relative &amp; Normalized sheet, three</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>full, side by side, on the Summary, Fundamental Valuation and DCF sheets. They are NOT averaged into one</t>
+          <t>times over — base, bear and bull — and the return it is struck on is what the ORDINARY holders earn, after</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>number. The regression's own 90% confidence interval on the primary estimate runs 0.758 to 1.412, and</t>
+          <t>the perpetual coupon that ranks ahead of them.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>those two bounds — not round numbers chosen by hand — are the betas used in the bear and bull cases, so the</t>
-        </is>
-      </c>
+      <c r="A100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>published range is the range the estimate itself supports.</t>
+          <t>THE CONTESTED JUDGEMENT, PUBLISHED BOTH WAYS — HOW THE MARKET IS MEASURED. The same weekly regression of the</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr"/>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>stock's own returns is run against two different measures of its market, and the answer moves a long way</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>between them. Against the published index of the exchange the share is listed on — the index the method</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges and distributions.</t>
+          <t>asks for, and the primary reading — the beta is 1.103. Against an equal-weight composite of that same</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>exchange's names, which gives its smallest listings the same say as its largest, the beta is</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
+          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+          <t>company belongs to; the composite is not. That single difference in construction, and nothing about the</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
+          <t>company, moves the cost of equity and the cash-flow value materially. BOTH are carried through the model in</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>is listed with its value, source and date in the companion bibliography document.</t>
+          <t>full, side by side, on the Summary, Fundamental Valuation and DCF sheets. They are NOT averaged into one</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr"/>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>number. The regression's own 90% confidence interval on the primary estimate runs 0.586 to 1.621, and</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+          <t>those two bounds — not round numbers chosen by hand — are the betas used in the bear and bull cases, so the</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+          <t>published range is the range the estimate itself supports.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
-        </is>
-      </c>
+      <c r="A113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>shown as ranges and distributions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 come from the company's own audited consolidated</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>financial statements; the first quarter of 2026 comes from the reviewed interim statements; the fleet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>rate and contract data come from the company's own investor presentations and earnings calls. Every input</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>is listed with its value, source and date in the companion bibliography document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Currency. US dollar thousand unless stated — the company reports in US dollars. Per-share figures are in</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>dirhams at the fixed parity of 3.6725 dirhams to the dollar. Spot AED 6.16 (2026-08-07 close).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Sheets: READ FIRST · Summary · Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Normalized · DCF · Income Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>Sensitivity · Per-Share &amp; Ratios · Peer &amp; Sector.</t>
         </is>
@@ -5497,64 +5570,64 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1.085</t>
+          <t>1.103</t>
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6.104211768824626</v>
+        <v>6.020153084134909</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>6.290365806735382</v>
+        <v>6.198777837752638</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>6.50557697172203</v>
+        <v>6.404817896532908</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>6.758173447014873</v>
+        <v>6.646025779733348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>1.350</t>
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>5.400935220772635</v>
+        <v>5.031072269544037</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>5.528638734441224</v>
+        <v>5.132117653317763</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>5.673387508676271</v>
+        <v>5.245334010186813</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>5.839532255632811</v>
+        <v>5.373634668456338</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>1.621</t>
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>4.819724922415764</v>
+        <v>4.192019140583034</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>4.906776041409081</v>
+        <v>4.242712935566582</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>5.003609464167625</v>
+        <v>4.297604675716044</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>5.112479795523905</v>
+        <v>4.357554251269803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.085 is the adopted regression against the exchange's published index, and 1.412 is the top of that regression's own 90% confidence interval (its bottom, 0.758, sits just above the composite reading). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.085 row is the published cash-flow value of AED 6.51 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 6.40 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5680,19 @@
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>5.466895404238599</v>
+        <v>5.380506785289913</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>5.986236187980316</v>
+        <v>5.892662340911411</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>6.50557697172203</v>
+        <v>6.404817896532908</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>7.024917755463745</v>
+        <v>6.916973452154407</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>7.544258539205458</v>
+        <v>7.429129007775901</v>
       </c>
     </row>
     <row r="15">
@@ -5636,7 +5709,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>This row and the one below it are re-runs of the whole model at the same 8.49% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 6.51 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
+          <t>This row and the one below it are re-runs of the whole model at the same 8.56% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 6.40 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
         </is>
       </c>
     </row>
@@ -5684,16 +5757,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6.914940440302763</v>
+        <v>6.81087218594573</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6.50557697172203</v>
+        <v>6.404817896532908</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>6.096213503141294</v>
+        <v>5.998763607120084</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>5.686850034560557</v>
+        <v>5.592709317707262</v>
       </c>
     </row>
     <row r="20">
@@ -5746,13 +5819,13 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>6.415224723153202</v>
+        <v>6.315163657148892</v>
       </c>
       <c r="C24" s="21" t="n">
-        <v>5.963130365206823</v>
+        <v>5.868212089093989</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>5.284988828287254</v>
+        <v>5.197784737011633</v>
       </c>
     </row>
     <row r="25">
@@ -7981,11 +8054,11 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>beta 1.412 — the TOP of the regression's own 90% confidence interval, not a round number picked by hand — with the rate anchor at 0.85x and capital expenditure at 1.10x. A whole-model re-run</t>
+          <t>beta 1.621 — the TOP of the regression's own 90% confidence interval, not a round number picked by hand — with the rate anchor at 0.85x and capital expenditure at 1.10x. A whole-model re-run</t>
         </is>
       </c>
       <c r="C6" s="21" t="n">
-        <v>4.025007328525061</v>
+        <v>3.417404968021705</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -7996,11 +8069,11 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>beta 0.758 — the BOTTOM of the same interval — with the rate anchor at 1.15x and capital expenditure at 0.95x. Taking both bounds from the interval means the published range is the range the estimate itself supports. A whole-model re-run</t>
+          <t>beta 0.586 — the BOTTOM of the same interval — with the rate anchor at 1.15x and capital expenditure at 0.95x. Taking both bounds from the interval means the published range is the range the estimate itself supports. A whole-model re-run</t>
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>10.13215941638862</v>
+        <v>12.2389432347382</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -8080,7 +8153,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>161 weekly observations, R-squared 15.8%, standard error 0.199, 90% confidence interval 0.758 to 1.412 — the usability gate is passed, and this is the index the method asks for</t>
+          <t>159 weekly observations, R-squared 18.1%, standard error 0.315, 90% confidence interval 0.586 to 1.621 — the usability gate is passed, and this is the index the method asks for</t>
         </is>
       </c>
       <c r="C15" s="23">
@@ -8342,13 +8415,13 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>6.302103806955713</v>
+        <v>6.226950849542018</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>4.612173662625463</v>
+        <v>4.183627650976118</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>8.85643410508878</v>
+        <v>10.54299487474104</v>
       </c>
     </row>
     <row r="33">
@@ -8363,13 +8436,13 @@
         </is>
       </c>
       <c r="C33" s="21" t="n">
-        <v>4.892938708214075</v>
+        <v>4.798904529252498</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>3.481417824283891</v>
+        <v>3.432639967125382</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>5.996520587194937</v>
+        <v>5.866633504326449</v>
       </c>
     </row>
     <row r="34">
@@ -8536,7 +8609,7 @@
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>1.085</v>
+        <v>1.1032</v>
       </c>
     </row>
     <row r="15">
@@ -8556,7 +8629,7 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.758</v>
+        <v>0.5855</v>
       </c>
     </row>
     <row r="17">
@@ -8566,17 +8639,17 @@
         </is>
       </c>
       <c r="C17" s="29" t="n">
-        <v>1.412</v>
+        <v>1.621</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Beta — lead-lag sum beta from the same series, one lead and two lags</t>
+          <t>Beta — the measured slope shrunk toward the market: two-thirds of it plus one-third of 1.0</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>1.164</v>
+        <v>1.0688</v>
       </c>
     </row>
     <row r="19">
@@ -19449,7 +19522,7 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Beta — lead-lag sum beta, one lead and two lags</t>
+          <t>Beta — the measured slope shrunk toward the market, two-thirds of it plus one-third of 1.0</t>
         </is>
       </c>
       <c r="C125" s="23">
@@ -19460,7 +19533,7 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Cost of equity on the lead-lag sum beta</t>
+          <t>Cost of equity on the slope shrunk toward the market</t>
         </is>
       </c>
       <c r="C126" s="50">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -1581,23 +1581,23 @@
         <v>19434</v>
       </c>
       <c r="E7" s="18">
-        <f>Assumptions!$C$160</f>
+        <f>Assumptions!$C$164</f>
         <v/>
       </c>
       <c r="F7" s="18">
-        <f>Assumptions!$C$160</f>
+        <f>Assumptions!$C$164</f>
         <v/>
       </c>
       <c r="G7" s="18">
-        <f>Assumptions!$C$160</f>
+        <f>Assumptions!$C$164</f>
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>Assumptions!$C$160</f>
+        <f>Assumptions!$C$164</f>
         <v/>
       </c>
       <c r="I7" s="18">
-        <f>Assumptions!$C$160</f>
+        <f>Assumptions!$C$164</f>
         <v/>
       </c>
     </row>
@@ -1617,23 +1617,23 @@
         <v>51368</v>
       </c>
       <c r="E8" s="18">
-        <f>Assumptions!$C$161</f>
+        <f>Assumptions!$C$165</f>
         <v/>
       </c>
       <c r="F8" s="18">
-        <f>Assumptions!$C$161</f>
+        <f>Assumptions!$C$165</f>
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>Assumptions!$C$161</f>
+        <f>Assumptions!$C$165</f>
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>Assumptions!$C$161</f>
+        <f>Assumptions!$C$165</f>
         <v/>
       </c>
       <c r="I8" s="18">
-        <f>Assumptions!$C$161</f>
+        <f>Assumptions!$C$165</f>
         <v/>
       </c>
     </row>
@@ -1694,23 +1694,23 @@
         <v>577769</v>
       </c>
       <c r="E10" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
       <c r="F10" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
       <c r="G10" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
     </row>
@@ -1802,23 +1802,23 @@
         <v>337794</v>
       </c>
       <c r="E13" s="18">
-        <f>Assumptions!$C$159</f>
+        <f>Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>Assumptions!$C$159</f>
+        <f>Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>Assumptions!$C$159</f>
+        <f>Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>Assumptions!$C$159</f>
+        <f>Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>Assumptions!$C$159</f>
+        <f>Assumptions!$C$163</f>
         <v/>
       </c>
     </row>
@@ -2029,23 +2029,23 @@
         <v>1978619</v>
       </c>
       <c r="E19" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="G19" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="I19" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -2065,23 +2065,23 @@
         <v>264512</v>
       </c>
       <c r="E20" s="18">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="F20" s="18">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="G20" s="18">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="I20" s="18">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>'Income Statement'!E28/((Assumptions!$C$158+E21)/2)</f>
+        <f>'Income Statement'!E28/((Assumptions!$C$162+E21)/2)</f>
         <v/>
       </c>
       <c r="F28" s="10">
@@ -2464,23 +2464,23 @@
         </is>
       </c>
       <c r="B32" s="18">
-        <f>Assumptions!$B$120</f>
+        <f>Assumptions!$B$124</f>
         <v/>
       </c>
       <c r="C32" s="18">
-        <f>Assumptions!$C$120</f>
+        <f>Assumptions!$C$124</f>
         <v/>
       </c>
       <c r="D32" s="18">
-        <f>Assumptions!$D$120</f>
+        <f>Assumptions!$D$124</f>
         <v/>
       </c>
       <c r="E32" s="18">
-        <f>Assumptions!$E$120</f>
+        <f>Assumptions!$E$124</f>
         <v/>
       </c>
       <c r="F32" s="18">
-        <f>Assumptions!$F$120</f>
+        <f>Assumptions!$F$124</f>
         <v/>
       </c>
     </row>
@@ -2518,23 +2518,23 @@
         </is>
       </c>
       <c r="B34" s="19">
-        <f>Assumptions!$C$121</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
       <c r="C34" s="19">
-        <f>Assumptions!$C$121</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
       <c r="D34" s="19">
-        <f>Assumptions!$C$121</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
       <c r="E34" s="19">
-        <f>Assumptions!$C$121</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
       <c r="F34" s="19">
-        <f>Assumptions!$C$121</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
     </row>
@@ -2626,23 +2626,23 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>Assumptions!$C$122*(1+Assumptions!$C$92)^1</f>
+        <f>Assumptions!$C$126*(1+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="C38" s="33">
-        <f>Assumptions!$C$122*(1+Assumptions!$C$92)^2</f>
+        <f>Assumptions!$C$126*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="D38" s="33">
-        <f>Assumptions!$C$122*(1+Assumptions!$C$92)^3</f>
+        <f>Assumptions!$C$126*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="E38" s="33">
-        <f>Assumptions!$C$122*(1+Assumptions!$C$92)^4</f>
+        <f>Assumptions!$C$126*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F38" s="33">
-        <f>Assumptions!$C$122*(1+Assumptions!$C$92)^5</f>
+        <f>Assumptions!$C$126*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)*(1+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -2766,23 +2766,23 @@
         </is>
       </c>
       <c r="B43" s="17">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$130</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$130</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$130</f>
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$130</f>
         <v/>
       </c>
       <c r="F43" s="17">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$130</f>
         <v/>
       </c>
     </row>
@@ -2793,23 +2793,23 @@
         </is>
       </c>
       <c r="B44" s="17">
-        <f>Assumptions!$C$127</f>
+        <f>Assumptions!$C$131</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>Assumptions!$C$127</f>
+        <f>Assumptions!$C$131</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>Assumptions!$C$127</f>
+        <f>Assumptions!$C$131</f>
         <v/>
       </c>
       <c r="E44" s="17">
-        <f>Assumptions!$C$127</f>
+        <f>Assumptions!$C$131</f>
         <v/>
       </c>
       <c r="F44" s="17">
-        <f>Assumptions!$C$127</f>
+        <f>Assumptions!$C$131</f>
         <v/>
       </c>
     </row>
@@ -2820,23 +2820,23 @@
         </is>
       </c>
       <c r="B45" s="17">
-        <f>Assumptions!$C$128</f>
+        <f>Assumptions!$C$132</f>
         <v/>
       </c>
       <c r="C45" s="17">
-        <f>Assumptions!$C$128</f>
+        <f>Assumptions!$C$132</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>Assumptions!$C$128</f>
+        <f>Assumptions!$C$132</f>
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>Assumptions!$C$128</f>
+        <f>Assumptions!$C$132</f>
         <v/>
       </c>
       <c r="F45" s="17">
-        <f>Assumptions!$C$128</f>
+        <f>Assumptions!$C$132</f>
         <v/>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B50" s="35">
-        <f>B49-Assumptions!$C$129</f>
+        <f>B49-Assumptions!$C$133</f>
         <v/>
       </c>
       <c r="C50" s="35">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="B53" s="18">
-        <f>Assumptions!$C$150+Assumptions!$C$151+Assumptions!$C$82</f>
+        <f>Assumptions!$C$154+Assumptions!$C$155+Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="C53" s="33">
@@ -3041,23 +3041,23 @@
         </is>
       </c>
       <c r="B54" s="33">
-        <f>B53+Assumptions!$C$159</f>
+        <f>B53+Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="C54" s="33">
-        <f>C53+Assumptions!$C$159</f>
+        <f>C53+Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="D54" s="33">
-        <f>D53+Assumptions!$C$159</f>
+        <f>D53+Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="E54" s="33">
-        <f>E53+Assumptions!$C$159</f>
+        <f>E53+Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="F54" s="33">
-        <f>F53+Assumptions!$C$159</f>
+        <f>F53+Assumptions!$C$163</f>
         <v/>
       </c>
     </row>
@@ -3149,23 +3149,23 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$159*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="C58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$159*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="D58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$159*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="E58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$159*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
       <c r="F58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$159*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163*(1-Assumptions!$C$21)</f>
         <v/>
       </c>
     </row>
@@ -3176,23 +3176,23 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="C59" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="D59" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="E59" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="F59" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
     </row>
@@ -3230,23 +3230,23 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>-Assumptions!$C$162*(1+Assumptions!$C$163)^0</f>
+        <f>-Assumptions!$C$166*(1+Assumptions!$C$167)^0</f>
         <v/>
       </c>
       <c r="C61" s="33">
-        <f>-Assumptions!$C$162*(1+Assumptions!$C$163)^1</f>
+        <f>-Assumptions!$C$166*(1+Assumptions!$C$167)^1</f>
         <v/>
       </c>
       <c r="D61" s="33">
-        <f>-Assumptions!$C$162*(1+Assumptions!$C$163)^2</f>
+        <f>-Assumptions!$C$166*(1+Assumptions!$C$167)^2</f>
         <v/>
       </c>
       <c r="E61" s="33">
-        <f>-Assumptions!$C$162*(1+Assumptions!$C$163)^3</f>
+        <f>-Assumptions!$C$166*(1+Assumptions!$C$167)^3</f>
         <v/>
       </c>
       <c r="F61" s="33">
-        <f>-Assumptions!$C$162*(1+Assumptions!$C$163)^4</f>
+        <f>-Assumptions!$C$166*(1+Assumptions!$C$167)^4</f>
         <v/>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="B65" s="18">
-        <f>Assumptions!$C$158</f>
+        <f>Assumptions!$C$162</f>
         <v/>
       </c>
       <c r="C65" s="33">
@@ -5536,16 +5536,16 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>8.374944338037677</v>
+        <v>7.256472712000055</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>8.822531851772526</v>
+        <v>7.552205629563578</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>9.370468800365373</v>
+        <v>7.903387977796284</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>10.05887125454404</v>
+        <v>8.328651590959588</v>
       </c>
     </row>
     <row r="7">
@@ -5555,16 +5555,16 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>7.070580934793161</v>
+        <v>6.214376836811512</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>7.354128948659886</v>
+        <v>6.404146285774652</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>7.690219368556742</v>
+        <v>6.623608748974647</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>8.096318366520435</v>
+        <v>6.881289793985491</v>
       </c>
     </row>
     <row r="8">
@@ -5574,16 +5574,16 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>6.020153084134909</v>
+        <v>5.351641415753465</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>6.198777837752638</v>
+        <v>5.470831964800543</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>6.404817896532908</v>
+        <v>5.605378969448954</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>6.646025779733348</v>
+        <v>5.759111119380354</v>
       </c>
     </row>
     <row r="9">
@@ -5593,16 +5593,16 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>5.031072269544037</v>
+        <v>4.519378801751275</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>5.132117653317763</v>
+        <v>4.584639620778216</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>5.245334010186813</v>
+        <v>4.656174931977572</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>5.373634668456338</v>
+        <v>4.735333430630773</v>
       </c>
     </row>
     <row r="10">
@@ -5612,22 +5612,22 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>4.192019140583034</v>
+        <v>3.797725353671114</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>4.242712935566582</v>
+        <v>3.827039684051177</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>4.297604675716044</v>
+        <v>3.857735918410984</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>4.357554251269803</v>
+        <v>3.890072041379242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 6.40 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 5.61 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>5.380506785289913</v>
+        <v>4.697022565963811</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>5.892662340911411</v>
+        <v>5.151200767706382</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>6.404817896532908</v>
+        <v>5.605378969448954</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>6.916973452154407</v>
+        <v>6.059557171191526</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>7.429129007775901</v>
+        <v>6.513735372934097</v>
       </c>
     </row>
     <row r="15">
@@ -5709,7 +5709,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>This row and the one below it are re-runs of the whole model at the same 8.56% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 6.40 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
+          <t>This row and the one below it are re-runs of the whole model at the same 8.55% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 5.61 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5757,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>6.81087218594573</v>
+        <v>5.985731492766608</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>6.404817896532908</v>
+        <v>5.605378969448954</v>
       </c>
       <c r="D19" s="21" t="n">
-        <v>5.998763607120084</v>
+        <v>5.225026446131299</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>5.592709317707262</v>
+        <v>4.844673922813643</v>
       </c>
     </row>
     <row r="20">
@@ -5819,13 +5819,13 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>6.315163657148892</v>
+        <v>5.520761762977124</v>
       </c>
       <c r="C24" s="21" t="n">
-        <v>5.868212089093989</v>
+        <v>5.114650357299365</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>5.197784737011633</v>
+        <v>4.505483248782724</v>
       </c>
     </row>
     <row r="25">
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>Assumptions!$C$167</f>
+        <f>Assumptions!$C$171</f>
         <v/>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$170</f>
+        <f>Assumptions!$C$174</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -7557,7 +7557,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$171</f>
+        <f>Assumptions!$C$175</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -7588,7 +7588,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$172</f>
+        <f>Assumptions!$C$176</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -7619,7 +7619,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$173</f>
+        <f>Assumptions!$C$177</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -7909,7 +7909,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt — the three constructions averaged (a simple average, not a weighted figure)</t>
+          <t>Cost of debt ADOPTED — the instruments actually outstanding, weighted by balance</t>
         </is>
       </c>
       <c r="C31" s="19">
@@ -7920,7 +7920,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Cost of debt — the balance-weighted construction alone, published beside the average rather than in place of it</t>
+          <t>Cost of debt — MEMORANDUM, the retired average of three constructions</t>
         </is>
       </c>
       <c r="C32" s="19">
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="C6" s="21" t="n">
-        <v>3.417404968021705</v>
+        <v>3.039484459774819</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="C7" s="21" t="n">
-        <v>12.2389432347382</v>
+        <v>10.17799404357926</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>7.308901618653692</v>
+        <v>7.328560250147793</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>5.481676213990269</v>
+        <v>5.496420187610844</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>9.136127023317115</v>
+        <v>9.160700312684741</v>
       </c>
     </row>
     <row r="32">
@@ -8415,13 +8415,13 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>6.226950849542018</v>
+        <v>6.252678827889344</v>
       </c>
       <c r="D32" s="21" t="n">
-        <v>4.183627650976118</v>
+        <v>4.200913202800493</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>10.54299487474104</v>
+        <v>10.58655551146475</v>
       </c>
     </row>
     <row r="33">
@@ -8436,13 +8436,13 @@
         </is>
       </c>
       <c r="C33" s="21" t="n">
-        <v>4.798904529252498</v>
+        <v>4.584776134196474</v>
       </c>
       <c r="D33" s="21" t="n">
-        <v>3.432639967125382</v>
+        <v>3.324971580016343</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>5.866633504326449</v>
+        <v>5.567457940829041</v>
       </c>
     </row>
     <row r="34">
@@ -8470,7 +8470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8674,7 +8674,7 @@
         </is>
       </c>
       <c r="C20" s="28" t="n">
-        <v>0.0325</v>
+        <v>0.039751</v>
       </c>
     </row>
     <row r="21">
@@ -9700,1031 +9700,1071 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>Running-cost escalation (services and wages)</t>
+          <t>House inflation ladder, FY2026</t>
         </is>
       </c>
       <c r="C92" s="30" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Gross-up from time-charter-equivalent revenue to reported revenue</t>
-        </is>
-      </c>
-      <c r="C93" s="26" t="n">
-        <v>1.6</v>
+          <t>House inflation ladder, FY2027</t>
+        </is>
+      </c>
+      <c r="C93" s="30" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>House inflation ladder, FY2028</t>
+        </is>
+      </c>
+      <c r="C94" s="30" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>Gas carriers</t>
-        </is>
-      </c>
-      <c r="B95" s="14" t="n"/>
-      <c r="C95" s="14" t="n"/>
-      <c r="D95" s="14" t="n"/>
-      <c r="E95" s="14" t="n"/>
-      <c r="F95" s="14" t="n"/>
-      <c r="G95" s="14" t="n"/>
-      <c r="H95" s="14" t="n"/>
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>House inflation ladder, FY2029</t>
+        </is>
+      </c>
+      <c r="C95" s="30" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>Consolidated gas vessels in service through 2025 (vessel-years)</t>
-        </is>
-      </c>
-      <c r="C96" s="24" t="n">
-        <v>8</v>
+          <t>House inflation ladder, FY2030</t>
+        </is>
+      </c>
+      <c r="C96" s="30" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
-        </is>
-      </c>
-      <c r="C97" s="18">
-        <f>Segments!B153</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>Gas carriers — earnings margin</t>
-        </is>
-      </c>
-      <c r="C98" s="30" t="n">
-        <v>0.7</v>
+          <t>Gross-up from time-charter-equivalent revenue to reported revenue</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Share of joint-venture profit carried in the disclosed 2025 Gas Carriers earnings (USD 000)</t>
-        </is>
-      </c>
-      <c r="C99" s="27" t="n">
-        <v>21313</v>
-      </c>
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>Gas carriers</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="n"/>
+      <c r="C99" s="14" t="n"/>
+      <c r="D99" s="14" t="n"/>
+      <c r="E99" s="14" t="n"/>
+      <c r="F99" s="14" t="n"/>
+      <c r="G99" s="14" t="n"/>
+      <c r="H99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>Share of joint-venture profit carried in the disclosed 2025 Services earnings (USD 000)</t>
-        </is>
-      </c>
-      <c r="C100" s="27" t="n">
-        <v>16079</v>
+          <t>Consolidated gas vessels in service through 2025 (vessel-years)</t>
+        </is>
+      </c>
+      <c r="C100" s="24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
+        </is>
+      </c>
+      <c r="C101" s="18">
+        <f>Segments!B153</f>
+        <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>Gas-carrier contract table — the vessel-years the fleet is contracted for, before and after the August 2026 purchase</t>
-        </is>
-      </c>
-      <c r="B102" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C102" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E102" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F102" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G102" s="14" t="n"/>
-      <c r="H102" s="14" t="n"/>
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Gas carriers — earnings margin</t>
+        </is>
+      </c>
+      <c r="C102" s="30" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>Contracted vessel-years before that purchase — the disclosed contract table</t>
-        </is>
-      </c>
-      <c r="B103" s="24" t="n">
-        <v>10.73972602739726</v>
-      </c>
-      <c r="C103" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="D103" s="24" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="E103" s="24" t="n">
-        <v>25</v>
-      </c>
-      <c r="F103" s="24" t="n">
-        <v>25</v>
+          <t>Share of joint-venture profit carried in the disclosed 2025 Gas Carriers earnings (USD 000)</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="n">
+        <v>21313</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>Vessel-years the gas carriers bought in August 2026 add — each tranche from its own delivery date</t>
-        </is>
-      </c>
-      <c r="B104" s="36">
-        <f>(Assumptions!$B$85*MAX(Assumptions!$B$79-MAX(Assumptions!$B$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$B$79-MAX(Assumptions!$B$78,Assumptions!$C$86),0))/(Assumptions!$B$79-Assumptions!$B$78)</f>
-        <v/>
-      </c>
-      <c r="C104" s="36">
-        <f>(Assumptions!$B$85*MAX(Assumptions!$C$79-MAX(Assumptions!$C$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$C$79-MAX(Assumptions!$C$78,Assumptions!$C$86),0))/(Assumptions!$C$79-Assumptions!$C$78)</f>
-        <v/>
-      </c>
-      <c r="D104" s="36">
-        <f>(Assumptions!$B$85*MAX(Assumptions!$D$79-MAX(Assumptions!$D$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$D$79-MAX(Assumptions!$D$78,Assumptions!$C$86),0))/(Assumptions!$D$79-Assumptions!$D$78)</f>
-        <v/>
-      </c>
-      <c r="E104" s="36">
-        <f>(Assumptions!$B$85*MAX(Assumptions!$E$79-MAX(Assumptions!$E$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$E$79-MAX(Assumptions!$E$78,Assumptions!$C$86),0))/(Assumptions!$E$79-Assumptions!$E$78)</f>
-        <v/>
-      </c>
-      <c r="F104" s="36">
-        <f>(Assumptions!$B$85*MAX(Assumptions!$F$79-MAX(Assumptions!$F$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$F$79-MAX(Assumptions!$F$78,Assumptions!$C$86),0))/(Assumptions!$F$79-Assumptions!$F$78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>Gas carriers — contracted vessel-years</t>
-        </is>
-      </c>
-      <c r="B105" s="37">
-        <f>B103+B104</f>
-        <v/>
-      </c>
-      <c r="C105" s="37">
-        <f>C103+C104</f>
-        <v/>
-      </c>
-      <c r="D105" s="37">
-        <f>D103+D104</f>
-        <v/>
-      </c>
-      <c r="E105" s="37">
-        <f>E103+E104</f>
-        <v/>
-      </c>
-      <c r="F105" s="37">
-        <f>F103+F104</f>
-        <v/>
-      </c>
+          <t>Share of joint-venture profit carried in the disclosed 2025 Services earnings (USD 000)</t>
+        </is>
+      </c>
+      <c r="C104" s="27" t="n">
+        <v>16079</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Gas-carrier contract table — the vessel-years the fleet is contracted for, before and after the August 2026 purchase</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="n"/>
+      <c r="H106" s="14" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>The remaining five units — revenue and margin drivers</t>
-        </is>
-      </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D107" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E107" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F107" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G107" s="14" t="n"/>
-      <c r="H107" s="14" t="n"/>
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Contracted vessel-years before that purchase — the disclosed contract table</t>
+        </is>
+      </c>
+      <c r="B107" s="24" t="n">
+        <v>10.73972602739726</v>
+      </c>
+      <c r="C107" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="D107" s="24" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="E107" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="F107" s="24" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B108" s="27" t="n">
-        <v>1248192</v>
-      </c>
-      <c r="C108" s="27" t="n">
-        <v>1298120</v>
-      </c>
-      <c r="D108" s="27" t="n">
-        <v>1350044</v>
-      </c>
-      <c r="E108" s="27" t="n">
-        <v>1404046</v>
-      </c>
-      <c r="F108" s="27" t="n">
-        <v>1460208</v>
+          <t>Vessel-years the gas carriers bought in August 2026 add — each tranche from its own delivery date</t>
+        </is>
+      </c>
+      <c r="B108" s="36">
+        <f>(Assumptions!$B$85*MAX(Assumptions!$B$79-MAX(Assumptions!$B$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$B$79-MAX(Assumptions!$B$78,Assumptions!$C$86),0))/(Assumptions!$B$79-Assumptions!$B$78)</f>
+        <v/>
+      </c>
+      <c r="C108" s="36">
+        <f>(Assumptions!$B$85*MAX(Assumptions!$C$79-MAX(Assumptions!$C$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$C$79-MAX(Assumptions!$C$78,Assumptions!$C$86),0))/(Assumptions!$C$79-Assumptions!$C$78)</f>
+        <v/>
+      </c>
+      <c r="D108" s="36">
+        <f>(Assumptions!$B$85*MAX(Assumptions!$D$79-MAX(Assumptions!$D$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$D$79-MAX(Assumptions!$D$78,Assumptions!$C$86),0))/(Assumptions!$D$79-Assumptions!$D$78)</f>
+        <v/>
+      </c>
+      <c r="E108" s="36">
+        <f>(Assumptions!$B$85*MAX(Assumptions!$E$79-MAX(Assumptions!$E$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$E$79-MAX(Assumptions!$E$78,Assumptions!$C$86),0))/(Assumptions!$E$79-Assumptions!$E$78)</f>
+        <v/>
+      </c>
+      <c r="F108" s="36">
+        <f>(Assumptions!$B$85*MAX(Assumptions!$F$79-MAX(Assumptions!$F$78,Assumptions!$C$85),0)+Assumptions!$B$86*MAX(Assumptions!$F$79-MAX(Assumptions!$F$78,Assumptions!$C$86),0))/(Assumptions!$F$79-Assumptions!$F$78)</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — earnings margin</t>
-        </is>
-      </c>
-      <c r="B109" s="30" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="C109" s="30" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="D109" s="30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E109" s="30" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="F109" s="30" t="n">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Services — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B110" s="27" t="n">
-        <v>662856</v>
-      </c>
-      <c r="C110" s="27" t="n">
-        <v>696000</v>
-      </c>
-      <c r="D110" s="27" t="n">
-        <v>730800</v>
-      </c>
-      <c r="E110" s="27" t="n">
-        <v>767340</v>
-      </c>
-      <c r="F110" s="27" t="n">
-        <v>805707</v>
+          <t>Gas carriers — contracted vessel-years</t>
+        </is>
+      </c>
+      <c r="B109" s="37">
+        <f>B107+B108</f>
+        <v/>
+      </c>
+      <c r="C109" s="37">
+        <f>C107+C108</f>
+        <v/>
+      </c>
+      <c r="D109" s="37">
+        <f>D107+D108</f>
+        <v/>
+      </c>
+      <c r="E109" s="37">
+        <f>E107+E108</f>
+        <v/>
+      </c>
+      <c r="F109" s="37">
+        <f>F107+F108</f>
+        <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Services — earnings margin</t>
-        </is>
-      </c>
-      <c r="B111" s="30" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="C111" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="D111" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E111" s="30" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F111" s="30" t="n">
-        <v>0.29</v>
-      </c>
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>The remaining five units — revenue and margin drivers</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E111" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F111" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G111" s="14" t="n"/>
+      <c r="H111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — revenue (USD 000)</t>
+          <t>Offshore Contracting — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B112" s="27" t="n">
-        <v>125000</v>
+        <v>1248192</v>
       </c>
       <c r="C112" s="27" t="n">
-        <v>200000</v>
+        <v>1298120</v>
       </c>
       <c r="D112" s="27" t="n">
-        <v>250000</v>
+        <v>1350044</v>
       </c>
       <c r="E112" s="27" t="n">
-        <v>275000</v>
+        <v>1404046</v>
       </c>
       <c r="F112" s="27" t="n">
-        <v>300000</v>
+        <v>1460208</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — earnings margin</t>
+          <t>Offshore Contracting — earnings margin</t>
         </is>
       </c>
       <c r="B113" s="30" t="n">
-        <v>-0.02</v>
+        <v>0.385</v>
       </c>
       <c r="C113" s="30" t="n">
-        <v>0.06</v>
+        <v>0.415</v>
       </c>
       <c r="D113" s="30" t="n">
-        <v>0.065</v>
+        <v>0.43</v>
       </c>
       <c r="E113" s="30" t="n">
-        <v>0.065</v>
+        <v>0.43</v>
       </c>
       <c r="F113" s="30" t="n">
-        <v>0.065</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
+          <t>Offshore Services — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B114" s="27" t="n">
-        <v>197164</v>
+        <v>662856</v>
       </c>
       <c r="C114" s="27" t="n">
-        <v>201107</v>
+        <v>696000</v>
       </c>
       <c r="D114" s="27" t="n">
-        <v>205129</v>
+        <v>730800</v>
       </c>
       <c r="E114" s="27" t="n">
-        <v>209232</v>
+        <v>767340</v>
       </c>
       <c r="F114" s="27" t="n">
-        <v>213417</v>
+        <v>805707</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — earnings margin</t>
+          <t>Offshore Services — earnings margin</t>
         </is>
       </c>
       <c r="B115" s="30" t="n">
-        <v>0.184</v>
+        <v>0.287</v>
       </c>
       <c r="C115" s="30" t="n">
-        <v>0.184</v>
+        <v>0.29</v>
       </c>
       <c r="D115" s="30" t="n">
-        <v>0.184</v>
+        <v>0.29</v>
       </c>
       <c r="E115" s="30" t="n">
-        <v>0.184</v>
+        <v>0.29</v>
       </c>
       <c r="F115" s="30" t="n">
-        <v>0.184</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Services — revenue (USD 000)</t>
+          <t>Offshore Projects — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B116" s="27" t="n">
-        <v>355372</v>
+        <v>125000</v>
       </c>
       <c r="C116" s="27" t="n">
-        <v>369587</v>
+        <v>200000</v>
       </c>
       <c r="D116" s="27" t="n">
-        <v>384370</v>
+        <v>250000</v>
       </c>
       <c r="E116" s="27" t="n">
-        <v>399745</v>
+        <v>275000</v>
       </c>
       <c r="F116" s="27" t="n">
-        <v>415735</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Services — earnings margin</t>
+          <t>Offshore Projects — earnings margin</t>
         </is>
       </c>
       <c r="B117" s="30" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="C117" s="30" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="D117" s="30" t="n">
-        <v>0.2</v>
+        <v>0.065</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>0.2</v>
+        <v>0.065</v>
       </c>
       <c r="F117" s="30" t="n">
-        <v>0.2</v>
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="n">
+        <v>197164</v>
+      </c>
+      <c r="C118" s="27" t="n">
+        <v>201107</v>
+      </c>
+      <c r="D118" s="27" t="n">
+        <v>205129</v>
+      </c>
+      <c r="E118" s="27" t="n">
+        <v>209232</v>
+      </c>
+      <c r="F118" s="27" t="n">
+        <v>213417</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>Capital expenditure, depreciation and working capital</t>
-        </is>
-      </c>
-      <c r="B119" s="14" t="inlineStr">
-        <is>
-          <t>FY2026</t>
-        </is>
-      </c>
-      <c r="C119" s="14" t="inlineStr">
-        <is>
-          <t>FY2027</t>
-        </is>
-      </c>
-      <c r="D119" s="14" t="inlineStr">
-        <is>
-          <t>FY2028</t>
-        </is>
-      </c>
-      <c r="E119" s="14" t="inlineStr">
-        <is>
-          <t>FY2029</t>
-        </is>
-      </c>
-      <c r="F119" s="14" t="inlineStr">
-        <is>
-          <t>FY2030</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="n"/>
-      <c r="H119" s="14" t="n"/>
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — earnings margin</t>
+        </is>
+      </c>
+      <c r="B119" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="C119" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="D119" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="E119" s="30" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="F119" s="30" t="n">
+        <v>0.184</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure (USD 000)</t>
+          <t>Services — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B120" s="27" t="n">
-        <v>1375000</v>
+        <v>355372</v>
       </c>
       <c r="C120" s="27" t="n">
-        <v>1245000</v>
+        <v>369587</v>
       </c>
       <c r="D120" s="27" t="n">
-        <v>1245000</v>
+        <v>384370</v>
       </c>
       <c r="E120" s="27" t="n">
-        <v>700000</v>
+        <v>399745</v>
       </c>
       <c r="F120" s="27" t="n">
-        <v>650000</v>
+        <v>415735</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>Depreciation rate on property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="C121" s="28" t="n">
-        <v>0.058</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
-        </is>
-      </c>
-      <c r="C122" s="27" t="n">
-        <v>109836</v>
+          <t>Services — earnings margin</t>
+        </is>
+      </c>
+      <c r="B121" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C121" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D121" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E121" s="30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F121" s="30" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Days sales outstanding measured on REPORTED 2025 revenue</t>
-        </is>
-      </c>
-      <c r="C123" s="17">
-        <f>'Balance Sheet'!D12/'Income Statement'!D5*365</f>
-        <v/>
-      </c>
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Capital expenditure, depreciation and working capital</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="E123" s="14" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="n"/>
+      <c r="H123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>Gross-up inside 2025 reported revenue — reported tanker revenue over the same fleet's charter-equivalent revenue</t>
-        </is>
-      </c>
-      <c r="C124" s="38">
-        <f>Segments!D8/Segments!B140</f>
-        <v/>
+          <t>Capital expenditure (USD 000)</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="C124" s="27" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="D124" s="27" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="E124" s="27" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F124" s="27" t="n">
+        <v>650000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Gross-up the forecast is built at, from 2026 onward</t>
-        </is>
-      </c>
-      <c r="C125" s="38">
-        <f>Assumptions!$C$93</f>
-        <v/>
+          <t>Depreciation rate on property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="n">
+        <v>0.058</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Days sales outstanding — the reported ratio RE-BASED onto the revenue basis the forecast actually uses</t>
-        </is>
-      </c>
-      <c r="C126" s="17">
-        <f>C123*'Income Statement'!D5/('Income Statement'!D5-Segments!D8+Segments!D8/C124*C125)</f>
-        <v/>
+          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
+        </is>
+      </c>
+      <c r="C126" s="27" t="n">
+        <v>109836</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>Days inventory outstanding</t>
+          <t>Days sales outstanding measured on REPORTED 2025 revenue</t>
         </is>
       </c>
       <c r="C127" s="17">
-        <f>'Balance Sheet'!D11/'Income Statement'!D17*365</f>
+        <f>'Balance Sheet'!D12/'Income Statement'!D5*365</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>Days payable outstanding</t>
-        </is>
-      </c>
-      <c r="C128" s="17">
-        <f>'Balance Sheet'!D15/'Income Statement'!D17*365</f>
+          <t>Gross-up inside 2025 reported revenue — reported tanker revenue over the same fleet's charter-equivalent revenue</t>
+        </is>
+      </c>
+      <c r="C128" s="38">
+        <f>Segments!D8/Segments!B140</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>Net working capital at 31 December 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C129" s="18">
-        <f>'Balance Sheet'!D16</f>
+          <t>Gross-up the forecast is built at, from 2026 onward</t>
+        </is>
+      </c>
+      <c r="C129" s="38">
+        <f>Assumptions!$C$97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Days sales outstanding — the reported ratio RE-BASED onto the revenue basis the forecast actually uses</t>
+        </is>
+      </c>
+      <c r="C130" s="17">
+        <f>C127*'Income Statement'!D5/('Income Statement'!D5-Segments!D8+Segments!D8/C128*C129)</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>DEPRECIATION — THE RATE USED, THE RATE REALISED IN 2025 AND THE DISCLOSED USEFUL LIVES, SO THE CHOICE CAN BE JUDGED. These three are memoranda: the rate the model runs on is the blue driver above, and it is sensitised</t>
-        </is>
-      </c>
-      <c r="B131" s="14" t="inlineStr">
-        <is>
-          <t>Memorandum</t>
-        </is>
-      </c>
-      <c r="C131" s="14" t="n"/>
-      <c r="D131" s="14" t="n"/>
-      <c r="E131" s="14" t="n"/>
-      <c r="F131" s="14" t="n"/>
-      <c r="G131" s="14" t="n"/>
-      <c r="H131" s="14" t="n"/>
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Days inventory outstanding</t>
+        </is>
+      </c>
+      <c r="C131" s="17">
+        <f>'Balance Sheet'!D11/'Income Statement'!D17*365</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>The rate used — first-quarter 2026 depreciation annualised over that quarter's average balance (the driver above)</t>
-        </is>
-      </c>
-      <c r="B132" s="19">
-        <f>C121</f>
+          <t>Days payable outstanding</t>
+        </is>
+      </c>
+      <c r="C132" s="17">
+        <f>'Balance Sheet'!D15/'Income Statement'!D17*365</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
+          <t>Net working capital at 31 December 2025 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C133" s="18">
+        <f>'Balance Sheet'!D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>DEPRECIATION — THE RATE USED, THE RATE REALISED IN 2025 AND THE DISCLOSED USEFUL LIVES, SO THE CHOICE CAN BE JUDGED. These three are memoranda: the rate the model runs on is the blue driver above, and it is sensitised</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>Memorandum</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="n"/>
+      <c r="D135" s="14" t="n"/>
+      <c r="E135" s="14" t="n"/>
+      <c r="F135" s="14" t="n"/>
+      <c r="G135" s="14" t="n"/>
+      <c r="H135" s="14" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>The rate used — first-quarter 2026 depreciation annualised over that quarter's average balance (the driver above)</t>
+        </is>
+      </c>
+      <c r="B136" s="19">
+        <f>C125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
           <t>The rate realised in 2025 — depreciation charged on property, plant and equipment over the average balance for that year</t>
         </is>
       </c>
-      <c r="B133" s="28" t="n">
+      <c r="B137" s="28" t="n">
         <v>0.0675</v>
       </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>Disclosed useful life of tankers (years, straight line) — dry-bulk and containers 25, gas carriers 25 to 40, offshore vessels 20 to 25, jack-up barges 40, and dry-docking components 2 to 5, which is why both rates above are heavier than a hull life alone implies</t>
-        </is>
-      </c>
-      <c r="B134" s="27" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>Average life implied by the rate used (years)</t>
-        </is>
-      </c>
-      <c r="B135" s="36">
-        <f>1/C121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>Tax by business unit and the 2025 depreciation allocation basis</t>
-        </is>
-      </c>
-      <c r="B137" s="14" t="n"/>
-      <c r="C137" s="14" t="n"/>
-      <c r="D137" s="14" t="n"/>
-      <c r="E137" s="14" t="n"/>
-      <c r="F137" s="14" t="n"/>
-      <c r="G137" s="14" t="n"/>
-      <c r="H137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Integrated Logistics — income tax rate</t>
-        </is>
-      </c>
-      <c r="C138" s="30" t="n">
-        <v>0.09</v>
+          <t>Disclosed useful life of tankers (years, straight line) — dry-bulk and containers 25, gas carriers 25 to 40, offshore vessels 20 to 25, jack-up barges 40, and dry-docking components 2 to 5, which is why both rates above are heavier than a hull life alone implies</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Shipping — income tax rate</t>
-        </is>
-      </c>
-      <c r="C139" s="30" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>Services — income tax rate</t>
-        </is>
-      </c>
-      <c r="C140" s="30" t="n">
-        <v>0.04</v>
+          <t>Average life implied by the rate used (years)</t>
+        </is>
+      </c>
+      <c r="B139" s="36">
+        <f>1/C125</f>
+        <v/>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C141" s="27" t="n">
-        <v>151367</v>
-      </c>
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>Tax by business unit and the 2025 depreciation allocation basis</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="n"/>
+      <c r="C141" s="14" t="n"/>
+      <c r="D141" s="14" t="n"/>
+      <c r="E141" s="14" t="n"/>
+      <c r="F141" s="14" t="n"/>
+      <c r="G141" s="14" t="n"/>
+      <c r="H141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C142" s="27" t="n">
-        <v>62963</v>
+          <t>Integrated Logistics — income tax rate</t>
+        </is>
+      </c>
+      <c r="C142" s="30" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C143" s="27" t="n">
-        <v>8860</v>
+          <t>Shipping — income tax rate</t>
+        </is>
+      </c>
+      <c r="C143" s="30" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C144" s="27" t="n">
-        <v>195374</v>
+          <t>Services — income tax rate</t>
+        </is>
+      </c>
+      <c r="C144" s="30" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C145" s="27" t="n">
-        <v>50526</v>
+        <v>151367</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C146" s="27" t="n">
-        <v>25225</v>
+        <v>62963</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>Services — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C147" s="27" t="n">
-        <v>30297</v>
+        <v>8860</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C148" s="27" t="n">
+        <v>195374</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>Funding, distributions and the bridge</t>
-        </is>
-      </c>
-      <c r="B149" s="14" t="n"/>
-      <c r="C149" s="14" t="n"/>
-      <c r="D149" s="14" t="n"/>
-      <c r="E149" s="14" t="n"/>
-      <c r="F149" s="14" t="n"/>
-      <c r="G149" s="14" t="n"/>
-      <c r="H149" s="14" t="n"/>
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="n">
+        <v>50526</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Net debt at 31 March 2026, company basis (USD 000)</t>
+          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C150" s="27" t="n">
-        <v>419867</v>
+        <v>25225</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Deferred consideration on acquisitions (USD 000)</t>
+          <t>Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C151" s="27" t="n">
-        <v>301462</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>Perpetual capital securities at carrying value (USD 000)</t>
-        </is>
-      </c>
-      <c r="C152" s="27" t="n">
-        <v>1978619</v>
+        <v>30297</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>Perpetual capital securities margin over the overnight rate</t>
-        </is>
-      </c>
-      <c r="C153" s="28" t="n">
-        <v>0.0125</v>
-      </c>
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>Funding, distributions and the bridge</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="n"/>
+      <c r="C153" s="14" t="n"/>
+      <c r="D153" s="14" t="n"/>
+      <c r="E153" s="14" t="n"/>
+      <c r="F153" s="14" t="n"/>
+      <c r="G153" s="14" t="n"/>
+      <c r="H153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests at carrying value (USD 000)</t>
+          <t>Net debt at 31 March 2026, company basis (USD 000)</t>
         </is>
       </c>
       <c r="C154" s="27" t="n">
-        <v>272134</v>
+        <v>419867</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Of which arose on the tanker combination — the 20% contracted for purchase in mid-2027 (USD 000)</t>
+          <t>Deferred consideration on acquisitions (USD 000)</t>
         </is>
       </c>
       <c r="C155" s="27" t="n">
-        <v>251985</v>
+        <v>301462</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests' share of profit</t>
-        </is>
-      </c>
-      <c r="C156" s="30" t="n">
-        <v>0.08799999999999999</v>
+          <t>Perpetual capital securities at carrying value (USD 000)</t>
+        </is>
+      </c>
+      <c r="C156" s="27" t="n">
+        <v>1978619</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Joint ventures and associates at carrying value (USD 000)</t>
-        </is>
-      </c>
-      <c r="C157" s="27" t="n">
-        <v>493120</v>
+          <t>Perpetual capital securities margin over the overnight rate</t>
+        </is>
+      </c>
+      <c r="C157" s="28" t="n">
+        <v>0.0125</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
+          <t>Non-controlling interests at carrying value (USD 000)</t>
         </is>
       </c>
       <c r="C158" s="27" t="n">
-        <v>5073902</v>
+        <v>272134</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents held (USD 000)</t>
+          <t>Of which arose on the tanker combination — the 20% contracted for purchase in mid-2027 (USD 000)</t>
         </is>
       </c>
       <c r="C159" s="27" t="n">
-        <v>695345</v>
+        <v>251985</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (USD 000)</t>
-        </is>
-      </c>
-      <c r="C160" s="18">
-        <f>'Balance Sheet'!D7</f>
-        <v/>
+          <t>Non-controlling interests' share of profit</t>
+        </is>
+      </c>
+      <c r="C160" s="30" t="n">
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>Goodwill (USD 000)</t>
-        </is>
-      </c>
-      <c r="C161" s="18">
-        <f>'Balance Sheet'!D8</f>
-        <v/>
+          <t>Joint ventures and associates at carrying value (USD 000)</t>
+        </is>
+      </c>
+      <c r="C161" s="27" t="n">
+        <v>493120</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C162" s="27" t="n">
-        <v>341000</v>
+        <v>5073902</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend growth</t>
-        </is>
-      </c>
-      <c r="C163" s="30" t="n">
-        <v>0.05</v>
+          <t>Cash and cash equivalents held (USD 000)</t>
+        </is>
+      </c>
+      <c r="C163" s="27" t="n">
+        <v>695345</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C164" s="30" t="n">
-        <v>0.02</v>
+          <t>Intangible assets (USD 000)</t>
+        </is>
+      </c>
+      <c r="C164" s="18">
+        <f>'Balance Sheet'!D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>Goodwill (USD 000)</t>
+        </is>
+      </c>
+      <c r="C165" s="18">
+        <f>'Balance Sheet'!D8</f>
+        <v/>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t>Lens weights and the multiple blend</t>
-        </is>
-      </c>
-      <c r="B166" s="14" t="n"/>
-      <c r="C166" s="14" t="n"/>
-      <c r="D166" s="14" t="n"/>
-      <c r="E166" s="14" t="n"/>
-      <c r="F166" s="14" t="n"/>
-      <c r="G166" s="14" t="n"/>
-      <c r="H166" s="14" t="n"/>
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C166" s="27" t="n">
+        <v>341000</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>Share of 2026 earnings exposed to spot rates</t>
+          <t>Ordinary dividend growth</t>
         </is>
       </c>
       <c r="C167" s="30" t="n">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>Rate at which the return above the cost of equity fades beyond the forecast (the book lens)</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="C168" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>Weight on the enterprise multiple within the relative lens</t>
-        </is>
-      </c>
-      <c r="C169" s="30" t="n">
-        <v>0.7</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C170" s="30" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>Lens weights and the multiple blend</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="n"/>
+      <c r="C170" s="14" t="n"/>
+      <c r="D170" s="14" t="n"/>
+      <c r="E170" s="14" t="n"/>
+      <c r="F170" s="14" t="n"/>
+      <c r="G170" s="14" t="n"/>
+      <c r="H170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative multiples</t>
+          <t>Share of 2026 earnings exposed to spot rates</t>
         </is>
       </c>
       <c r="C171" s="30" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings power</t>
+          <t>Rate at which the return above the cost of equity fades beyond the forecast (the book lens)</t>
         </is>
       </c>
       <c r="C172" s="30" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
+          <t>Weight on the enterprise multiple within the relative lens</t>
+        </is>
+      </c>
+      <c r="C173" s="30" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>Weight — discounted cash flow</t>
+        </is>
+      </c>
+      <c r="C174" s="30" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>Weight — relative multiples</t>
+        </is>
+      </c>
+      <c r="C175" s="30" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised earnings power</t>
+        </is>
+      </c>
+      <c r="C176" s="30" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
           <t>Weight — book value and sustainable return</t>
         </is>
       </c>
-      <c r="C173" s="30" t="n">
+      <c r="C177" s="30" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>Blue cells on this sheet are independent inputs. Green cells are DERIVED — they are live formulas pointing at the build that produces them, and they are on this sheet only so that every driver the model reads can be found in one place. Nothing here is a pasted result.</t>
         </is>
@@ -10853,7 +10893,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
       <c r="D9" s="9">
@@ -10884,7 +10924,7 @@
         </is>
       </c>
       <c r="C11" s="18">
-        <f>-Assumptions!$C$150</f>
+        <f>-Assumptions!$C$154</f>
         <v/>
       </c>
       <c r="D11" s="9">
@@ -10899,7 +10939,7 @@
         </is>
       </c>
       <c r="C12" s="18">
-        <f>-Assumptions!$C$151</f>
+        <f>-Assumptions!$C$155</f>
         <v/>
       </c>
       <c r="D12" s="9">
@@ -10929,7 +10969,7 @@
         </is>
       </c>
       <c r="C14" s="18">
-        <f>-Assumptions!$C$152</f>
+        <f>-Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="D14" s="9">
@@ -11163,7 +11203,7 @@
         </is>
       </c>
       <c r="C30" s="8">
-        <f>Assumptions!$C$167</f>
+        <f>Assumptions!$C$171</f>
         <v/>
       </c>
     </row>
@@ -11208,7 +11248,7 @@
         </is>
       </c>
       <c r="C35" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
     </row>
@@ -11230,7 +11270,7 @@
         </is>
       </c>
       <c r="C37" s="18">
-        <f>-Assumptions!$C$150</f>
+        <f>-Assumptions!$C$154</f>
         <v/>
       </c>
     </row>
@@ -11241,7 +11281,7 @@
         </is>
       </c>
       <c r="C38" s="18">
-        <f>-Assumptions!$C$151</f>
+        <f>-Assumptions!$C$155</f>
         <v/>
       </c>
     </row>
@@ -11263,7 +11303,7 @@
         </is>
       </c>
       <c r="C40" s="18">
-        <f>-Assumptions!$C$152</f>
+        <f>-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -11274,7 +11314,7 @@
         </is>
       </c>
       <c r="C41" s="18">
-        <f>-Assumptions!$C$154</f>
+        <f>-Assumptions!$C$158</f>
         <v/>
       </c>
     </row>
@@ -14598,23 +14638,23 @@
         </is>
       </c>
       <c r="B144" s="44">
-        <f>Assumptions!$C$91*(1+Assumptions!$C$92)^1</f>
+        <f>Assumptions!$C$91*(1+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="C144" s="44">
-        <f>Assumptions!$C$91*(1+Assumptions!$C$92)^2</f>
+        <f>Assumptions!$C$91*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="D144" s="44">
-        <f>Assumptions!$C$91*(1+Assumptions!$C$92)^3</f>
+        <f>Assumptions!$C$91*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="E144" s="44">
-        <f>Assumptions!$C$91*(1+Assumptions!$C$92)^4</f>
+        <f>Assumptions!$C$91*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F144" s="44">
-        <f>Assumptions!$C$91*(1+Assumptions!$C$92)^5</f>
+        <f>Assumptions!$C$91*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)*(1+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -14679,23 +14719,23 @@
         </is>
       </c>
       <c r="B147" s="38">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="C147" s="38">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="D147" s="38">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="E147" s="38">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
       <c r="F147" s="38">
-        <f>Assumptions!$C$93</f>
+        <f>Assumptions!$C$97</f>
         <v/>
       </c>
     </row>
@@ -14745,7 +14785,7 @@
         </is>
       </c>
       <c r="B151" s="17">
-        <f>Assumptions!$C$96</f>
+        <f>Assumptions!$C$100</f>
         <v/>
       </c>
     </row>
@@ -14778,23 +14818,23 @@
         </is>
       </c>
       <c r="B155" s="45">
-        <f>Assumptions!$B$103</f>
+        <f>Assumptions!$B$107</f>
         <v/>
       </c>
       <c r="C155" s="45">
-        <f>Assumptions!$C$103</f>
+        <f>Assumptions!$C$107</f>
         <v/>
       </c>
       <c r="D155" s="45">
-        <f>Assumptions!$D$103</f>
+        <f>Assumptions!$D$107</f>
         <v/>
       </c>
       <c r="E155" s="45">
-        <f>Assumptions!$E$103</f>
+        <f>Assumptions!$E$107</f>
         <v/>
       </c>
       <c r="F155" s="45">
-        <f>Assumptions!$F$103</f>
+        <f>Assumptions!$F$107</f>
         <v/>
       </c>
     </row>
@@ -14805,23 +14845,23 @@
         </is>
       </c>
       <c r="B156" s="17">
-        <f>Assumptions!$B$104</f>
+        <f>Assumptions!$B$108</f>
         <v/>
       </c>
       <c r="C156" s="17">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$108</f>
         <v/>
       </c>
       <c r="D156" s="17">
-        <f>Assumptions!$D$104</f>
+        <f>Assumptions!$D$108</f>
         <v/>
       </c>
       <c r="E156" s="17">
-        <f>Assumptions!$E$104</f>
+        <f>Assumptions!$E$108</f>
         <v/>
       </c>
       <c r="F156" s="17">
-        <f>Assumptions!$F$104</f>
+        <f>Assumptions!$F$108</f>
         <v/>
       </c>
     </row>
@@ -14832,23 +14872,23 @@
         </is>
       </c>
       <c r="B157" s="46">
-        <f>Assumptions!$B$105</f>
+        <f>Assumptions!$B$109</f>
         <v/>
       </c>
       <c r="C157" s="46">
-        <f>Assumptions!$C$105</f>
+        <f>Assumptions!$C$109</f>
         <v/>
       </c>
       <c r="D157" s="46">
-        <f>Assumptions!$D$105</f>
+        <f>Assumptions!$D$109</f>
         <v/>
       </c>
       <c r="E157" s="46">
-        <f>Assumptions!$E$105</f>
+        <f>Assumptions!$E$109</f>
         <v/>
       </c>
       <c r="F157" s="46">
-        <f>Assumptions!$F$105</f>
+        <f>Assumptions!$F$109</f>
         <v/>
       </c>
     </row>
@@ -14859,23 +14899,23 @@
         </is>
       </c>
       <c r="B158" s="33">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$92)^1</f>
+        <f>Assumptions!$C$101*(1+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="C158" s="33">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$92)^2</f>
+        <f>Assumptions!$C$101*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="D158" s="33">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$92)^3</f>
+        <f>Assumptions!$C$101*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="E158" s="33">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$92)^4</f>
+        <f>Assumptions!$C$101*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F158" s="33">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$92)^5</f>
+        <f>Assumptions!$C$101*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)*(1+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -14913,23 +14953,23 @@
         </is>
       </c>
       <c r="B160" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="C160" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="D160" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="E160" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
       <c r="F160" s="8">
-        <f>Assumptions!$C$98</f>
+        <f>Assumptions!$C$102</f>
         <v/>
       </c>
     </row>
@@ -14967,23 +15007,23 @@
         </is>
       </c>
       <c r="B162" s="33">
-        <f>-Assumptions!$C$99*(1+Assumptions!$C$92)^1</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="C162" s="33">
-        <f>-Assumptions!$C$99*(1+Assumptions!$C$92)^2</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="D162" s="33">
-        <f>-Assumptions!$C$99*(1+Assumptions!$C$92)^3</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="E162" s="33">
-        <f>-Assumptions!$C$99*(1+Assumptions!$C$92)^4</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F162" s="33">
-        <f>-Assumptions!$C$99*(1+Assumptions!$C$92)^5</f>
+        <f>-Assumptions!$C$103*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)*(1+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -15053,23 +15093,23 @@
         </is>
       </c>
       <c r="B166" s="18">
-        <f>Assumptions!$B$108</f>
+        <f>Assumptions!$B$112</f>
         <v/>
       </c>
       <c r="C166" s="18">
-        <f>Assumptions!$C$108</f>
+        <f>Assumptions!$C$112</f>
         <v/>
       </c>
       <c r="D166" s="18">
-        <f>Assumptions!$D$108</f>
+        <f>Assumptions!$D$112</f>
         <v/>
       </c>
       <c r="E166" s="18">
-        <f>Assumptions!$E$108</f>
+        <f>Assumptions!$E$112</f>
         <v/>
       </c>
       <c r="F166" s="18">
-        <f>Assumptions!$F$108</f>
+        <f>Assumptions!$F$112</f>
         <v/>
       </c>
     </row>
@@ -15080,23 +15120,23 @@
         </is>
       </c>
       <c r="B167" s="33">
-        <f>B166*Assumptions!$B$109</f>
+        <f>B166*Assumptions!$B$113</f>
         <v/>
       </c>
       <c r="C167" s="33">
-        <f>C166*Assumptions!$C$109</f>
+        <f>C166*Assumptions!$C$113</f>
         <v/>
       </c>
       <c r="D167" s="33">
-        <f>D166*Assumptions!$D$109</f>
+        <f>D166*Assumptions!$D$113</f>
         <v/>
       </c>
       <c r="E167" s="33">
-        <f>E166*Assumptions!$E$109</f>
+        <f>E166*Assumptions!$E$113</f>
         <v/>
       </c>
       <c r="F167" s="33">
-        <f>F166*Assumptions!$F$109</f>
+        <f>F166*Assumptions!$F$113</f>
         <v/>
       </c>
     </row>
@@ -15107,23 +15147,23 @@
         </is>
       </c>
       <c r="B168" s="18">
-        <f>Assumptions!$B$110</f>
+        <f>Assumptions!$B$114</f>
         <v/>
       </c>
       <c r="C168" s="18">
-        <f>Assumptions!$C$110</f>
+        <f>Assumptions!$C$114</f>
         <v/>
       </c>
       <c r="D168" s="18">
-        <f>Assumptions!$D$110</f>
+        <f>Assumptions!$D$114</f>
         <v/>
       </c>
       <c r="E168" s="18">
-        <f>Assumptions!$E$110</f>
+        <f>Assumptions!$E$114</f>
         <v/>
       </c>
       <c r="F168" s="18">
-        <f>Assumptions!$F$110</f>
+        <f>Assumptions!$F$114</f>
         <v/>
       </c>
     </row>
@@ -15134,23 +15174,23 @@
         </is>
       </c>
       <c r="B169" s="33">
-        <f>B168*Assumptions!$B$111</f>
+        <f>B168*Assumptions!$B$115</f>
         <v/>
       </c>
       <c r="C169" s="33">
-        <f>C168*Assumptions!$C$111</f>
+        <f>C168*Assumptions!$C$115</f>
         <v/>
       </c>
       <c r="D169" s="33">
-        <f>D168*Assumptions!$D$111</f>
+        <f>D168*Assumptions!$D$115</f>
         <v/>
       </c>
       <c r="E169" s="33">
-        <f>E168*Assumptions!$E$111</f>
+        <f>E168*Assumptions!$E$115</f>
         <v/>
       </c>
       <c r="F169" s="33">
-        <f>F168*Assumptions!$F$111</f>
+        <f>F168*Assumptions!$F$115</f>
         <v/>
       </c>
     </row>
@@ -15161,23 +15201,23 @@
         </is>
       </c>
       <c r="B170" s="18">
-        <f>Assumptions!$B$112</f>
+        <f>Assumptions!$B$116</f>
         <v/>
       </c>
       <c r="C170" s="18">
-        <f>Assumptions!$C$112</f>
+        <f>Assumptions!$C$116</f>
         <v/>
       </c>
       <c r="D170" s="18">
-        <f>Assumptions!$D$112</f>
+        <f>Assumptions!$D$116</f>
         <v/>
       </c>
       <c r="E170" s="18">
-        <f>Assumptions!$E$112</f>
+        <f>Assumptions!$E$116</f>
         <v/>
       </c>
       <c r="F170" s="18">
-        <f>Assumptions!$F$112</f>
+        <f>Assumptions!$F$116</f>
         <v/>
       </c>
     </row>
@@ -15188,23 +15228,23 @@
         </is>
       </c>
       <c r="B171" s="33">
-        <f>B170*Assumptions!$B$113</f>
+        <f>B170*Assumptions!$B$117</f>
         <v/>
       </c>
       <c r="C171" s="33">
-        <f>C170*Assumptions!$C$113</f>
+        <f>C170*Assumptions!$C$117</f>
         <v/>
       </c>
       <c r="D171" s="33">
-        <f>D170*Assumptions!$D$113</f>
+        <f>D170*Assumptions!$D$117</f>
         <v/>
       </c>
       <c r="E171" s="33">
-        <f>E170*Assumptions!$E$113</f>
+        <f>E170*Assumptions!$E$117</f>
         <v/>
       </c>
       <c r="F171" s="33">
-        <f>F170*Assumptions!$F$113</f>
+        <f>F170*Assumptions!$F$117</f>
         <v/>
       </c>
     </row>
@@ -15215,23 +15255,23 @@
         </is>
       </c>
       <c r="B172" s="18">
-        <f>Assumptions!$B$114</f>
+        <f>Assumptions!$B$118</f>
         <v/>
       </c>
       <c r="C172" s="18">
-        <f>Assumptions!$C$114</f>
+        <f>Assumptions!$C$118</f>
         <v/>
       </c>
       <c r="D172" s="18">
-        <f>Assumptions!$D$114</f>
+        <f>Assumptions!$D$118</f>
         <v/>
       </c>
       <c r="E172" s="18">
-        <f>Assumptions!$E$114</f>
+        <f>Assumptions!$E$118</f>
         <v/>
       </c>
       <c r="F172" s="18">
-        <f>Assumptions!$F$114</f>
+        <f>Assumptions!$F$118</f>
         <v/>
       </c>
     </row>
@@ -15242,23 +15282,23 @@
         </is>
       </c>
       <c r="B173" s="33">
-        <f>B172*Assumptions!$B$115</f>
+        <f>B172*Assumptions!$B$119</f>
         <v/>
       </c>
       <c r="C173" s="33">
-        <f>C172*Assumptions!$C$115</f>
+        <f>C172*Assumptions!$C$119</f>
         <v/>
       </c>
       <c r="D173" s="33">
-        <f>D172*Assumptions!$D$115</f>
+        <f>D172*Assumptions!$D$119</f>
         <v/>
       </c>
       <c r="E173" s="33">
-        <f>E172*Assumptions!$E$115</f>
+        <f>E172*Assumptions!$E$119</f>
         <v/>
       </c>
       <c r="F173" s="33">
-        <f>F172*Assumptions!$F$115</f>
+        <f>F172*Assumptions!$F$119</f>
         <v/>
       </c>
     </row>
@@ -15269,23 +15309,23 @@
         </is>
       </c>
       <c r="B174" s="18">
-        <f>Assumptions!$B$116</f>
+        <f>Assumptions!$B$120</f>
         <v/>
       </c>
       <c r="C174" s="18">
-        <f>Assumptions!$C$116</f>
+        <f>Assumptions!$C$120</f>
         <v/>
       </c>
       <c r="D174" s="18">
-        <f>Assumptions!$D$116</f>
+        <f>Assumptions!$D$120</f>
         <v/>
       </c>
       <c r="E174" s="18">
-        <f>Assumptions!$E$116</f>
+        <f>Assumptions!$E$120</f>
         <v/>
       </c>
       <c r="F174" s="18">
-        <f>Assumptions!$F$116</f>
+        <f>Assumptions!$F$120</f>
         <v/>
       </c>
     </row>
@@ -15296,23 +15336,23 @@
         </is>
       </c>
       <c r="B175" s="33">
-        <f>B174*Assumptions!$B$117</f>
+        <f>B174*Assumptions!$B$121</f>
         <v/>
       </c>
       <c r="C175" s="33">
-        <f>C174*Assumptions!$C$117</f>
+        <f>C174*Assumptions!$C$121</f>
         <v/>
       </c>
       <c r="D175" s="33">
-        <f>D174*Assumptions!$D$117</f>
+        <f>D174*Assumptions!$D$121</f>
         <v/>
       </c>
       <c r="E175" s="33">
-        <f>E174*Assumptions!$E$117</f>
+        <f>E174*Assumptions!$E$121</f>
         <v/>
       </c>
       <c r="F175" s="33">
-        <f>F174*Assumptions!$F$117</f>
+        <f>F174*Assumptions!$F$121</f>
         <v/>
       </c>
     </row>
@@ -15323,23 +15363,23 @@
         </is>
       </c>
       <c r="B176" s="33">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$92)^1</f>
+        <f>-Assumptions!$C$104*(1+Assumptions!$C$92)</f>
         <v/>
       </c>
       <c r="C176" s="33">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$92)^2</f>
+        <f>-Assumptions!$C$104*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)</f>
         <v/>
       </c>
       <c r="D176" s="33">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$92)^3</f>
+        <f>-Assumptions!$C$104*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)</f>
         <v/>
       </c>
       <c r="E176" s="33">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$92)^4</f>
+        <f>-Assumptions!$C$104*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)</f>
         <v/>
       </c>
       <c r="F176" s="33">
-        <f>-Assumptions!$C$100*(1+Assumptions!$C$92)^5</f>
+        <f>-Assumptions!$C$104*(1+Assumptions!$C$92)*(1+Assumptions!$C$93)*(1+Assumptions!$C$94)*(1+Assumptions!$C$95)*(1+Assumptions!$C$96)</f>
         <v/>
       </c>
     </row>
@@ -16267,7 +16307,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
     </row>
@@ -16278,7 +16318,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>-Assumptions!$C$150</f>
+        <f>-Assumptions!$C$154</f>
         <v/>
       </c>
     </row>
@@ -16289,7 +16329,7 @@
         </is>
       </c>
       <c r="C10" s="18">
-        <f>-Assumptions!$C$151</f>
+        <f>-Assumptions!$C$155</f>
         <v/>
       </c>
     </row>
@@ -16311,7 +16351,7 @@
         </is>
       </c>
       <c r="C12" s="18">
-        <f>-Assumptions!$C$152</f>
+        <f>-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -16399,7 +16439,7 @@
         </is>
       </c>
       <c r="C20" s="8">
-        <f>Assumptions!$C$169</f>
+        <f>Assumptions!$C$173</f>
         <v/>
       </c>
     </row>
@@ -16439,11 +16479,11 @@
         </is>
       </c>
       <c r="C23" s="33">
-        <f>C22+Assumptions!$C$157-Assumptions!$C$150-Assumptions!$C$151-Assumptions!$C$82-Assumptions!$C$152</f>
+        <f>C22+Assumptions!$C$161-Assumptions!$C$154-Assumptions!$C$155-Assumptions!$C$82-Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="D23" s="33">
-        <f>D22+Assumptions!$C$157-Assumptions!$C$150-Assumptions!$C$151-Assumptions!$C$82-Assumptions!$C$152</f>
+        <f>D22+Assumptions!$C$161-Assumptions!$C$154-Assumptions!$C$155-Assumptions!$C$82-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -16532,7 +16572,7 @@
         </is>
       </c>
       <c r="C31" s="18">
-        <f>Assumptions!$C$150+Assumptions!$C$151+Assumptions!$C$82</f>
+        <f>Assumptions!$C$154+Assumptions!$C$155+Assumptions!$C$82</f>
         <v/>
       </c>
     </row>
@@ -16598,7 +16638,7 @@
         </is>
       </c>
       <c r="C37" s="40">
-        <f>C30/(Assumptions!$C$158+Assumptions!$C$152)</f>
+        <f>C30/(Assumptions!$C$162+Assumptions!$C$156)</f>
         <v/>
       </c>
     </row>
@@ -16609,7 +16649,7 @@
         </is>
       </c>
       <c r="C38" s="8">
-        <f>Assumptions!$C$162/C30</f>
+        <f>Assumptions!$C$166/C30</f>
         <v/>
       </c>
     </row>
@@ -16620,7 +16660,7 @@
         </is>
       </c>
       <c r="C39" s="33">
-        <f>C32+Assumptions!$C$152+Assumptions!$C$154</f>
+        <f>C32+Assumptions!$C$156+Assumptions!$C$158</f>
         <v/>
       </c>
     </row>
@@ -16695,7 +16735,7 @@
         </is>
       </c>
       <c r="C46" s="33">
-        <f>C45+Assumptions!$C$157-Assumptions!$C$150-Assumptions!$C$151-Assumptions!$C$82-Assumptions!$C$152</f>
+        <f>C45+Assumptions!$C$161-Assumptions!$C$154-Assumptions!$C$155-Assumptions!$C$82-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -16801,11 +16841,11 @@
         </is>
       </c>
       <c r="C55" s="33">
-        <f>C54+Assumptions!$C$157-Assumptions!$C$150-Assumptions!$C$151-Assumptions!$C$82-Assumptions!$C$152</f>
+        <f>C54+Assumptions!$C$161-Assumptions!$C$154-Assumptions!$C$155-Assumptions!$C$82-Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="D55" s="33">
-        <f>D54+Assumptions!$C$157-Assumptions!$C$150-Assumptions!$C$151-Assumptions!$C$82-Assumptions!$C$152</f>
+        <f>D54+Assumptions!$C$161-Assumptions!$C$154-Assumptions!$C$155-Assumptions!$C$82-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -16874,7 +16914,7 @@
         </is>
       </c>
       <c r="C61" s="18">
-        <f>Assumptions!$C$158</f>
+        <f>Assumptions!$C$162</f>
         <v/>
       </c>
     </row>
@@ -16929,7 +16969,7 @@
         </is>
       </c>
       <c r="C66" s="8">
-        <f>Assumptions!$C$164</f>
+        <f>Assumptions!$C$168</f>
         <v/>
       </c>
     </row>
@@ -16940,7 +16980,7 @@
         </is>
       </c>
       <c r="C67" s="8">
-        <f>Assumptions!$C$168</f>
+        <f>Assumptions!$C$172</f>
         <v/>
       </c>
     </row>
@@ -17951,23 +17991,23 @@
         </is>
       </c>
       <c r="B13" s="18">
-        <f>-Assumptions!$B$120</f>
+        <f>-Assumptions!$B$124</f>
         <v/>
       </c>
       <c r="C13" s="18">
-        <f>-Assumptions!$C$120</f>
+        <f>-Assumptions!$C$124</f>
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>-Assumptions!$D$120</f>
+        <f>-Assumptions!$D$124</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>-Assumptions!$E$120</f>
+        <f>-Assumptions!$E$124</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>-Assumptions!$F$120</f>
+        <f>-Assumptions!$F$124</f>
         <v/>
       </c>
     </row>
@@ -18280,23 +18320,23 @@
         </is>
       </c>
       <c r="B26" s="33">
-        <f>-B8*(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-B8*(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="C26" s="33">
-        <f>-C8*(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-C8*(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="D26" s="33">
-        <f>-D8*(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-D8*(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>-E8*(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-E8*(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>-F8*(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-F8*(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
     </row>
@@ -18307,23 +18347,23 @@
         </is>
       </c>
       <c r="B27" s="33">
-        <f>-B8*(Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-B8*(Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="C27" s="33">
-        <f>-C8*(Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-C8*(Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="D27" s="33">
-        <f>-D8*(Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-D8*(Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="E27" s="33">
-        <f>-E8*(Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-E8*(Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>-F8*(Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-F8*(Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
     </row>
@@ -18334,23 +18374,23 @@
         </is>
       </c>
       <c r="B28" s="33">
-        <f>-B8*(Assumptions!$C$147)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-B8*(Assumptions!$C$151)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="C28" s="33">
-        <f>-C8*(Assumptions!$C$147)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-C8*(Assumptions!$C$151)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="D28" s="33">
-        <f>-D8*(Assumptions!$C$147)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-D8*(Assumptions!$C$151)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="E28" s="33">
-        <f>-E8*(Assumptions!$C$147)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-E8*(Assumptions!$C$151)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>-F8*(Assumptions!$C$147)/(Assumptions!$C$141+Assumptions!$C$142+Assumptions!$C$143+Assumptions!$C$144+Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147)</f>
+        <f>-F8*(Assumptions!$C$151)/(Assumptions!$C$145+Assumptions!$C$146+Assumptions!$C$147+Assumptions!$C$148+Assumptions!$C$149+Assumptions!$C$150+Assumptions!$C$151)</f>
         <v/>
       </c>
     </row>
@@ -18442,23 +18482,23 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>B29*Assumptions!$C$138</f>
+        <f>B29*Assumptions!$C$142</f>
         <v/>
       </c>
       <c r="C32" s="33">
-        <f>C29*Assumptions!$C$138</f>
+        <f>C29*Assumptions!$C$142</f>
         <v/>
       </c>
       <c r="D32" s="33">
-        <f>D29*Assumptions!$C$138</f>
+        <f>D29*Assumptions!$C$142</f>
         <v/>
       </c>
       <c r="E32" s="33">
-        <f>E29*Assumptions!$C$138</f>
+        <f>E29*Assumptions!$C$142</f>
         <v/>
       </c>
       <c r="F32" s="33">
-        <f>F29*Assumptions!$C$138</f>
+        <f>F29*Assumptions!$C$142</f>
         <v/>
       </c>
     </row>
@@ -18469,23 +18509,23 @@
         </is>
       </c>
       <c r="B33" s="33">
-        <f>B30*Assumptions!$C$139</f>
+        <f>B30*Assumptions!$C$143</f>
         <v/>
       </c>
       <c r="C33" s="33">
-        <f>C30*Assumptions!$C$139</f>
+        <f>C30*Assumptions!$C$143</f>
         <v/>
       </c>
       <c r="D33" s="33">
-        <f>D30*Assumptions!$C$139</f>
+        <f>D30*Assumptions!$C$143</f>
         <v/>
       </c>
       <c r="E33" s="33">
-        <f>E30*Assumptions!$C$139</f>
+        <f>E30*Assumptions!$C$143</f>
         <v/>
       </c>
       <c r="F33" s="33">
-        <f>F30*Assumptions!$C$139</f>
+        <f>F30*Assumptions!$C$143</f>
         <v/>
       </c>
     </row>
@@ -18496,23 +18536,23 @@
         </is>
       </c>
       <c r="B34" s="33">
-        <f>B31*Assumptions!$C$140</f>
+        <f>B31*Assumptions!$C$144</f>
         <v/>
       </c>
       <c r="C34" s="33">
-        <f>C31*Assumptions!$C$140</f>
+        <f>C31*Assumptions!$C$144</f>
         <v/>
       </c>
       <c r="D34" s="33">
-        <f>D31*Assumptions!$C$140</f>
+        <f>D31*Assumptions!$C$144</f>
         <v/>
       </c>
       <c r="E34" s="33">
-        <f>E31*Assumptions!$C$140</f>
+        <f>E31*Assumptions!$C$144</f>
         <v/>
       </c>
       <c r="F34" s="33">
-        <f>F31*Assumptions!$C$140</f>
+        <f>F31*Assumptions!$C$144</f>
         <v/>
       </c>
     </row>
@@ -18589,7 +18629,7 @@
         </is>
       </c>
       <c r="C39" s="8">
-        <f>Assumptions!$C$164</f>
+        <f>Assumptions!$C$168</f>
         <v/>
       </c>
     </row>
@@ -18699,7 +18739,7 @@
         </is>
       </c>
       <c r="C49" s="18">
-        <f>Assumptions!$C$157</f>
+        <f>Assumptions!$C$161</f>
         <v/>
       </c>
     </row>
@@ -18721,7 +18761,7 @@
         </is>
       </c>
       <c r="C51" s="18">
-        <f>-Assumptions!$C$150</f>
+        <f>-Assumptions!$C$154</f>
         <v/>
       </c>
     </row>
@@ -18732,7 +18772,7 @@
         </is>
       </c>
       <c r="C52" s="18">
-        <f>-Assumptions!$C$151</f>
+        <f>-Assumptions!$C$155</f>
         <v/>
       </c>
     </row>
@@ -18754,7 +18794,7 @@
         </is>
       </c>
       <c r="C54" s="18">
-        <f>-Assumptions!$C$152</f>
+        <f>-Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -18776,7 +18816,7 @@
         </is>
       </c>
       <c r="C56" s="18">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$159</f>
         <v/>
       </c>
     </row>
@@ -18787,7 +18827,7 @@
         </is>
       </c>
       <c r="C57" s="33">
-        <f>Assumptions!$C$154-C56</f>
+        <f>Assumptions!$C$158-C56</f>
         <v/>
       </c>
     </row>
@@ -18798,7 +18838,7 @@
         </is>
       </c>
       <c r="C58" s="50">
-        <f>Assumptions!$C$156*C57/Assumptions!$C$154</f>
+        <f>Assumptions!$C$160*C57/Assumptions!$C$158</f>
         <v/>
       </c>
     </row>
@@ -19165,12 +19205,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>Cost of debt — the three constructions averaged. This is a simple average of three independent readings, NOT a figure weighted by what is drawn; the weighted one is the line below</t>
+          <t>Cost of debt ADOPTED — method 2, the instruments actually outstanding weighted by balance. It is the only one of the three that reproduces from the facility lines, which is what makes it checkable from outside this model; methods 1 and 3 are published above as what they are, a marginal drawdown rate and a disclosed range midpoint, and are no longer averaged into the answer</t>
         </is>
       </c>
       <c r="B92" s="14" t="n"/>
       <c r="C92" s="51">
-        <f>AVERAGE(C74,C90,C91)</f>
+        <f>C90</f>
         <v/>
       </c>
       <c r="D92" s="14" t="n"/>
@@ -19178,11 +19218,11 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Memorandum — cost of debt on the balance-weighted construction alone (method 2), the only one of the three that is weighted by the instruments actually outstanding</t>
+          <t>MEMORANDUM — the retired average of the three constructions, which reproduces from no set of balances and rates and is shown so a reader can see what the previous construction said</t>
         </is>
       </c>
       <c r="C93" s="50">
-        <f>C90</f>
+        <f>AVERAGE(C74,C90,C91)</f>
         <v/>
       </c>
     </row>
@@ -19249,7 +19289,7 @@
         </is>
       </c>
       <c r="C99" s="18">
-        <f>Assumptions!$C$152</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -19304,7 +19344,7 @@
         </is>
       </c>
       <c r="C104" s="50">
-        <f>C72+Assumptions!$C$153</f>
+        <f>C72+Assumptions!$C$157</f>
         <v/>
       </c>
     </row>
@@ -19372,7 +19412,7 @@
         </is>
       </c>
       <c r="C110" s="50">
-        <f>C106+Assumptions!$C$153</f>
+        <f>C106+Assumptions!$C$157</f>
         <v/>
       </c>
     </row>
@@ -20569,23 +20609,23 @@
         <v>18959</v>
       </c>
       <c r="E22" s="18">
-        <f>Assumptions!$C$24*Assumptions!$C$159</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="F22" s="18">
-        <f>Assumptions!$C$24*Assumptions!$C$159</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="G22" s="18">
-        <f>Assumptions!$C$24*Assumptions!$C$159</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="H22" s="18">
-        <f>Assumptions!$C$24*Assumptions!$C$159</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163</f>
         <v/>
       </c>
       <c r="I22" s="18">
-        <f>Assumptions!$C$24*Assumptions!$C$159</f>
+        <f>Assumptions!$C$24*Assumptions!$C$163</f>
         <v/>
       </c>
     </row>
@@ -20755,23 +20795,23 @@
         <v>-24306</v>
       </c>
       <c r="E27" s="33">
-        <f>-E26*Assumptions!$C$156</f>
+        <f>-E26*Assumptions!$C$160</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>-F26*Assumptions!$C$156</f>
+        <f>-F26*Assumptions!$C$160</f>
         <v/>
       </c>
       <c r="G27" s="33">
-        <f>-G26*Assumptions!$C$156</f>
+        <f>-G26*Assumptions!$C$160</f>
         <v/>
       </c>
       <c r="H27" s="33">
-        <f>-H26*Assumptions!$C$156</f>
+        <f>-H26*Assumptions!$C$160</f>
         <v/>
       </c>
       <c r="I27" s="33">
-        <f>-I26*Assumptions!$C$156</f>
+        <f>-I26*Assumptions!$C$160</f>
         <v/>
       </c>
     </row>
@@ -20830,23 +20870,23 @@
         <v>-61333</v>
       </c>
       <c r="E29" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="G29" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="H29" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
       <c r="I29" s="33">
-        <f>-Assumptions!$C$152*(Assumptions!$C$24+Assumptions!$C$153)</f>
+        <f>-Assumptions!$C$156*(Assumptions!$C$24+Assumptions!$C$157)</f>
         <v/>
       </c>
     </row>

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -1264,7 +1264,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>0.705. The published index is weighted by size and is therefore dominated by the very group this</t>
+          <t>0.690. The published index is weighted by size and is therefore dominated by the very group this</t>
         </is>
       </c>
     </row>
@@ -5534,20 +5534,20 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.690</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>7.256472712000055</v>
+        <v>7.347689414158981</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>7.552205629563578</v>
+        <v>7.653804628596395</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>7.903387977796284</v>
+        <v>8.018135758598335</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>8.328651590959588</v>
+        <v>8.460503842511894</v>
       </c>
     </row>
     <row r="7">
@@ -5629,7 +5629,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.705 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 5.61 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.690 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 5.61 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Discounted cash flow (composite-index beta of 0.705)</t>
+          <t>Discounted cash flow (composite-index beta of 0.690)</t>
         </is>
       </c>
       <c r="B12" s="9">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="C15" s="31" t="n">
-        <v>0.705</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -5180,7 +5180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5429,13 +5429,21 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Calibration verdict on the five-year walk-forward</t>
-        </is>
-      </c>
-      <c r="C19" s="55" t="inlineStr">
-        <is>
-          <t>PARITY</t>
-        </is>
+          <t>Resolved three-month forecasts scored</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Price finished inside the 90% band</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="21">
@@ -5443,6 +5451,19 @@
         <is>
           <t>The price map is a dispersion forecast from the price series alone. It is deliberately not reconciled to the valuation lenses: one is a statement about what a price could do over weeks, the other about what a business is worth.</t>
         </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Band width against a naive carry-anchored band</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="n">
+        <v>1.181952275030422</v>
       </c>
     </row>
   </sheetData>

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -8153,7 +8153,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Weighted central</t>
+          <t>Central — the cash-flow lens</t>
         </is>
       </c>
       <c r="B12" s="16" t="n"/>
@@ -8238,12 +8238,12 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Weighted central — published-index beta (AED)</t>
+          <t>Central — published-index beta (AED)</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>all four lenses</t>
+          <t>the cash-flow lens alone; the other reads are cross-checks published beside it and never averaged into it</t>
         </is>
       </c>
       <c r="C19" s="7">
@@ -8318,12 +8318,12 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Weighted central — composite-index beta (AED)</t>
+          <t>Central — composite-index beta (AED)</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>all four lenses, the discounted-cash-flow leg swapped</t>
+          <t>the same cash-flow lens with the composite beta in place of the published-index one; nothing else moves</t>
         </is>
       </c>
       <c r="C24" s="7">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -5562,16 +5562,16 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>6.938037692964431</v>
+        <v>6.728083378789989</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>7.137781232079598</v>
+        <v>6.906809600441632</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>7.373422039059579</v>
+        <v>7.116249427717197</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>7.656918976576681</v>
+        <v>7.366274120519086</v>
       </c>
     </row>
     <row r="7">
@@ -5581,16 +5581,16 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>5.959600015752238</v>
+        <v>5.906348792912149</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>6.070595937395918</v>
+        <v>6.013177127638978</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>6.197231672373617</v>
+        <v>6.134806347064103</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>6.343889891279893</v>
+        <v>6.275343312247685</v>
       </c>
     </row>
     <row r="8">
@@ -5600,16 +5600,16 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>5.215043964560241</v>
+        <v>5.259742527779303</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>5.273778672941666</v>
+        <v>5.32125418366628</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>5.338494934992969</v>
+        <v>5.389209857567612</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>5.410645630801445</v>
+        <v>5.465188765743561</v>
       </c>
     </row>
     <row r="9">
@@ -5619,16 +5619,16 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>4.496048415139696</v>
+        <v>4.617282331362698</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>4.516240689244266</v>
+        <v>4.643177472038053</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>4.53671263228333</v>
+        <v>4.670102265596956</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>4.557522713376986</v>
+        <v>4.698277698445229</v>
       </c>
     </row>
     <row r="10">
@@ -5638,22 +5638,22 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>3.871039805611379</v>
+        <v>4.04406102323366</v>
       </c>
       <c r="C10" s="23" t="n">
-        <v>3.866770810871812</v>
+        <v>4.045749698560035</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>3.860048052867076</v>
+        <v>4.045566909808216</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>3.850426579562018</v>
+        <v>4.043159213101122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.690 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 5.34 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
+          <t>The beta rows are not evenly spaced round numbers. They span the two index constructions and the interval around the adopted one: 0.690 is the equal-weight composite of the exchange's own names, 1.103 is the adopted regression against the exchange's published index, and 1.621 is the top of that regression's own 90% confidence interval (its bottom, 0.586, sits below the composite reading, so the bull case is struck outside this grid). The terminal growth column at 2.0% is the one the model runs on, so the cell where that column meets the 1.103 row is the published cash-flow value of AED 5.39 — every cell here is a complete re-run of the model discounted at the same three tranches of capital the valuation itself uses, equity, debt and the perpetual securities, so the grid is centred on the figure it brackets.</t>
         </is>
       </c>
     </row>
@@ -5706,19 +5706,19 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>3.923090177641181</v>
+        <v>3.960529174125023</v>
       </c>
       <c r="C14" s="23" t="n">
-        <v>4.630792556317077</v>
+        <v>4.674869515846321</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>5.338494934992969</v>
+        <v>5.389209857567612</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>6.046197313668863</v>
+        <v>6.103550199288907</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>6.753899692344756</v>
+        <v>6.817890541010201</v>
       </c>
     </row>
     <row r="15">
@@ -5735,7 +5735,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>This row and the one below it are re-runs of the whole model at the same 8.71% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 5.34 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
+          <t>This row and the one below it are re-runs of the whole model at the same 8.66% cost of capital the valuation uses, so the 1.00x cell reproduces the published AED 5.39 exactly and the swing across the row is a clean read of what that single driver is worth.</t>
         </is>
       </c>
     </row>
@@ -5783,16 +5783,16 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>5.722931417958425</v>
+        <v>5.775643184894931</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>5.338494934992969</v>
+        <v>5.389209857567612</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>4.954058452027515</v>
+        <v>5.002776530240293</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>4.569621969062061</v>
+        <v>4.616343202912974</v>
       </c>
     </row>
     <row r="20">
@@ -5845,13 +5845,13 @@
         </is>
       </c>
       <c r="B24" s="23" t="n">
-        <v>5.229751393214664</v>
+        <v>5.280150790035071</v>
       </c>
       <c r="C24" s="23" t="n">
-        <v>4.835923270223883</v>
+        <v>4.883674482048688</v>
       </c>
       <c r="D24" s="23" t="n">
-        <v>4.24518108573771</v>
+        <v>4.288960020069105</v>
       </c>
     </row>
     <row r="25">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="C6" s="23" t="n">
-        <v>2.757748617839643</v>
+        <v>2.901206740142437</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -8102,7 +8102,7 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>9.979174693829732</v>
+        <v>9.487133335472489</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -8444,13 +8444,13 @@
         </is>
       </c>
       <c r="C32" s="23" t="n">
-        <v>9.345433196698188</v>
+        <v>9.429012541620233</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>6.278805418053406</v>
+        <v>6.514574635137859</v>
       </c>
       <c r="E32" s="23" t="n">
-        <v>15.82296964850308</v>
+        <v>14.92754150840185</v>
       </c>
     </row>
     <row r="33">
@@ -8465,13 +8465,13 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>4.671573090127655</v>
+        <v>4.723665256272398</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>3.5807763747911</v>
+        <v>3.608196688676206</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>5.504711667694399</v>
+        <v>5.576266469484299</v>
       </c>
     </row>
     <row r="34">

--- a/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
+++ b/engine/adnocls_study/ADNOCLS_Valuation_Model_09082026_public.xlsx
@@ -1586,23 +1586,23 @@
         <v>19434</v>
       </c>
       <c r="E7" s="20">
-        <f>Assumptions!$C$189</f>
+        <f>Assumptions!$C$191</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>Assumptions!$C$189</f>
+        <f>Assumptions!$C$191</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>Assumptions!$C$189</f>
+        <f>Assumptions!$C$191</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>Assumptions!$C$189</f>
+        <f>Assumptions!$C$191</f>
         <v/>
       </c>
       <c r="I7" s="20">
-        <f>Assumptions!$C$189</f>
+        <f>Assumptions!$C$191</f>
         <v/>
       </c>
     </row>
@@ -1622,23 +1622,23 @@
         <v>51368</v>
       </c>
       <c r="E8" s="20">
-        <f>Assumptions!$C$190</f>
+        <f>Assumptions!$C$192</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>Assumptions!$C$190</f>
+        <f>Assumptions!$C$192</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>Assumptions!$C$190</f>
+        <f>Assumptions!$C$192</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>Assumptions!$C$190</f>
+        <f>Assumptions!$C$192</f>
         <v/>
       </c>
       <c r="I8" s="20">
-        <f>Assumptions!$C$190</f>
+        <f>Assumptions!$C$192</f>
         <v/>
       </c>
     </row>
@@ -1699,23 +1699,23 @@
         <v>577769</v>
       </c>
       <c r="E10" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
       <c r="I10" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
     </row>
@@ -1807,23 +1807,23 @@
         <v>337794</v>
       </c>
       <c r="E13" s="20">
-        <f>Assumptions!$C$188</f>
+        <f>Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>Assumptions!$C$188</f>
+        <f>Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="G13" s="20">
-        <f>Assumptions!$C$188</f>
+        <f>Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>Assumptions!$C$188</f>
+        <f>Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="I13" s="20">
-        <f>Assumptions!$C$188</f>
+        <f>Assumptions!$C$190</f>
         <v/>
       </c>
     </row>
@@ -2034,23 +2034,23 @@
         <v>1978619</v>
       </c>
       <c r="E19" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
     </row>
@@ -2070,23 +2070,23 @@
         <v>264512</v>
       </c>
       <c r="E20" s="20">
-        <f>Assumptions!$C$183</f>
+        <f>Assumptions!$C$185</f>
         <v/>
       </c>
       <c r="F20" s="20">
-        <f>Assumptions!$C$183</f>
+        <f>Assumptions!$C$185</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>Assumptions!$C$183</f>
+        <f>Assumptions!$C$185</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>Assumptions!$C$183</f>
+        <f>Assumptions!$C$185</f>
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>Assumptions!$C$183</f>
+        <f>Assumptions!$C$185</f>
         <v/>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>'Income Statement'!E28/((Assumptions!$C$187+E21)/2)</f>
+        <f>'Income Statement'!E28/((Assumptions!$C$189+E21)/2)</f>
         <v/>
       </c>
       <c r="F28" s="10">
@@ -2469,23 +2469,23 @@
         </is>
       </c>
       <c r="B32" s="20">
-        <f>Assumptions!$B$148</f>
+        <f>Assumptions!$B$150</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>Assumptions!$C$148</f>
+        <f>Assumptions!$C$150</f>
         <v/>
       </c>
       <c r="D32" s="20">
-        <f>Assumptions!$D$148</f>
+        <f>Assumptions!$D$150</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>Assumptions!$E$148</f>
+        <f>Assumptions!$E$150</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f>Assumptions!$F$148</f>
+        <f>Assumptions!$F$150</f>
         <v/>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="B33" s="20">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="C33" s="33">
@@ -2523,23 +2523,23 @@
         </is>
       </c>
       <c r="B34" s="21">
-        <f>Assumptions!$C$149</f>
+        <f>Assumptions!$C$151</f>
         <v/>
       </c>
       <c r="C34" s="21">
-        <f>Assumptions!$C$149</f>
+        <f>Assumptions!$C$151</f>
         <v/>
       </c>
       <c r="D34" s="21">
-        <f>Assumptions!$C$149</f>
+        <f>Assumptions!$C$151</f>
         <v/>
       </c>
       <c r="E34" s="21">
-        <f>Assumptions!$C$149</f>
+        <f>Assumptions!$C$151</f>
         <v/>
       </c>
       <c r="F34" s="21">
-        <f>Assumptions!$C$149</f>
+        <f>Assumptions!$C$151</f>
         <v/>
       </c>
     </row>
@@ -2631,23 +2631,23 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>Assumptions!$C$150*(1+Assumptions!$C$99)</f>
+        <f>Assumptions!$C$152*(1+Assumptions!$C$101)</f>
         <v/>
       </c>
       <c r="C38" s="33">
-        <f>Assumptions!$C$150*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)</f>
+        <f>Assumptions!$C$152*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
         <v/>
       </c>
       <c r="D38" s="33">
-        <f>Assumptions!$C$150*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)</f>
+        <f>Assumptions!$C$152*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
         <v/>
       </c>
       <c r="E38" s="33">
-        <f>Assumptions!$C$150*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
+        <f>Assumptions!$C$152*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)</f>
         <v/>
       </c>
       <c r="F38" s="33">
-        <f>Assumptions!$C$150*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
+        <f>Assumptions!$C$152*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)*(1+Assumptions!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -2771,23 +2771,23 @@
         </is>
       </c>
       <c r="B43" s="19">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="C43" s="19">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="D43" s="19">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="E43" s="19">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
       <c r="F43" s="19">
-        <f>Assumptions!$C$154</f>
+        <f>Assumptions!$C$156</f>
         <v/>
       </c>
     </row>
@@ -2798,23 +2798,23 @@
         </is>
       </c>
       <c r="B44" s="19">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$157</f>
         <v/>
       </c>
       <c r="C44" s="19">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$157</f>
         <v/>
       </c>
       <c r="D44" s="19">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$157</f>
         <v/>
       </c>
       <c r="E44" s="19">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$157</f>
         <v/>
       </c>
       <c r="F44" s="19">
-        <f>Assumptions!$C$155</f>
+        <f>Assumptions!$C$157</f>
         <v/>
       </c>
     </row>
@@ -2825,23 +2825,23 @@
         </is>
       </c>
       <c r="B45" s="19">
-        <f>Assumptions!$C$156</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="C45" s="19">
-        <f>Assumptions!$C$156</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="D45" s="19">
-        <f>Assumptions!$C$156</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="E45" s="19">
-        <f>Assumptions!$C$156</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
       <c r="F45" s="19">
-        <f>Assumptions!$C$156</f>
+        <f>Assumptions!$C$158</f>
         <v/>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B50" s="38">
-        <f>B49-Assumptions!$C$157</f>
+        <f>B49-Assumptions!$C$159</f>
         <v/>
       </c>
       <c r="C50" s="38">
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>Assumptions!$C$178+Assumptions!$C$180+Assumptions!$C$88</f>
+        <f>Assumptions!$C$180+Assumptions!$C$182+Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="C53" s="33">
@@ -3046,23 +3046,23 @@
         </is>
       </c>
       <c r="B54" s="33">
-        <f>B53+Assumptions!$C$188</f>
+        <f>B53+Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="C54" s="33">
-        <f>C53+Assumptions!$C$188</f>
+        <f>C53+Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="D54" s="33">
-        <f>D53+Assumptions!$C$188</f>
+        <f>D53+Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="E54" s="33">
-        <f>E53+Assumptions!$C$188</f>
+        <f>E53+Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="F54" s="33">
-        <f>F53+Assumptions!$C$188</f>
+        <f>F53+Assumptions!$C$190</f>
         <v/>
       </c>
     </row>
@@ -3127,23 +3127,23 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>-B55*(1-Assumptions!$C$21)</f>
+        <f>-B55*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="C57" s="33">
-        <f>-C55*(1-Assumptions!$C$21)</f>
+        <f>-C55*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="D57" s="33">
-        <f>-D55*(1-Assumptions!$C$21)</f>
+        <f>-D55*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="E57" s="33">
-        <f>-E55*(1-Assumptions!$C$21)</f>
+        <f>-E55*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="F57" s="33">
-        <f>-F55*(1-Assumptions!$C$21)</f>
+        <f>-F55*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -3154,23 +3154,23 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$188*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="C58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$188*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="D58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$188*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="E58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$188*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
       <c r="F58" s="33">
-        <f>Assumptions!$C$24*Assumptions!$C$188*(1-Assumptions!$C$21)</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190*(1-Assumptions!$C$23)</f>
         <v/>
       </c>
     </row>
@@ -3181,23 +3181,23 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="C59" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="D59" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="E59" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="F59" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
     </row>
@@ -3235,23 +3235,23 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>-Assumptions!$C$191*(1+Assumptions!$C$192)^0</f>
+        <f>-Assumptions!$C$193*(1+Assumptions!$C$194)^0</f>
         <v/>
       </c>
       <c r="C61" s="33">
-        <f>-Assumptions!$C$191*(1+Assumptions!$C$192)^1</f>
+        <f>-Assumptions!$C$193*(1+Assumptions!$C$194)^1</f>
         <v/>
       </c>
       <c r="D61" s="33">
-        <f>-Assumptions!$C$191*(1+Assumptions!$C$192)^2</f>
+        <f>-Assumptions!$C$193*(1+Assumptions!$C$194)^2</f>
         <v/>
       </c>
       <c r="E61" s="33">
-        <f>-Assumptions!$C$191*(1+Assumptions!$C$192)^3</f>
+        <f>-Assumptions!$C$193*(1+Assumptions!$C$194)^3</f>
         <v/>
       </c>
       <c r="F61" s="33">
-        <f>-Assumptions!$C$191*(1+Assumptions!$C$192)^4</f>
+        <f>-Assumptions!$C$193*(1+Assumptions!$C$194)^4</f>
         <v/>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="B65" s="20">
-        <f>Assumptions!$C$187</f>
+        <f>Assumptions!$C$189</f>
         <v/>
       </c>
       <c r="C65" s="33">
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>Assumptions!$C$196</f>
+        <f>Assumptions!$C$198</f>
         <v/>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>Assumptions!$C$199</f>
+        <f>Assumptions!$C$201</f>
         <v/>
       </c>
       <c r="F5" s="9">
@@ -7583,7 +7583,7 @@
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>Assumptions!$C$200</f>
+        <f>Assumptions!$C$202</f>
         <v/>
       </c>
       <c r="F6" s="9">
@@ -7614,7 +7614,7 @@
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>Assumptions!$C$201</f>
+        <f>Assumptions!$C$203</f>
         <v/>
       </c>
       <c r="F7" s="9">
@@ -7645,7 +7645,7 @@
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>Assumptions!$C$202</f>
+        <f>Assumptions!$C$204</f>
         <v/>
       </c>
       <c r="F8" s="9">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="C23" s="20">
-        <f>Assumptions!$C$88</f>
+        <f>Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J204"/>
+  <dimension ref="A1:J206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8684,7 +8684,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium (mature premium plus country risk)</t>
+          <t>Equity risk premium, TOTAL (the two legs below add to it)</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
@@ -8699,1111 +8699,1108 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t xml:space="preserve">   of which the MATURE premium — beta applies to this leg only</t>
         </is>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.039751</v>
+        <v>0.042316</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
+          <t>Country premium — charged FLAT, once, never multiplied by beta</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>0.006384</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>0.039751</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>Statutory corporate tax rate</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C23" s="32" t="n">
         <v>0.09</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Cost of debt — the evidence behind the three constructions</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n"/>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Secured overnight financing rate</t>
-        </is>
-      </c>
-      <c r="C24" s="30" t="n">
-        <v>0.0365</v>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>The Central Bank base rate of 3.65% was maintained at the 29 July 2026 decision; the last change was a 25 basis point cut from 3.90% on 10 December 2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Parent revolving credit facility margin</t>
-        </is>
-      </c>
-      <c r="C25" s="30" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Third-party bank loans — low end of the disclosed range</t>
+          <t>Secured overnight financing rate</t>
         </is>
       </c>
       <c r="C26" s="30" t="n">
-        <v>0.0711</v>
+        <v>0.0365</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>The Central Bank base rate of 3.65% was maintained at the 29 July 2026 decision; the last change was a 25 basis point cut from 3.90% on 10 December 2025.</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Third-party bank loans — high end of the disclosed range</t>
+          <t>Parent revolving credit facility margin</t>
         </is>
       </c>
       <c r="C27" s="30" t="n">
-        <v>0.0755</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Other third-party borrowings — low end of the disclosed range</t>
+          <t>Third-party bank loans — low end of the disclosed range</t>
         </is>
       </c>
       <c r="C28" s="30" t="n">
-        <v>0.0436</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Other third-party borrowings — high end of the disclosed range</t>
+          <t>Third-party bank loans — high end of the disclosed range</t>
         </is>
       </c>
       <c r="C29" s="30" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Lease interest charged in 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="n">
-        <v>12719</v>
+          <t>Other third-party borrowings — low end of the disclosed range</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>0.0436</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, opening balance 2025 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>170274</v>
+          <t>Other third-party borrowings — high end of the disclosed range</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>0.08309999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Lease liabilities, closing balance 2025 (USD 000)</t>
+          <t>Lease interest charged in 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C32" s="29" t="n">
-        <v>223153</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Shareholder loan at 30 June 2026 (USD 000)</t>
+          <t>Lease liabilities, opening balance 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C33" s="29" t="n">
-        <v>125000</v>
+        <v>170274</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Third-party borrowings at 30 June 2026 (USD 000)</t>
+          <t>Lease liabilities, closing balance 2025 (USD 000)</t>
         </is>
       </c>
       <c r="C34" s="29" t="n">
-        <v>431353</v>
+        <v>223153</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>Shareholder loan at 30 June 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Third-party borrowings at 30 June 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>431353</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>Lease liabilities at 30 June 2026 (USD 000)</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C37" s="29" t="n">
         <v>243647</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Tanker fleet — vessel counts by class</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Handysize</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>Medium range</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>Long range 1</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>Long range 2</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>Very large crude carrier</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Vessels owned at 31 December 2025</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B40" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C40" s="29" t="n">
         <v>16</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D40" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E40" s="29" t="n">
         <v>17</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F40" s="29" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Less vessels sold between the year end and the valuation date</t>
         </is>
       </c>
-      <c r="B39" s="29" t="n">
+      <c r="B41" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C41" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D41" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E41" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F41" s="29" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>Tanker rates — the published blended rate by class and quarter (USD per day). It is a BLEND across the whole class, charters out included; the spot rate is solved out of it on the Segments sheet, never read off it</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>First quarter</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>Second quarter</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Third quarter</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>Fourth quarter</t>
         </is>
       </c>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Long range 1 — 2024</t>
-        </is>
-      </c>
-      <c r="B42" s="29" t="n">
-        <v>51645</v>
-      </c>
-      <c r="C42" s="29" t="n">
-        <v>49424</v>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>31911</v>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>27640</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Long range 2 — 2024</t>
-        </is>
-      </c>
-      <c r="B43" s="29" t="n">
-        <v>60038</v>
-      </c>
-      <c r="C43" s="29" t="n">
-        <v>63734</v>
-      </c>
-      <c r="D43" s="29" t="n">
-        <v>36237</v>
-      </c>
-      <c r="E43" s="29" t="n">
-        <v>32034</v>
-      </c>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="16" t="n"/>
+      <c r="H43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Very large crude carrier — 2024</t>
+          <t>Long range 1 — 2024</t>
         </is>
       </c>
       <c r="B44" s="29" t="n">
-        <v>54580</v>
+        <v>51645</v>
       </c>
       <c r="C44" s="29" t="n">
-        <v>46097</v>
+        <v>49424</v>
       </c>
       <c r="D44" s="29" t="n">
-        <v>39681</v>
+        <v>31911</v>
       </c>
       <c r="E44" s="29" t="n">
-        <v>33167</v>
+        <v>27640</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Medium range — 2025</t>
+          <t>Long range 2 — 2024</t>
         </is>
       </c>
       <c r="B45" s="29" t="n">
-        <v>23459</v>
+        <v>60038</v>
       </c>
       <c r="C45" s="29" t="n">
-        <v>25161</v>
+        <v>63734</v>
       </c>
       <c r="D45" s="29" t="n">
-        <v>23391</v>
+        <v>36237</v>
       </c>
       <c r="E45" s="29" t="n">
-        <v>24547</v>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>The handysize class is not broken out in the disclosure, so the medium-range rate stands in for it — SCALED by the disclosed relative move, because the company said handysize rates fell 21% while medium range rose 29%, and an unadjusted substitution therefore had the sign wrong. The gap is still flagged. The 2024 quarterly rates for the medium-range class are not disclosed either, so its 2025 average stands in on both sides of the mid-cycle average.</t>
-        </is>
+        <v>32034</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Long range 1 — 2025</t>
+          <t>Very large crude carrier — 2024</t>
         </is>
       </c>
       <c r="B46" s="29" t="n">
-        <v>21546</v>
+        <v>54580</v>
       </c>
       <c r="C46" s="29" t="n">
-        <v>24225</v>
+        <v>46097</v>
       </c>
       <c r="D46" s="29" t="n">
-        <v>24452</v>
+        <v>39681</v>
       </c>
       <c r="E46" s="29" t="n">
-        <v>26574</v>
+        <v>33167</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Long range 2 — 2025</t>
+          <t>Medium range — 2025</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>31033</v>
+        <v>23459</v>
       </c>
       <c r="C47" s="29" t="n">
-        <v>35533</v>
+        <v>25161</v>
       </c>
       <c r="D47" s="29" t="n">
-        <v>34410</v>
+        <v>23391</v>
       </c>
       <c r="E47" s="29" t="n">
-        <v>41973</v>
+        <v>24547</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>The handysize class is not broken out in the disclosure, so the medium-range rate stands in for it — SCALED by the disclosed relative move, because the company said handysize rates fell 21% while medium range rose 29%, and an unadjusted substitution therefore had the sign wrong. The gap is still flagged. The 2024 quarterly rates for the medium-range class are not disclosed either, so its 2025 average stands in on both sides of the mid-cycle average.</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>Long range 1 — 2025</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="n">
+        <v>21546</v>
+      </c>
+      <c r="C48" s="29" t="n">
+        <v>24225</v>
+      </c>
+      <c r="D48" s="29" t="n">
+        <v>24452</v>
+      </c>
+      <c r="E48" s="29" t="n">
+        <v>26574</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Long range 2 — 2025</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="n">
+        <v>31033</v>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>35533</v>
+      </c>
+      <c r="D49" s="29" t="n">
+        <v>34410</v>
+      </c>
+      <c r="E49" s="29" t="n">
+        <v>41973</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>Very large crude carrier — 2025</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B50" s="29" t="n">
         <v>39245</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C50" s="29" t="n">
         <v>44350</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D50" s="29" t="n">
         <v>40996</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E50" s="29" t="n">
         <v>85273</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Tanker rates — the published blended rate by class through 2026 (USD per day). The first two quarters are REPORTED; the third is DISCLOSED to 11 August on the share of vessel days it covers, with the balance at the mid-cycle rate; the fourth reverts halfway to mid-cycle</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>First quarter 2026</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>Second quarter 2026</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Third quarter 2026</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>Fourth quarter 2026</t>
         </is>
       </c>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="16" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Medium range</t>
-        </is>
-      </c>
-      <c r="B51" s="29" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C51" s="29" t="n">
-        <v>36229</v>
-      </c>
-      <c r="D51" s="33">
-        <f>B57*C57+(1-C57)*Segments!$J$39</f>
-        <v/>
-      </c>
-      <c r="E51" s="33">
-        <f>(1-Assumptions!$C$96)*D51+Assumptions!$C$96*Segments!$J$39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Long range 1</t>
-        </is>
-      </c>
-      <c r="B52" s="29" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C52" s="29" t="n">
-        <v>80206</v>
-      </c>
-      <c r="D52" s="33">
-        <f>B58*C58+(1-C58)*Segments!$J$40</f>
-        <v/>
-      </c>
-      <c r="E52" s="33">
-        <f>(1-Assumptions!$C$96)*D52+Assumptions!$C$96*Segments!$J$40</f>
-        <v/>
-      </c>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="16" t="n"/>
+      <c r="H52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Long range 2</t>
+          <t>Medium range</t>
         </is>
       </c>
       <c r="B53" s="29" t="n">
-        <v>58000</v>
+        <v>30000</v>
       </c>
       <c r="C53" s="29" t="n">
-        <v>129568</v>
+        <v>36229</v>
       </c>
       <c r="D53" s="33">
-        <f>B59*C59+(1-C59)*Segments!$J$41</f>
+        <f>B59*C59+(1-C59)*Segments!$J$39</f>
         <v/>
       </c>
       <c r="E53" s="33">
-        <f>(1-Assumptions!$C$96)*D53+Assumptions!$C$96*Segments!$J$41</f>
+        <f>(1-Assumptions!$C$98)*D53+Assumptions!$C$98*Segments!$J$39</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
+          <t>Long range 1</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>80206</v>
+      </c>
+      <c r="D54" s="33">
+        <f>B60*C60+(1-C60)*Segments!$J$40</f>
+        <v/>
+      </c>
+      <c r="E54" s="33">
+        <f>(1-Assumptions!$C$98)*D54+Assumptions!$C$98*Segments!$J$40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Long range 2</t>
+        </is>
+      </c>
+      <c r="B55" s="29" t="n">
+        <v>58000</v>
+      </c>
+      <c r="C55" s="29" t="n">
+        <v>129568</v>
+      </c>
+      <c r="D55" s="33">
+        <f>B61*C61+(1-C61)*Segments!$J$41</f>
+        <v/>
+      </c>
+      <c r="E55" s="33">
+        <f>(1-Assumptions!$C$98)*D55+Assumptions!$C$98*Segments!$J$41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
           <t>Very large crude carrier</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="B56" s="29" t="n">
         <v>145000</v>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C56" s="29" t="n">
         <v>291145</v>
       </c>
-      <c r="D54" s="33">
-        <f>B60*C60+(1-C60)*Segments!$J$42</f>
-        <v/>
-      </c>
-      <c r="E54" s="33">
-        <f>(1-Assumptions!$C$96)*D54+Assumptions!$C$96*Segments!$J$42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="D56" s="33">
+        <f>B62*C62+(1-C62)*Segments!$J$42</f>
+        <v/>
+      </c>
+      <c r="E56" s="33">
+        <f>(1-Assumptions!$C$98)*D56+Assumptions!$C$98*Segments!$J$42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>The disclosed third quarter and its coverage — the rate applies to the days it covers and the balance is taken at the mid-cycle rate</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Disclosed rate (USD per day)</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>Share of vessel days contracted</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Medium range — disclosed third-quarter rate and share of days covered</t>
-        </is>
-      </c>
-      <c r="B57" s="34" t="n">
-        <v>30441</v>
-      </c>
-      <c r="C57" s="34" t="n">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Long range 1</t>
-        </is>
-      </c>
-      <c r="B58" s="34" t="n">
-        <v>89721</v>
-      </c>
-      <c r="C58" s="34" t="n">
-        <v>0.62</v>
-      </c>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="16" t="n"/>
+      <c r="H58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Long range 2</t>
+          <t>Medium range — disclosed third-quarter rate and share of days covered</t>
         </is>
       </c>
       <c r="B59" s="34" t="n">
-        <v>107917</v>
+        <v>30441</v>
       </c>
       <c r="C59" s="34" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>Long range 1</t>
+        </is>
+      </c>
+      <c r="B60" s="34" t="n">
+        <v>89721</v>
+      </c>
+      <c r="C60" s="34" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Long range 2</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="n">
+        <v>107917</v>
+      </c>
+      <c r="C61" s="34" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
           <t>Very large crude carrier</t>
         </is>
       </c>
-      <c r="B60" s="34" t="n">
+      <c r="B62" s="34" t="n">
         <v>159518</v>
       </c>
-      <c r="C60" s="34" t="n">
+      <c r="C62" s="34" t="n">
         <v>0.78</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>The smallest tankers, which the rate disclosure does not break out</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="n"/>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="16" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Handysize rate as a proportion of the medium-range rate — the company disclosed Handysize DOWN 21% against medium range UP 29%, so the two smallest classes moved in OPPOSITE directions and the medium-range rate cannot stand in for the smallest unadjusted. It scales the medium-range rate in every window and on both sides of the mid-cycle average</t>
         </is>
       </c>
-      <c r="C63" s="28" t="n">
+      <c r="C65" s="28" t="n">
         <v>0.79</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>Tanker charters out — the twelve fixtures as disclosed, each at its own rate for exactly the days its own contract runs</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>Rate (USD per day)</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <t>Contract begins</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Contract ends</t>
         </is>
       </c>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="16" t="n"/>
-      <c r="H65" s="16" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Navig8 Macallister — long range 1, fixed for 18 months</t>
-        </is>
-      </c>
-      <c r="B66" s="29" t="n">
-        <v>19750</v>
-      </c>
-      <c r="C66" s="35" t="n">
-        <v>45928</v>
-      </c>
-      <c r="D66" s="35" t="n">
-        <v>46474</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Navig8 Martinez — long range 1, fixed for 32 months</t>
-        </is>
-      </c>
-      <c r="B67" s="29" t="n">
-        <v>19750</v>
-      </c>
-      <c r="C67" s="35" t="n">
-        <v>45989</v>
-      </c>
-      <c r="D67" s="35" t="n">
-        <v>46962</v>
-      </c>
+      <c r="E67" s="16" t="n"/>
+      <c r="F67" s="16" t="n"/>
+      <c r="G67" s="16" t="n"/>
+      <c r="H67" s="16" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Prosperity — long range 2, fixed for 36 months</t>
+          <t>Navig8 Macallister — long range 1, fixed for 18 months</t>
         </is>
       </c>
       <c r="B68" s="29" t="n">
-        <v>30561</v>
+        <v>19750</v>
       </c>
       <c r="C68" s="35" t="n">
-        <v>45050</v>
+        <v>45928</v>
       </c>
       <c r="D68" s="35" t="n">
-        <v>46146</v>
+        <v>46474</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Promise — long range 2, fixed for 12 months</t>
+          <t>Navig8 Martinez — long range 1, fixed for 32 months</t>
         </is>
       </c>
       <c r="B69" s="29" t="n">
-        <v>32125</v>
+        <v>19750</v>
       </c>
       <c r="C69" s="35" t="n">
-        <v>45896</v>
+        <v>45989</v>
       </c>
       <c r="D69" s="35" t="n">
-        <v>46261</v>
+        <v>46962</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Pride — long range 2, fixed for 12 months</t>
+          <t>Navig8 Prosperity — long range 2, fixed for 36 months</t>
         </is>
       </c>
       <c r="B70" s="29" t="n">
-        <v>32125</v>
+        <v>30561</v>
       </c>
       <c r="C70" s="35" t="n">
-        <v>45937</v>
+        <v>45050</v>
       </c>
       <c r="D70" s="35" t="n">
-        <v>46302</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Prestige — long range 2, fixed for 12 months</t>
+          <t>Navig8 Promise — long range 2, fixed for 12 months</t>
         </is>
       </c>
       <c r="B71" s="29" t="n">
-        <v>36850</v>
+        <v>32125</v>
       </c>
       <c r="C71" s="35" t="n">
-        <v>45998</v>
+        <v>45896</v>
       </c>
       <c r="D71" s="35" t="n">
-        <v>46363</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Providence — long range 2, fixed for 12 months</t>
+          <t>Navig8 Pride — long range 2, fixed for 12 months</t>
         </is>
       </c>
       <c r="B72" s="29" t="n">
-        <v>42000</v>
+        <v>32125</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>46130</v>
+        <v>45937</v>
       </c>
       <c r="D72" s="35" t="n">
-        <v>46495</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>Navig8 Passion — long range 2, fixed for 12 months</t>
+          <t>Navig8 Prestige — long range 2, fixed for 12 months</t>
         </is>
       </c>
       <c r="B73" s="29" t="n">
-        <v>42000</v>
+        <v>36850</v>
       </c>
       <c r="C73" s="35" t="n">
-        <v>46193</v>
+        <v>45998</v>
       </c>
       <c r="D73" s="35" t="n">
-        <v>46558</v>
+        <v>46363</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>Zakum — very large crude carrier, fixed for 22 months</t>
+          <t>Navig8 Providence — long range 2, fixed for 12 months</t>
         </is>
       </c>
       <c r="B74" s="29" t="n">
-        <v>50633</v>
+        <v>42000</v>
       </c>
       <c r="C74" s="35" t="n">
-        <v>46083</v>
+        <v>46130</v>
       </c>
       <c r="D74" s="35" t="n">
-        <v>46754</v>
+        <v>46495</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Hili — very large crude carrier, fixed for 22 months</t>
+          <t>Navig8 Passion — long range 2, fixed for 12 months</t>
         </is>
       </c>
       <c r="B75" s="29" t="n">
-        <v>50633</v>
+        <v>42000</v>
       </c>
       <c r="C75" s="35" t="n">
-        <v>46097</v>
+        <v>46193</v>
       </c>
       <c r="D75" s="35" t="n">
-        <v>46768</v>
+        <v>46558</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>Arzanah — very large crude carrier, fixed for 12 months</t>
+          <t>Zakum — very large crude carrier, fixed for 22 months</t>
         </is>
       </c>
       <c r="B76" s="29" t="n">
-        <v>70000</v>
+        <v>50633</v>
       </c>
       <c r="C76" s="35" t="n">
-        <v>46132</v>
+        <v>46083</v>
       </c>
       <c r="D76" s="35" t="n">
-        <v>46497</v>
+        <v>46754</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
+          <t>Hili — very large crude carrier, fixed for 22 months</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="n">
+        <v>50633</v>
+      </c>
+      <c r="C77" s="35" t="n">
+        <v>46097</v>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>46768</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Arzanah — very large crude carrier, fixed for 12 months</t>
+        </is>
+      </c>
+      <c r="B78" s="29" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C78" s="35" t="n">
+        <v>46132</v>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>46497</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
           <t>Habshan — very large crude carrier, fixed for 12 months</t>
         </is>
       </c>
-      <c r="B77" s="29" t="n">
+      <c r="B79" s="29" t="n">
         <v>72500</v>
       </c>
-      <c r="C77" s="35" t="n">
+      <c r="C79" s="35" t="n">
         <v>46163</v>
       </c>
-      <c r="D77" s="35" t="n">
+      <c r="D79" s="35" t="n">
         <v>46528</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>Rate windows and forecast years — the calendar the fleet build runs on (dates)</t>
         </is>
       </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>Q1 2025</t>
         </is>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>Q2 2025</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Q3 2025</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E81" s="16" t="inlineStr">
         <is>
           <t>Q4 2025</t>
         </is>
       </c>
-      <c r="F79" s="16" t="inlineStr">
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>Q1 2026</t>
         </is>
       </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="G81" s="16" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="H79" s="16" t="inlineStr">
+      <c r="H81" s="16" t="inlineStr">
         <is>
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="I79" s="16" t="inlineStr">
+      <c r="I81" s="16" t="inlineStr">
         <is>
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="J79" s="16" t="inlineStr">
+      <c r="J81" s="16" t="inlineStr">
         <is>
           <t>Mid-cycle anchor</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>Rate window begins</t>
         </is>
       </c>
-      <c r="B80" s="35" t="n">
+      <c r="B82" s="35" t="n">
         <v>45658</v>
       </c>
-      <c r="C80" s="35" t="n">
+      <c r="C82" s="35" t="n">
         <v>45748</v>
       </c>
-      <c r="D80" s="35" t="n">
+      <c r="D82" s="35" t="n">
         <v>45839</v>
       </c>
-      <c r="E80" s="35" t="n">
+      <c r="E82" s="35" t="n">
         <v>45931</v>
       </c>
-      <c r="F80" s="35" t="n">
+      <c r="F82" s="35" t="n">
         <v>46023</v>
       </c>
-      <c r="G80" s="35" t="n">
+      <c r="G82" s="35" t="n">
         <v>46113</v>
       </c>
-      <c r="H80" s="35" t="n">
+      <c r="H82" s="35" t="n">
         <v>46204</v>
       </c>
-      <c r="I80" s="35" t="n">
+      <c r="I82" s="35" t="n">
         <v>46296</v>
       </c>
-      <c r="J80" s="35" t="n">
+      <c r="J82" s="35" t="n">
         <v>45658</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Rate window ends — each window closes where the next one opens; the last is the disclosed quarter end</t>
         </is>
       </c>
-      <c r="B81" s="36">
-        <f>C80</f>
-        <v/>
-      </c>
-      <c r="C81" s="36">
-        <f>D80</f>
-        <v/>
-      </c>
-      <c r="D81" s="36">
-        <f>E80</f>
-        <v/>
-      </c>
-      <c r="E81" s="36">
-        <f>F80</f>
-        <v/>
-      </c>
-      <c r="F81" s="36">
-        <f>G80</f>
-        <v/>
-      </c>
-      <c r="G81" s="36">
-        <f>H80</f>
-        <v/>
-      </c>
-      <c r="H81" s="36">
-        <f>I80</f>
-        <v/>
-      </c>
-      <c r="I81" s="35" t="n">
+      <c r="B83" s="36">
+        <f>C82</f>
+        <v/>
+      </c>
+      <c r="C83" s="36">
+        <f>D82</f>
+        <v/>
+      </c>
+      <c r="D83" s="36">
+        <f>E82</f>
+        <v/>
+      </c>
+      <c r="E83" s="36">
+        <f>F82</f>
+        <v/>
+      </c>
+      <c r="F83" s="36">
+        <f>G82</f>
+        <v/>
+      </c>
+      <c r="G83" s="36">
+        <f>H82</f>
+        <v/>
+      </c>
+      <c r="H83" s="36">
+        <f>I82</f>
+        <v/>
+      </c>
+      <c r="I83" s="35" t="n">
         <v>46388</v>
       </c>
-      <c r="J81" s="35" t="n">
+      <c r="J83" s="35" t="n">
         <v>45748</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>Forecast years (dates)</t>
         </is>
       </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D85" s="16" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F83" s="16" t="inlineStr">
+      <c r="F85" s="16" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G83" s="16" t="n"/>
-      <c r="H83" s="16" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+      <c r="G85" s="16" t="n"/>
+      <c r="H85" s="16" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Forecast year begins</t>
         </is>
       </c>
-      <c r="B84" s="36">
-        <f>H80</f>
-        <v/>
-      </c>
-      <c r="C84" s="35" t="n">
+      <c r="B86" s="36">
+        <f>H82</f>
+        <v/>
+      </c>
+      <c r="C86" s="35" t="n">
         <v>46388</v>
       </c>
-      <c r="D84" s="35" t="n">
+      <c r="D86" s="35" t="n">
         <v>46753</v>
       </c>
-      <c r="E84" s="35" t="n">
+      <c r="E86" s="35" t="n">
         <v>47119</v>
       </c>
-      <c r="F84" s="35" t="n">
+      <c r="F86" s="35" t="n">
         <v>47484</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>Forecast year ends — each year closes where the next one opens</t>
         </is>
       </c>
-      <c r="B85" s="36">
-        <f>C84</f>
-        <v/>
-      </c>
-      <c r="C85" s="36">
-        <f>D84</f>
-        <v/>
-      </c>
-      <c r="D85" s="36">
-        <f>E84</f>
-        <v/>
-      </c>
-      <c r="E85" s="36">
-        <f>F84</f>
-        <v/>
-      </c>
-      <c r="F85" s="35" t="n">
+      <c r="B87" s="36">
+        <f>C86</f>
+        <v/>
+      </c>
+      <c r="C87" s="36">
+        <f>D86</f>
+        <v/>
+      </c>
+      <c r="D87" s="36">
+        <f>E86</f>
+        <v/>
+      </c>
+      <c r="E87" s="36">
+        <f>F86</f>
+        <v/>
+      </c>
+      <c r="F87" s="35" t="n">
         <v>47849</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
         <is>
           <t>THE FLEET PURCHASE ANNOUNCED 7 AUGUST 2026 — eleven vessels for about USD 1.3 billion, announced on the anchor date of this study and therefore already inside the market price the valuation is compared against</t>
         </is>
       </c>
-      <c r="B87" s="16" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>Vessels</t>
         </is>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C89" s="16" t="inlineStr">
         <is>
           <t>Delivery date</t>
         </is>
       </c>
-      <c r="D87" s="16" t="n"/>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
-      <c r="G87" s="16" t="n"/>
-      <c r="H87" s="16" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Purchase price — added BOTH to net debt, because it is committed and funded, and to the opening asset base, so it depreciates and shields tax (USD 000)</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="n">
-        <v>1300000</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>Very large crude carriers bought secondhand — they join the spot fleet on delivery and earn at the implied spot rate from that date</t>
-        </is>
-      </c>
-      <c r="B89" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C89" s="35" t="n">
-        <v>46266</v>
-      </c>
+      <c r="D89" s="16" t="n"/>
+      <c r="E89" s="16" t="n"/>
+      <c r="F89" s="16" t="n"/>
+      <c r="G89" s="16" t="n"/>
+      <c r="H89" s="16" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>Gas carriers acquired in total — they add contracted vessel-years to the gas fleet</t>
-        </is>
-      </c>
-      <c r="B90" s="29" t="n">
-        <v>5</v>
+          <t>Purchase price — added BOTH to net debt, because it is committed and funded, and to the opening asset base, so it depreciates and shields tax (USD 000)</t>
+        </is>
+      </c>
+      <c r="C90" s="29" t="n">
+        <v>1300000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>Of which bought secondhand, delivering in the third quarter</t>
+          <t>Very large crude carriers bought secondhand — they join the spot fleet on delivery and earn at the implied spot rate from that date</t>
         </is>
       </c>
       <c r="B91" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C91" s="35" t="n">
         <v>46266</v>
@@ -9812,113 +9809,116 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t>Gas carriers acquired in total — they add contracted vessel-years to the gas fleet</t>
+        </is>
+      </c>
+      <c r="B92" s="29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Of which bought secondhand, delivering in the third quarter</t>
+        </is>
+      </c>
+      <c r="B93" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="35" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>Of which newbuildings resold from the yard, delivering in the fourth quarter</t>
         </is>
       </c>
-      <c r="B92" s="33">
-        <f>B90-B91</f>
-        <v/>
-      </c>
-      <c r="C92" s="35" t="n">
+      <c r="B94" s="33">
+        <f>B92-B93</f>
+        <v/>
+      </c>
+      <c r="C94" s="35" t="n">
         <v>46341</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="37" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="37" t="inlineStr">
         <is>
           <t>Vessels acquired in total</t>
         </is>
       </c>
-      <c r="B93" s="38">
-        <f>B89+B90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="11" t="inlineStr">
+      <c r="B95" s="38">
+        <f>B91+B92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
         <is>
           <t>Tanker fleet — rate path and cost stack</t>
         </is>
       </c>
-      <c r="B95" s="16" t="n"/>
-      <c r="C95" s="16" t="n"/>
-      <c r="D95" s="16" t="n"/>
-      <c r="E95" s="16" t="n"/>
-      <c r="F95" s="16" t="n"/>
-      <c r="G95" s="16" t="n"/>
-      <c r="H95" s="16" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Weight on the mid-cycle rate against the disclosed third-quarter 2026 rate, in setting the fourth quarter of 2026</t>
-        </is>
-      </c>
-      <c r="C96" s="32" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Tanker cost stack — fixed base a year before escalation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C97" s="20">
-        <f>Segments!B144</f>
-        <v/>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>GREEN, NOT BLUE. The fixed cost base is not an assumption: it is solved on the Segments sheet so that the same construction reproduces the tanker earnings the company actually reported for 2025. The same is true of the gas-carrier day rate, the three days ratios and the opening net working capital immediately below.</t>
-        </is>
-      </c>
+      <c r="B97" s="16" t="n"/>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="n"/>
+      <c r="E97" s="16" t="n"/>
+      <c r="F97" s="16" t="n"/>
+      <c r="G97" s="16" t="n"/>
+      <c r="H97" s="16" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>Tanker cost stack — variable cost per unit of charter-equivalent revenue</t>
-        </is>
-      </c>
-      <c r="C98" s="39">
-        <f>Assumptions!$C$104-Segments!B143</f>
-        <v/>
+          <t>Weight on the mid-cycle rate against the disclosed third-quarter 2026 rate, in setting the fourth quarter of 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>House inflation ladder, FY2026</t>
-        </is>
-      </c>
-      <c r="C99" s="32" t="n">
-        <v>0.025</v>
+          <t>Tanker cost stack — fixed base a year before escalation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C99" s="20">
+        <f>Segments!B144</f>
+        <v/>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>GREEN, NOT BLUE. The fixed cost base is not an assumption: it is solved on the Segments sheet so that the same construction reproduces the tanker earnings the company actually reported for 2025. The same is true of the gas-carrier day rate, the three days ratios and the opening net working capital immediately below.</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>House inflation ladder, FY2027</t>
-        </is>
-      </c>
-      <c r="C100" s="32" t="n">
-        <v>0.02</v>
+          <t>Tanker cost stack — variable cost per unit of charter-equivalent revenue</t>
+        </is>
+      </c>
+      <c r="C100" s="39">
+        <f>Assumptions!$C$106-Segments!B143</f>
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>House inflation ladder, FY2028</t>
+          <t>House inflation ladder, FY2026</t>
         </is>
       </c>
       <c r="C101" s="32" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>House inflation ladder, FY2029</t>
+          <t>House inflation ladder, FY2027</t>
         </is>
       </c>
       <c r="C102" s="32" t="n">
@@ -9928,7 +9928,7 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>House inflation ladder, FY2030</t>
+          <t>House inflation ladder, FY2028</t>
         </is>
       </c>
       <c r="C103" s="32" t="n">
@@ -9938,1194 +9938,1214 @@
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>House inflation ladder, FY2029</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>House inflation ladder, FY2030</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
           <t>Gross-up from time-charter-equivalent revenue to reported revenue</t>
         </is>
       </c>
-      <c r="C104" s="28" t="n">
+      <c r="C106" s="28" t="n">
         <v>2.608567993323544</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>The reviewed first half of 2026, as reported — the anchor every unit is built from</t>
         </is>
       </c>
-      <c r="B106" s="16" t="n"/>
-      <c r="C106" s="16" t="n"/>
-      <c r="D106" s="16" t="n"/>
-      <c r="E106" s="16" t="n"/>
-      <c r="F106" s="16" t="n"/>
-      <c r="G106" s="16" t="n"/>
-      <c r="H106" s="16" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Contracting — revenue, six months to 30 June 2026 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C107" s="29" t="n">
-        <v>667002</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Services — revenue, six months to 30 June 2026 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C108" s="29" t="n">
-        <v>371157</v>
-      </c>
+      <c r="B108" s="16" t="n"/>
+      <c r="C108" s="16" t="n"/>
+      <c r="D108" s="16" t="n"/>
+      <c r="E108" s="16" t="n"/>
+      <c r="F108" s="16" t="n"/>
+      <c r="G108" s="16" t="n"/>
+      <c r="H108" s="16" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — revenue, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Contracting — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C109" s="29" t="n">
-        <v>1884</v>
+        <v>667002</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>Tankers — revenue, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Services — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C110" s="29" t="n">
-        <v>2102006</v>
+        <v>371157</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>Gas Carriers — revenue, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Projects — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C111" s="29" t="n">
-        <v>186656</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — revenue, six months to 30 June 2026 (USD 000)</t>
+          <t>Tankers — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C112" s="29" t="n">
-        <v>149038</v>
+        <v>2102006</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>Services — revenue, six months to 30 June 2026 (USD 000)</t>
+          <t>Gas Carriers — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C113" s="29" t="n">
-        <v>188931</v>
+        <v>186656</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Dry-Bulk and Containers — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C114" s="29" t="n">
-        <v>210970</v>
+        <v>149038</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Services — revenue, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C115" s="29" t="n">
-        <v>89262</v>
+        <v>188931</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Contracting — EBITDA, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C116" s="29" t="n">
-        <v>-16959</v>
+        <v>210970</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>Tankers — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Services — EBITDA, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C117" s="29" t="n">
-        <v>994166</v>
+        <v>89262</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>Gas Carriers — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Offshore Projects — EBITDA, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C118" s="29" t="n">
-        <v>92694</v>
+        <v>-16959</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — EBITDA, six months to 30 June 2026 (USD 000)</t>
+          <t>Tankers — EBITDA, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C119" s="29" t="n">
-        <v>52852</v>
+        <v>994166</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
+          <t>Gas Carriers — EBITDA, six months to 30 June 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C120" s="29" t="n">
+        <v>92694</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — EBITDA, six months to 30 June 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C121" s="29" t="n">
+        <v>52852</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
           <t>Services — EBITDA, six months to 30 June 2026 (USD 000)</t>
         </is>
       </c>
-      <c r="C120" s="29" t="n">
+      <c r="C122" s="29" t="n">
         <v>52035</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>Gas carriers</t>
         </is>
       </c>
-      <c r="B122" s="16" t="n"/>
-      <c r="C122" s="16" t="n"/>
-      <c r="D122" s="16" t="n"/>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="n"/>
-      <c r="G122" s="16" t="n"/>
-      <c r="H122" s="16" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Consolidated gas vessels in service through 2025 (vessel-years)</t>
-        </is>
-      </c>
-      <c r="C123" s="26" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Consolidated gas vessels in service through the first half of 2026 (vessel-years)</t>
-        </is>
-      </c>
-      <c r="C124" s="26" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="B124" s="16" t="n"/>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="16" t="n"/>
+      <c r="G124" s="16" t="n"/>
+      <c r="H124" s="16" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
-        </is>
-      </c>
-      <c r="C125" s="20">
-        <f>Segments!B155</f>
-        <v/>
+          <t>Consolidated gas vessels in service through 2025 (vessel-years)</t>
+        </is>
+      </c>
+      <c r="C125" s="26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>Gas carriers — earnings margin</t>
-        </is>
-      </c>
-      <c r="C126" s="32" t="n">
-        <v>0.4966</v>
+          <t>Consolidated gas vessels in service through the first half of 2026 (vessel-years)</t>
+        </is>
+      </c>
+      <c r="C126" s="26" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>Share of joint-venture profit carried in the disclosed 2025 Gas Carriers earnings (USD 000)</t>
-        </is>
-      </c>
-      <c r="C127" s="29" t="n">
-        <v>24880</v>
+          <t>Gas carriers — implied revenue per vessel-day (USD)</t>
+        </is>
+      </c>
+      <c r="C127" s="20">
+        <f>Segments!B155</f>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
+          <t>Gas carriers — earnings margin</t>
+        </is>
+      </c>
+      <c r="C128" s="32" t="n">
+        <v>0.4966</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Share of joint-venture profit carried in the disclosed 2025 Gas Carriers earnings (USD 000)</t>
+        </is>
+      </c>
+      <c r="C129" s="29" t="n">
+        <v>24880</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
           <t>Share of joint-venture profit carried in the disclosed 2025 Services earnings (USD 000)</t>
         </is>
       </c>
-      <c r="C128" s="29" t="n">
+      <c r="C130" s="29" t="n">
         <v>52160</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="11" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>Gas-carrier contract table — the vessel-years the fleet is contracted for, before and after the August 2026 purchase</t>
         </is>
       </c>
-      <c r="B130" s="16" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C130" s="16" t="inlineStr">
+      <c r="C132" s="16" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E130" s="16" t="inlineStr">
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
+      <c r="F132" s="16" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G130" s="16" t="n"/>
-      <c r="H130" s="16" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Contracted vessel-years before that purchase — the disclosed contract table</t>
-        </is>
-      </c>
-      <c r="B131" s="26" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="C131" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="D131" s="26" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="E131" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="F131" s="26" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Vessel-years the gas carriers bought in August 2026 add — each tranche from its own delivery date</t>
-        </is>
-      </c>
-      <c r="B132" s="40">
-        <f>(Assumptions!$B$91*MAX(Assumptions!$B$85-MAX(Assumptions!$B$84,Assumptions!$C$91),0)+Assumptions!$B$92*MAX(Assumptions!$B$85-MAX(Assumptions!$B$84,Assumptions!$C$92),0))/(Assumptions!$B$85-Assumptions!$B$84)</f>
-        <v/>
-      </c>
-      <c r="C132" s="40">
-        <f>(Assumptions!$B$91*MAX(Assumptions!$C$85-MAX(Assumptions!$C$84,Assumptions!$C$91),0)+Assumptions!$B$92*MAX(Assumptions!$C$85-MAX(Assumptions!$C$84,Assumptions!$C$92),0))/(Assumptions!$C$85-Assumptions!$C$84)</f>
-        <v/>
-      </c>
-      <c r="D132" s="40">
-        <f>(Assumptions!$B$91*MAX(Assumptions!$D$85-MAX(Assumptions!$D$84,Assumptions!$C$91),0)+Assumptions!$B$92*MAX(Assumptions!$D$85-MAX(Assumptions!$D$84,Assumptions!$C$92),0))/(Assumptions!$D$85-Assumptions!$D$84)</f>
-        <v/>
-      </c>
-      <c r="E132" s="40">
-        <f>(Assumptions!$B$91*MAX(Assumptions!$E$85-MAX(Assumptions!$E$84,Assumptions!$C$91),0)+Assumptions!$B$92*MAX(Assumptions!$E$85-MAX(Assumptions!$E$84,Assumptions!$C$92),0))/(Assumptions!$E$85-Assumptions!$E$84)</f>
-        <v/>
-      </c>
-      <c r="F132" s="40">
-        <f>(Assumptions!$B$91*MAX(Assumptions!$F$85-MAX(Assumptions!$F$84,Assumptions!$C$91),0)+Assumptions!$B$92*MAX(Assumptions!$F$85-MAX(Assumptions!$F$84,Assumptions!$C$92),0))/(Assumptions!$F$85-Assumptions!$F$84)</f>
-        <v/>
-      </c>
+      <c r="G132" s="16" t="n"/>
+      <c r="H132" s="16" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
+          <t>Contracted vessel-years before that purchase — the disclosed contract table</t>
+        </is>
+      </c>
+      <c r="B133" s="26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C133" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D133" s="26" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="E133" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" s="26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Vessel-years the gas carriers bought in August 2026 add — each tranche from its own delivery date</t>
+        </is>
+      </c>
+      <c r="B134" s="40">
+        <f>(Assumptions!$B$93*MAX(Assumptions!$B$87-MAX(Assumptions!$B$86,Assumptions!$C$93),0)+Assumptions!$B$94*MAX(Assumptions!$B$87-MAX(Assumptions!$B$86,Assumptions!$C$94),0))/(Assumptions!$B$87-Assumptions!$B$86)</f>
+        <v/>
+      </c>
+      <c r="C134" s="40">
+        <f>(Assumptions!$B$93*MAX(Assumptions!$C$87-MAX(Assumptions!$C$86,Assumptions!$C$93),0)+Assumptions!$B$94*MAX(Assumptions!$C$87-MAX(Assumptions!$C$86,Assumptions!$C$94),0))/(Assumptions!$C$87-Assumptions!$C$86)</f>
+        <v/>
+      </c>
+      <c r="D134" s="40">
+        <f>(Assumptions!$B$93*MAX(Assumptions!$D$87-MAX(Assumptions!$D$86,Assumptions!$C$93),0)+Assumptions!$B$94*MAX(Assumptions!$D$87-MAX(Assumptions!$D$86,Assumptions!$C$94),0))/(Assumptions!$D$87-Assumptions!$D$86)</f>
+        <v/>
+      </c>
+      <c r="E134" s="40">
+        <f>(Assumptions!$B$93*MAX(Assumptions!$E$87-MAX(Assumptions!$E$86,Assumptions!$C$93),0)+Assumptions!$B$94*MAX(Assumptions!$E$87-MAX(Assumptions!$E$86,Assumptions!$C$94),0))/(Assumptions!$E$87-Assumptions!$E$86)</f>
+        <v/>
+      </c>
+      <c r="F134" s="40">
+        <f>(Assumptions!$B$93*MAX(Assumptions!$F$87-MAX(Assumptions!$F$86,Assumptions!$C$93),0)+Assumptions!$B$94*MAX(Assumptions!$F$87-MAX(Assumptions!$F$86,Assumptions!$C$94),0))/(Assumptions!$F$87-Assumptions!$F$86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
           <t>Gas carriers — contracted vessel-years</t>
         </is>
       </c>
-      <c r="B133" s="41">
-        <f>B131+B132</f>
-        <v/>
-      </c>
-      <c r="C133" s="41">
-        <f>C131+C132</f>
-        <v/>
-      </c>
-      <c r="D133" s="41">
-        <f>D131+D132</f>
-        <v/>
-      </c>
-      <c r="E133" s="41">
-        <f>E131+E132</f>
-        <v/>
-      </c>
-      <c r="F133" s="41">
-        <f>F131+F132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="11" t="inlineStr">
+      <c r="B135" s="41">
+        <f>B133+B134</f>
+        <v/>
+      </c>
+      <c r="C135" s="41">
+        <f>C133+C134</f>
+        <v/>
+      </c>
+      <c r="D135" s="41">
+        <f>D133+D134</f>
+        <v/>
+      </c>
+      <c r="E135" s="41">
+        <f>E133+E134</f>
+        <v/>
+      </c>
+      <c r="F135" s="41">
+        <f>F133+F134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
         <is>
           <t>The remaining five units — revenue and margin drivers</t>
         </is>
       </c>
-      <c r="B135" s="16" t="inlineStr">
+      <c r="B137" s="16" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr">
+      <c r="C137" s="16" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D135" s="16" t="inlineStr">
+      <c r="D137" s="16" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E135" s="16" t="inlineStr">
+      <c r="E137" s="16" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F135" s="16" t="inlineStr">
+      <c r="F137" s="16" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G135" s="16" t="n"/>
-      <c r="H135" s="16" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Contracting — revenue (USD 000)</t>
-        </is>
-      </c>
-      <c r="B136" s="29" t="n">
-        <v>1334004</v>
-      </c>
-      <c r="C136" s="29" t="n">
-        <v>1387364.16</v>
-      </c>
-      <c r="D136" s="29" t="n">
-        <v>1442858.7264</v>
-      </c>
-      <c r="E136" s="29" t="n">
-        <v>1500573.075456</v>
-      </c>
-      <c r="F136" s="29" t="n">
-        <v>1560595.99847424</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>Offshore Contracting — earnings margin</t>
-        </is>
-      </c>
-      <c r="B137" s="32" t="n">
-        <v>0.3875565590507974</v>
-      </c>
-      <c r="C137" s="32" t="n">
-        <v>0.3875565590507974</v>
-      </c>
-      <c r="D137" s="32" t="n">
-        <v>0.3875565590507974</v>
-      </c>
-      <c r="E137" s="32" t="n">
-        <v>0.3875565590507974</v>
-      </c>
-      <c r="F137" s="32" t="n">
-        <v>0.3875565590507974</v>
-      </c>
+      <c r="G137" s="16" t="n"/>
+      <c r="H137" s="16" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — revenue (USD 000)</t>
+          <t>Offshore Contracting — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B138" s="29" t="n">
-        <v>742314</v>
+        <v>1334004</v>
       </c>
       <c r="C138" s="29" t="n">
-        <v>779429.7000000001</v>
+        <v>1387364.16</v>
       </c>
       <c r="D138" s="29" t="n">
-        <v>818401.1850000001</v>
+        <v>1442858.7264</v>
       </c>
       <c r="E138" s="29" t="n">
-        <v>859321.2442500001</v>
+        <v>1500573.075456</v>
       </c>
       <c r="F138" s="29" t="n">
-        <v>902287.3064625001</v>
+        <v>1560595.99847424</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — earnings margin</t>
+          <t>Offshore Contracting — earnings margin</t>
         </is>
       </c>
       <c r="B139" s="32" t="n">
-        <v>0.2404966092516105</v>
+        <v>0.3875565590507974</v>
       </c>
       <c r="C139" s="32" t="n">
-        <v>0.2404966092516105</v>
+        <v>0.3875565590507974</v>
       </c>
       <c r="D139" s="32" t="n">
-        <v>0.2404966092516105</v>
+        <v>0.3875565590507974</v>
       </c>
       <c r="E139" s="32" t="n">
-        <v>0.2404966092516105</v>
+        <v>0.3875565590507974</v>
       </c>
       <c r="F139" s="32" t="n">
-        <v>0.2404966092516105</v>
+        <v>0.3875565590507974</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — revenue (USD 000)</t>
+          <t>Offshore Services — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B140" s="29" t="n">
-        <v>3768</v>
+        <v>742314</v>
       </c>
       <c r="C140" s="29" t="n">
-        <v>3768</v>
+        <v>779429.7000000001</v>
       </c>
       <c r="D140" s="29" t="n">
-        <v>3768</v>
+        <v>818401.1850000001</v>
       </c>
       <c r="E140" s="29" t="n">
-        <v>3768</v>
+        <v>859321.2442500001</v>
       </c>
       <c r="F140" s="29" t="n">
-        <v>3768</v>
+        <v>902287.3064625001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — earnings margin</t>
+          <t>Offshore Services — earnings margin</t>
         </is>
       </c>
       <c r="B141" s="32" t="n">
-        <v>0</v>
+        <v>0.2404966092516105</v>
       </c>
       <c r="C141" s="32" t="n">
-        <v>0</v>
+        <v>0.2404966092516105</v>
       </c>
       <c r="D141" s="32" t="n">
-        <v>0</v>
+        <v>0.2404966092516105</v>
       </c>
       <c r="E141" s="32" t="n">
-        <v>0</v>
+        <v>0.2404966092516105</v>
       </c>
       <c r="F141" s="32" t="n">
-        <v>0</v>
+        <v>0.2404966092516105</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
+          <t>Offshore Projects — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B142" s="29" t="n">
-        <v>298076</v>
+        <v>3768</v>
       </c>
       <c r="C142" s="29" t="n">
-        <v>279819</v>
+        <v>3768</v>
       </c>
       <c r="D142" s="29" t="n">
-        <v>261562</v>
+        <v>3768</v>
       </c>
       <c r="E142" s="29" t="n">
-        <v>243305</v>
+        <v>3768</v>
       </c>
       <c r="F142" s="29" t="n">
-        <v>225048</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — earnings margin</t>
+          <t>Offshore Projects — earnings margin</t>
         </is>
       </c>
       <c r="B143" s="32" t="n">
-        <v>0.3546209691488077</v>
+        <v>0</v>
       </c>
       <c r="C143" s="32" t="n">
-        <v>0.3080256429683919</v>
+        <v>0</v>
       </c>
       <c r="D143" s="32" t="n">
-        <v>0.2614303167879761</v>
+        <v>0</v>
       </c>
       <c r="E143" s="32" t="n">
-        <v>0.2148349906075603</v>
+        <v>0</v>
       </c>
       <c r="F143" s="32" t="n">
-        <v>0.1682396644271444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>Services — revenue (USD 000)</t>
+          <t>Dry-Bulk and Containers — revenue (USD 000)</t>
         </is>
       </c>
       <c r="B144" s="29" t="n">
-        <v>377862</v>
+        <v>298076</v>
       </c>
       <c r="C144" s="29" t="n">
-        <v>392976.48</v>
+        <v>279819</v>
       </c>
       <c r="D144" s="29" t="n">
-        <v>408695.5392000001</v>
+        <v>261562</v>
       </c>
       <c r="E144" s="29" t="n">
-        <v>425043.360768</v>
+        <v>243305</v>
       </c>
       <c r="F144" s="29" t="n">
-        <v>442045.0951987201</v>
+        <v>225048</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
+          <t>Dry-Bulk and Containers — earnings margin</t>
+        </is>
+      </c>
+      <c r="B145" s="32" t="n">
+        <v>0.3546209691488077</v>
+      </c>
+      <c r="C145" s="32" t="n">
+        <v>0.3080256429683919</v>
+      </c>
+      <c r="D145" s="32" t="n">
+        <v>0.2614303167879761</v>
+      </c>
+      <c r="E145" s="32" t="n">
+        <v>0.2148349906075603</v>
+      </c>
+      <c r="F145" s="32" t="n">
+        <v>0.1682396644271444</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>Services — revenue (USD 000)</t>
+        </is>
+      </c>
+      <c r="B146" s="29" t="n">
+        <v>377862</v>
+      </c>
+      <c r="C146" s="29" t="n">
+        <v>392976.48</v>
+      </c>
+      <c r="D146" s="29" t="n">
+        <v>408695.5392000001</v>
+      </c>
+      <c r="E146" s="29" t="n">
+        <v>425043.360768</v>
+      </c>
+      <c r="F146" s="29" t="n">
+        <v>442045.0951987201</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
           <t>Services — earnings margin</t>
         </is>
       </c>
-      <c r="B145" s="32" t="n">
+      <c r="B147" s="32" t="n">
         <v>0.2754180097495911</v>
       </c>
-      <c r="C145" s="32" t="n">
+      <c r="C147" s="32" t="n">
         <v>0.2754180097495911</v>
       </c>
-      <c r="D145" s="32" t="n">
+      <c r="D147" s="32" t="n">
         <v>0.2754180097495911</v>
       </c>
-      <c r="E145" s="32" t="n">
+      <c r="E147" s="32" t="n">
         <v>0.2754180097495911</v>
       </c>
-      <c r="F145" s="32" t="n">
+      <c r="F147" s="32" t="n">
         <v>0.2754180097495911</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="11" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="11" t="inlineStr">
         <is>
           <t>Capital expenditure, depreciation and working capital</t>
         </is>
       </c>
-      <c r="B147" s="16" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="C147" s="16" t="inlineStr">
+      <c r="C149" s="16" t="inlineStr">
         <is>
           <t>FY2027</t>
         </is>
       </c>
-      <c r="D147" s="16" t="inlineStr">
+      <c r="D149" s="16" t="inlineStr">
         <is>
           <t>FY2028</t>
         </is>
       </c>
-      <c r="E147" s="16" t="inlineStr">
+      <c r="E149" s="16" t="inlineStr">
         <is>
           <t>FY2029</t>
         </is>
       </c>
-      <c r="F147" s="16" t="inlineStr">
+      <c r="F149" s="16" t="inlineStr">
         <is>
           <t>FY2030</t>
         </is>
       </c>
-      <c r="G147" s="16" t="n"/>
-      <c r="H147" s="16" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>Capital expenditure (USD 000)</t>
-        </is>
-      </c>
-      <c r="B148" s="29" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="C148" s="29" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="D148" s="29" t="n">
-        <v>1245000</v>
-      </c>
-      <c r="E148" s="29" t="n">
-        <v>700000</v>
-      </c>
-      <c r="F148" s="29" t="n">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation rate on property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="C149" s="30" t="n">
-        <v>0.0591</v>
-      </c>
+      <c r="G149" s="16" t="n"/>
+      <c r="H149" s="16" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
-        </is>
+          <t>Capital expenditure (USD 000)</t>
+        </is>
+      </c>
+      <c r="B150" s="29" t="n">
+        <v>1375000</v>
       </c>
       <c r="C150" s="29" t="n">
-        <v>112962</v>
+        <v>1245000</v>
+      </c>
+      <c r="D150" s="29" t="n">
+        <v>1245000</v>
+      </c>
+      <c r="E150" s="29" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F150" s="29" t="n">
+        <v>650000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>Days sales outstanding measured on REPORTED 2025 revenue</t>
-        </is>
-      </c>
-      <c r="C151" s="19">
-        <f>'Balance Sheet'!D12/'Income Statement'!D5*365</f>
-        <v/>
+          <t>Depreciation rate on property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="C151" s="30" t="n">
+        <v>0.0591</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>Gross-up inside 2025 reported revenue — reported tanker revenue over the same fleet's charter-equivalent revenue</t>
-        </is>
-      </c>
-      <c r="C152" s="42">
-        <f>Segments!D8/Segments!B139</f>
-        <v/>
+          <t>Other depreciation and amortisation, 2026 run rate (USD 000)</t>
+        </is>
+      </c>
+      <c r="C152" s="29" t="n">
+        <v>112962</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>Gross-up the forecast is built at, from 2026 onward</t>
-        </is>
-      </c>
-      <c r="C153" s="42">
-        <f>Assumptions!$C$104</f>
+          <t>Days sales outstanding measured on REPORTED 2025 revenue</t>
+        </is>
+      </c>
+      <c r="C153" s="19">
+        <f>'Balance Sheet'!D12/'Income Statement'!D5*365</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Days sales outstanding — the reported ratio RE-BASED onto the revenue basis the forecast actually uses</t>
-        </is>
-      </c>
-      <c r="C154" s="19">
-        <f>C151*'Income Statement'!D5/('Income Statement'!D5-Segments!D8+Segments!D8/C152*C153)</f>
+          <t>Gross-up inside 2025 reported revenue — reported tanker revenue over the same fleet's charter-equivalent revenue</t>
+        </is>
+      </c>
+      <c r="C154" s="42">
+        <f>Segments!D8/Segments!B139</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Days inventory outstanding</t>
-        </is>
-      </c>
-      <c r="C155" s="19">
-        <f>'Balance Sheet'!D11/'Income Statement'!D17*365</f>
+          <t>Gross-up the forecast is built at, from 2026 onward</t>
+        </is>
+      </c>
+      <c r="C155" s="42">
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Days payable outstanding</t>
+          <t>Days sales outstanding — the reported ratio RE-BASED onto the revenue basis the forecast actually uses</t>
         </is>
       </c>
       <c r="C156" s="19">
-        <f>'Balance Sheet'!D15/'Income Statement'!D17*365</f>
+        <f>C153*'Income Statement'!D5/('Income Statement'!D5-Segments!D8+Segments!D8/C154*C155)</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
+          <t>Days inventory outstanding</t>
+        </is>
+      </c>
+      <c r="C157" s="19">
+        <f>'Balance Sheet'!D11/'Income Statement'!D17*365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>Days payable outstanding</t>
+        </is>
+      </c>
+      <c r="C158" s="19">
+        <f>'Balance Sheet'!D15/'Income Statement'!D17*365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
           <t>Net working capital at 31 December 2025 (USD 000)</t>
         </is>
       </c>
-      <c r="C157" s="20">
+      <c r="C159" s="20">
         <f>'Balance Sheet'!D16</f>
         <v/>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="11" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
         <is>
           <t>DEPRECIATION — THE RATE USED, THE RATE REALISED IN 2025 AND THE DISCLOSED USEFUL LIVES, SO THE CHOICE CAN BE JUDGED. These three are memoranda: the rate the model runs on is the blue driver above, and it is sensitised</t>
         </is>
       </c>
-      <c r="B159" s="16" t="inlineStr">
+      <c r="B161" s="16" t="inlineStr">
         <is>
           <t>Memorandum</t>
         </is>
       </c>
-      <c r="C159" s="16" t="n"/>
-      <c r="D159" s="16" t="n"/>
-      <c r="E159" s="16" t="n"/>
-      <c r="F159" s="16" t="n"/>
-      <c r="G159" s="16" t="n"/>
-      <c r="H159" s="16" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>The rate used — first-quarter 2026 depreciation annualised over that quarter's average balance (the driver above)</t>
-        </is>
-      </c>
-      <c r="B160" s="21">
-        <f>C149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>The rate realised in 2025 — depreciation charged on property, plant and equipment over the average balance for that year</t>
-        </is>
-      </c>
-      <c r="B161" s="30" t="n">
-        <v>0.0675</v>
-      </c>
+      <c r="C161" s="16" t="n"/>
+      <c r="D161" s="16" t="n"/>
+      <c r="E161" s="16" t="n"/>
+      <c r="F161" s="16" t="n"/>
+      <c r="G161" s="16" t="n"/>
+      <c r="H161" s="16" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>Disclosed useful life of tankers (years, straight line) — dry-bulk and containers 25, gas carriers 25 to 40, offshore vessels 20 to 25, jack-up barges 40, and dry-docking components 2 to 5, which is why both rates above are heavier than a hull life alone implies</t>
-        </is>
-      </c>
-      <c r="B162" s="29" t="n">
-        <v>25</v>
+          <t>The rate used — first-quarter 2026 depreciation annualised over that quarter's average balance (the driver above)</t>
+        </is>
+      </c>
+      <c r="B162" s="21">
+        <f>C151</f>
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
+          <t>The rate realised in 2025 — depreciation charged on property, plant and equipment over the average balance for that year</t>
+        </is>
+      </c>
+      <c r="B163" s="30" t="n">
+        <v>0.0675</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>Disclosed useful life of tankers (years, straight line) — dry-bulk and containers 25, gas carriers 25 to 40, offshore vessels 20 to 25, jack-up barges 40, and dry-docking components 2 to 5, which is why both rates above are heavier than a hull life alone implies</t>
+        </is>
+      </c>
+      <c r="B164" s="29" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
           <t>Average life implied by the rate used (years)</t>
         </is>
       </c>
-      <c r="B163" s="40">
-        <f>1/C149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="11" t="inlineStr">
+      <c r="B165" s="40">
+        <f>1/C151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11" t="inlineStr">
         <is>
           <t>Tax by business unit and the 2025 depreciation allocation basis</t>
         </is>
       </c>
-      <c r="B165" s="16" t="n"/>
-      <c r="C165" s="16" t="n"/>
-      <c r="D165" s="16" t="n"/>
-      <c r="E165" s="16" t="n"/>
-      <c r="F165" s="16" t="n"/>
-      <c r="G165" s="16" t="n"/>
-      <c r="H165" s="16" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>Integrated Logistics — income tax rate</t>
-        </is>
-      </c>
-      <c r="C166" s="32" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>Shipping — income tax rate</t>
-        </is>
-      </c>
-      <c r="C167" s="32" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="B167" s="16" t="n"/>
+      <c r="C167" s="16" t="n"/>
+      <c r="D167" s="16" t="n"/>
+      <c r="E167" s="16" t="n"/>
+      <c r="F167" s="16" t="n"/>
+      <c r="G167" s="16" t="n"/>
+      <c r="H167" s="16" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>Services — income tax rate</t>
+          <t>Integrated Logistics — income tax rate</t>
         </is>
       </c>
       <c r="C168" s="32" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C169" s="29" t="n">
-        <v>151367</v>
+          <t>Shipping — income tax rate</t>
+        </is>
+      </c>
+      <c r="C169" s="32" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
-        </is>
-      </c>
-      <c r="C170" s="29" t="n">
-        <v>62963</v>
+          <t>Services — income tax rate</t>
+        </is>
+      </c>
+      <c r="C170" s="32" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Contracting — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C171" s="29" t="n">
-        <v>8860</v>
+        <v>151367</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C172" s="29" t="n">
-        <v>195374</v>
+        <v>62963</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Offshore Projects — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C173" s="29" t="n">
-        <v>50526</v>
+        <v>8860</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
+          <t>Tankers — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
       <c r="C174" s="29" t="n">
-        <v>25225</v>
+        <v>195374</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
+          <t>Gas Carriers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C175" s="29" t="n">
+        <v>50526</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Dry-Bulk and Containers — 2025 depreciation and amortisation (USD 000)</t>
+        </is>
+      </c>
+      <c r="C176" s="29" t="n">
+        <v>25225</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
           <t>Services — 2025 depreciation and amortisation (USD 000)</t>
         </is>
       </c>
-      <c r="C175" s="29" t="n">
+      <c r="C177" s="29" t="n">
         <v>30297</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="11" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="11" t="inlineStr">
         <is>
           <t>Funding, distributions and the bridge</t>
         </is>
       </c>
-      <c r="B177" s="16" t="n"/>
-      <c r="C177" s="16" t="n"/>
-      <c r="D177" s="16" t="n"/>
-      <c r="E177" s="16" t="n"/>
-      <c r="F177" s="16" t="n"/>
-      <c r="G177" s="16" t="n"/>
-      <c r="H177" s="16" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>Net debt at 30 June 2026, company basis (USD 000)</t>
-        </is>
-      </c>
-      <c r="C178" s="29" t="n">
-        <v>257318</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
-        <is>
-          <t>Interim dividend declared after the balance-sheet date (USD 000)</t>
-        </is>
-      </c>
-      <c r="C179" s="29" t="n">
-        <v>85300</v>
-      </c>
+      <c r="B179" s="16" t="n"/>
+      <c r="C179" s="16" t="n"/>
+      <c r="D179" s="16" t="n"/>
+      <c r="E179" s="16" t="n"/>
+      <c r="F179" s="16" t="n"/>
+      <c r="G179" s="16" t="n"/>
+      <c r="H179" s="16" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>Deferred consideration on acquisitions (USD 000)</t>
+          <t>Net debt at 30 June 2026, company basis (USD 000)</t>
         </is>
       </c>
       <c r="C180" s="29" t="n">
-        <v>304297</v>
+        <v>257318</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>Perpetual capital securities at carrying value (USD 000)</t>
+          <t>Interim dividend declared after the balance-sheet date (USD 000)</t>
         </is>
       </c>
       <c r="C181" s="29" t="n">
-        <v>1978619</v>
+        <v>85300</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>Perpetual capital securities margin over the overnight rate</t>
-        </is>
-      </c>
-      <c r="C182" s="30" t="n">
-        <v>0.0125</v>
+          <t>Deferred consideration on acquisitions (USD 000)</t>
+        </is>
+      </c>
+      <c r="C182" s="29" t="n">
+        <v>304297</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests at carrying value (USD 000)</t>
+          <t>Perpetual capital securities at carrying value (USD 000)</t>
         </is>
       </c>
       <c r="C183" s="29" t="n">
-        <v>289197</v>
+        <v>1978619</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>Of which arose on the tanker combination — the 20% contracted for purchase in mid-2027 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C184" s="29" t="n">
-        <v>251985</v>
+          <t>Perpetual capital securities margin over the overnight rate</t>
+        </is>
+      </c>
+      <c r="C184" s="30" t="n">
+        <v>0.0125</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>Non-controlling interests' share of profit</t>
-        </is>
-      </c>
-      <c r="C185" s="32" t="n">
-        <v>0.0454</v>
+          <t>Non-controlling interests at carrying value (USD 000)</t>
+        </is>
+      </c>
+      <c r="C185" s="29" t="n">
+        <v>289197</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>Joint ventures and associates at carrying value (USD 000)</t>
+          <t>Of which arose on the tanker combination — the 20% contracted for purchase in mid-2027 (USD 000)</t>
         </is>
       </c>
       <c r="C186" s="29" t="n">
-        <v>522768</v>
+        <v>251985</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
-        </is>
-      </c>
-      <c r="C187" s="29" t="n">
-        <v>5883066</v>
+          <t>Non-controlling interests' share of profit</t>
+        </is>
+      </c>
+      <c r="C187" s="32" t="n">
+        <v>0.0454</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents held (USD 000)</t>
+          <t>Joint ventures and associates at carrying value (USD 000)</t>
         </is>
       </c>
       <c r="C188" s="29" t="n">
-        <v>542682</v>
+        <v>522768</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets (USD 000)</t>
+          <t>Equity attributable to shareholders at 31 March 2026 (USD 000)</t>
         </is>
       </c>
       <c r="C189" s="29" t="n">
-        <v>16192</v>
+        <v>5883066</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>Goodwill (USD 000)</t>
-        </is>
-      </c>
-      <c r="C190" s="20">
-        <f>'Balance Sheet'!D8</f>
-        <v/>
+          <t>Cash and cash equivalents held (USD 000)</t>
+        </is>
+      </c>
+      <c r="C190" s="29" t="n">
+        <v>542682</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+          <t>Intangible assets (USD 000)</t>
         </is>
       </c>
       <c r="C191" s="29" t="n">
-        <v>341000</v>
+        <v>16192</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>Ordinary dividend growth</t>
-        </is>
-      </c>
-      <c r="C192" s="32" t="n">
-        <v>0.05</v>
+          <t>Goodwill (USD 000)</t>
+        </is>
+      </c>
+      <c r="C192" s="20">
+        <f>'Balance Sheet'!D8</f>
+        <v/>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
+          <t>Ordinary dividend declared for 2026 (USD 000)</t>
+        </is>
+      </c>
+      <c r="C193" s="29" t="n">
+        <v>341000</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>Ordinary dividend growth</t>
+        </is>
+      </c>
+      <c r="C194" s="32" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C193" s="32" t="n">
+      <c r="C195" s="32" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="11" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="11" t="inlineStr">
         <is>
           <t>Lens weights and the multiple blend</t>
         </is>
       </c>
-      <c r="B195" s="16" t="n"/>
-      <c r="C195" s="16" t="n"/>
-      <c r="D195" s="16" t="n"/>
-      <c r="E195" s="16" t="n"/>
-      <c r="F195" s="16" t="n"/>
-      <c r="G195" s="16" t="n"/>
-      <c r="H195" s="16" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>Share of 2026 earnings exposed to spot rates</t>
-        </is>
-      </c>
-      <c r="C196" s="32" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>Rate at which the return above the cost of equity fades beyond the forecast (the book lens)</t>
-        </is>
-      </c>
-      <c r="C197" s="32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="B197" s="16" t="n"/>
+      <c r="C197" s="16" t="n"/>
+      <c r="D197" s="16" t="n"/>
+      <c r="E197" s="16" t="n"/>
+      <c r="F197" s="16" t="n"/>
+      <c r="G197" s="16" t="n"/>
+      <c r="H197" s="16" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>Weight on the enterprise multiple within the relative lens</t>
+          <t>Share of 2026 earnings exposed to spot rates</t>
         </is>
       </c>
       <c r="C198" s="32" t="n">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
+          <t>Rate at which the return above the cost of equity fades beyond the forecast (the book lens)</t>
         </is>
       </c>
       <c r="C199" s="32" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative multiples</t>
+          <t>Weight on the enterprise multiple within the relative lens</t>
         </is>
       </c>
       <c r="C200" s="32" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised earnings power</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C201" s="32" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
+          <t>Weight — relative multiples</t>
+        </is>
+      </c>
+      <c r="C202" s="32" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised earnings power</t>
+        </is>
+      </c>
+      <c r="C203" s="32" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
           <t>Weight — book value and sustainable return</t>
         </is>
       </c>
-      <c r="C202" s="32" t="n">
+      <c r="C204" s="32" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
         <is>
           <t>Blue cells on this sheet are independent inputs. Green cells are DERIVED — they are live formulas pointing at the build that produces them, and they are on this sheet only so that every driver the model reads can be found in one place. Nothing here is a pasted result.</t>
         </is>
@@ -11254,7 +11274,7 @@
         </is>
       </c>
       <c r="C9" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
       <c r="D9" s="9">
@@ -11285,7 +11305,7 @@
         </is>
       </c>
       <c r="C11" s="20">
-        <f>-Assumptions!$C$178</f>
+        <f>-Assumptions!$C$180</f>
         <v/>
       </c>
       <c r="D11" s="9">
@@ -11300,7 +11320,7 @@
         </is>
       </c>
       <c r="C12" s="20">
-        <f>-Assumptions!$C$180</f>
+        <f>-Assumptions!$C$182</f>
         <v/>
       </c>
       <c r="D12" s="9">
@@ -11315,7 +11335,7 @@
         </is>
       </c>
       <c r="C13" s="20">
-        <f>-Assumptions!$C$88</f>
+        <f>-Assumptions!$C$90</f>
         <v/>
       </c>
       <c r="D13" s="9">
@@ -11330,7 +11350,7 @@
         </is>
       </c>
       <c r="C14" s="20">
-        <f>-Assumptions!$C$181</f>
+        <f>-Assumptions!$C$183</f>
         <v/>
       </c>
       <c r="D14" s="9">
@@ -11345,7 +11365,7 @@
         </is>
       </c>
       <c r="C15" s="20">
-        <f>-Assumptions!$C$179</f>
+        <f>-Assumptions!$C$181</f>
         <v/>
       </c>
       <c r="D15" s="9">
@@ -11579,7 +11599,7 @@
         </is>
       </c>
       <c r="C31" s="8">
-        <f>Assumptions!$C$196</f>
+        <f>Assumptions!$C$198</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +11644,7 @@
         </is>
       </c>
       <c r="C36" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
     </row>
@@ -11646,7 +11666,7 @@
         </is>
       </c>
       <c r="C38" s="20">
-        <f>-Assumptions!$C$178</f>
+        <f>-Assumptions!$C$180</f>
         <v/>
       </c>
     </row>
@@ -11657,7 +11677,7 @@
         </is>
       </c>
       <c r="C39" s="20">
-        <f>-Assumptions!$C$180</f>
+        <f>-Assumptions!$C$182</f>
         <v/>
       </c>
     </row>
@@ -11668,7 +11688,7 @@
         </is>
       </c>
       <c r="C40" s="20">
-        <f>-Assumptions!$C$88</f>
+        <f>-Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -11679,7 +11699,7 @@
         </is>
       </c>
       <c r="C41" s="20">
-        <f>-Assumptions!$C$181</f>
+        <f>-Assumptions!$C$183</f>
         <v/>
       </c>
     </row>
@@ -11690,7 +11710,7 @@
         </is>
       </c>
       <c r="C42" s="20">
-        <f>-Assumptions!$C$179</f>
+        <f>-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -11701,7 +11721,7 @@
         </is>
       </c>
       <c r="C43" s="20">
-        <f>-Assumptions!$C$183</f>
+        <f>-Assumptions!$C$185</f>
         <v/>
       </c>
     </row>
@@ -12156,23 +12176,23 @@
         </is>
       </c>
       <c r="B26" s="20">
-        <f>Assumptions!$B$38</f>
+        <f>Assumptions!$B$40</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>Assumptions!$D$38</f>
+        <f>Assumptions!$D$40</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>Assumptions!$E$38</f>
+        <f>Assumptions!$E$40</f>
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>Assumptions!$F$38</f>
+        <f>Assumptions!$F$40</f>
         <v/>
       </c>
     </row>
@@ -12183,23 +12203,23 @@
         </is>
       </c>
       <c r="B27" s="20">
-        <f>Assumptions!$B$39</f>
+        <f>Assumptions!$B$41</f>
         <v/>
       </c>
       <c r="C27" s="20">
-        <f>Assumptions!$C$39</f>
+        <f>Assumptions!$C$41</f>
         <v/>
       </c>
       <c r="D27" s="20">
-        <f>Assumptions!$D$39</f>
+        <f>Assumptions!$D$41</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>Assumptions!$E$39</f>
+        <f>Assumptions!$E$41</f>
         <v/>
       </c>
       <c r="F27" s="20">
-        <f>Assumptions!$F$39</f>
+        <f>Assumptions!$F$41</f>
         <v/>
       </c>
     </row>
@@ -12253,7 +12273,7 @@
         <v/>
       </c>
       <c r="F29" s="20">
-        <f>Assumptions!$B$89</f>
+        <f>Assumptions!$B$91</f>
         <v/>
       </c>
     </row>
@@ -12280,7 +12300,7 @@
         <v/>
       </c>
       <c r="F30" s="47">
-        <f>Assumptions!$C$89</f>
+        <f>Assumptions!$C$91</f>
         <v/>
       </c>
     </row>
@@ -12343,35 +12363,35 @@
         </is>
       </c>
       <c r="B33" s="47">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="C33" s="47">
-        <f>Assumptions!$C$80</f>
+        <f>Assumptions!$C$82</f>
         <v/>
       </c>
       <c r="D33" s="47">
-        <f>Assumptions!$D$80</f>
+        <f>Assumptions!$D$82</f>
         <v/>
       </c>
       <c r="E33" s="47">
-        <f>Assumptions!$E$80</f>
+        <f>Assumptions!$E$82</f>
         <v/>
       </c>
       <c r="F33" s="47">
-        <f>Assumptions!$F$80</f>
+        <f>Assumptions!$F$82</f>
         <v/>
       </c>
       <c r="G33" s="47">
-        <f>Assumptions!$G$80</f>
+        <f>Assumptions!$G$82</f>
         <v/>
       </c>
       <c r="H33" s="47">
-        <f>Assumptions!$H$80</f>
+        <f>Assumptions!$H$82</f>
         <v/>
       </c>
       <c r="I33" s="47">
-        <f>Assumptions!$I$80</f>
+        <f>Assumptions!$I$82</f>
         <v/>
       </c>
       <c r="J33" s="36">
@@ -12386,35 +12406,35 @@
         </is>
       </c>
       <c r="B34" s="47">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C34" s="47">
-        <f>Assumptions!$C$81</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="D34" s="47">
-        <f>Assumptions!$D$81</f>
+        <f>Assumptions!$D$83</f>
         <v/>
       </c>
       <c r="E34" s="47">
-        <f>Assumptions!$E$81</f>
+        <f>Assumptions!$E$83</f>
         <v/>
       </c>
       <c r="F34" s="47">
-        <f>Assumptions!$F$81</f>
+        <f>Assumptions!$F$83</f>
         <v/>
       </c>
       <c r="G34" s="47">
-        <f>Assumptions!$G$81</f>
+        <f>Assumptions!$G$83</f>
         <v/>
       </c>
       <c r="H34" s="47">
-        <f>Assumptions!$H$81</f>
+        <f>Assumptions!$H$83</f>
         <v/>
       </c>
       <c r="I34" s="47">
-        <f>Assumptions!$I$81</f>
+        <f>Assumptions!$I$83</f>
         <v/>
       </c>
       <c r="J34" s="36">
@@ -12487,39 +12507,39 @@
         </is>
       </c>
       <c r="B38" s="20">
-        <f>Assumptions!$B$45*Assumptions!$C$63</f>
+        <f>Assumptions!$B$47*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>Assumptions!$C$45*Assumptions!$C$63</f>
+        <f>Assumptions!$C$47*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="D38" s="20">
-        <f>Assumptions!$D$45*Assumptions!$C$63</f>
+        <f>Assumptions!$D$47*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>Assumptions!$E$45*Assumptions!$C$63</f>
+        <f>Assumptions!$E$47*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="F38" s="20">
-        <f>Assumptions!$B$51*Assumptions!$C$63</f>
+        <f>Assumptions!$B$53*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="G38" s="20">
-        <f>Assumptions!$C$51*Assumptions!$C$63</f>
+        <f>Assumptions!$C$53*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="H38" s="20">
-        <f>Assumptions!$D$51*Assumptions!$C$63</f>
+        <f>Assumptions!$D$53*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="I38" s="20">
-        <f>Assumptions!$E$51*Assumptions!$C$63</f>
+        <f>Assumptions!$E$53*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="J38" s="20">
-        <f>AVERAGE(Assumptions!$B$45:$E$45)*Assumptions!$C$63</f>
+        <f>AVERAGE(Assumptions!$B$47:$E$47)*Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -12530,39 +12550,39 @@
         </is>
       </c>
       <c r="B39" s="20">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$47</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>Assumptions!$C$45</f>
+        <f>Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="D39" s="20">
-        <f>Assumptions!$D$45</f>
+        <f>Assumptions!$D$47</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>Assumptions!$E$45</f>
+        <f>Assumptions!$E$47</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>Assumptions!$B$51</f>
+        <f>Assumptions!$B$53</f>
         <v/>
       </c>
       <c r="G39" s="20">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$53</f>
         <v/>
       </c>
       <c r="H39" s="20">
-        <f>Assumptions!$D$51</f>
+        <f>Assumptions!$D$53</f>
         <v/>
       </c>
       <c r="I39" s="20">
-        <f>Assumptions!$E$51</f>
+        <f>Assumptions!$E$53</f>
         <v/>
       </c>
       <c r="J39" s="20">
-        <f>AVERAGE(Assumptions!$B$45:$E$45)</f>
+        <f>AVERAGE(Assumptions!$B$47:$E$47)</f>
         <v/>
       </c>
     </row>
@@ -12573,39 +12593,39 @@
         </is>
       </c>
       <c r="B40" s="20">
-        <f>Assumptions!$B$46</f>
+        <f>Assumptions!$B$48</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>Assumptions!$C$46</f>
+        <f>Assumptions!$C$48</f>
         <v/>
       </c>
       <c r="D40" s="20">
-        <f>Assumptions!$D$46</f>
+        <f>Assumptions!$D$48</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>Assumptions!$E$46</f>
+        <f>Assumptions!$E$48</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>Assumptions!$B$52</f>
+        <f>Assumptions!$B$54</f>
         <v/>
       </c>
       <c r="G40" s="20">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="H40" s="20">
-        <f>Assumptions!$D$52</f>
+        <f>Assumptions!$D$54</f>
         <v/>
       </c>
       <c r="I40" s="20">
-        <f>Assumptions!$E$52</f>
+        <f>Assumptions!$E$54</f>
         <v/>
       </c>
       <c r="J40" s="20">
-        <f>(AVERAGE(Assumptions!$B$42:$E$42)+AVERAGE(Assumptions!$B$46:$E$46))/2</f>
+        <f>(AVERAGE(Assumptions!$B$44:$E$44)+AVERAGE(Assumptions!$B$48:$E$48))/2</f>
         <v/>
       </c>
     </row>
@@ -12616,39 +12636,39 @@
         </is>
       </c>
       <c r="B41" s="20">
-        <f>Assumptions!$B$47</f>
+        <f>Assumptions!$B$49</f>
         <v/>
       </c>
       <c r="C41" s="20">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="D41" s="20">
-        <f>Assumptions!$D$47</f>
+        <f>Assumptions!$D$49</f>
         <v/>
       </c>
       <c r="E41" s="20">
-        <f>Assumptions!$E$47</f>
+        <f>Assumptions!$E$49</f>
         <v/>
       </c>
       <c r="F41" s="20">
-        <f>Assumptions!$B$53</f>
+        <f>Assumptions!$B$55</f>
         <v/>
       </c>
       <c r="G41" s="20">
-        <f>Assumptions!$C$53</f>
+        <f>Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="H41" s="20">
-        <f>Assumptions!$D$53</f>
+        <f>Assumptions!$D$55</f>
         <v/>
       </c>
       <c r="I41" s="20">
-        <f>Assumptions!$E$53</f>
+        <f>Assumptions!$E$55</f>
         <v/>
       </c>
       <c r="J41" s="20">
-        <f>(AVERAGE(Assumptions!$B$43:$E$43)+AVERAGE(Assumptions!$B$47:$E$47))/2</f>
+        <f>(AVERAGE(Assumptions!$B$45:$E$45)+AVERAGE(Assumptions!$B$49:$E$49))/2</f>
         <v/>
       </c>
     </row>
@@ -12659,39 +12679,39 @@
         </is>
       </c>
       <c r="B42" s="20">
-        <f>Assumptions!$B$48</f>
+        <f>Assumptions!$B$50</f>
         <v/>
       </c>
       <c r="C42" s="20">
-        <f>Assumptions!$C$48</f>
+        <f>Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="D42" s="20">
-        <f>Assumptions!$D$48</f>
+        <f>Assumptions!$D$50</f>
         <v/>
       </c>
       <c r="E42" s="20">
-        <f>Assumptions!$E$48</f>
+        <f>Assumptions!$E$50</f>
         <v/>
       </c>
       <c r="F42" s="20">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="G42" s="20">
-        <f>Assumptions!$C$54</f>
+        <f>Assumptions!$C$56</f>
         <v/>
       </c>
       <c r="H42" s="20">
-        <f>Assumptions!$D$54</f>
+        <f>Assumptions!$D$56</f>
         <v/>
       </c>
       <c r="I42" s="20">
-        <f>Assumptions!$E$54</f>
+        <f>Assumptions!$E$56</f>
         <v/>
       </c>
       <c r="J42" s="20">
-        <f>(AVERAGE(Assumptions!$B$44:$E$44)+AVERAGE(Assumptions!$B$48:$E$48))/2</f>
+        <f>(AVERAGE(Assumptions!$B$46:$E$46)+AVERAGE(Assumptions!$B$50:$E$50))/2</f>
         <v/>
       </c>
     </row>
@@ -13033,39 +13053,39 @@
         </is>
       </c>
       <c r="B54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,B$34)-MAX(Assumptions!$C$66,B$33),0)+MAX(MIN(Assumptions!$D$67,B$34)-MAX(Assumptions!$C$67,B$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,B$34)-MAX(Assumptions!$C$68,B$33),0)+MAX(MIN(Assumptions!$D$69,B$34)-MAX(Assumptions!$C$69,B$33),0)</f>
         <v/>
       </c>
       <c r="C54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,C$34)-MAX(Assumptions!$C$66,C$33),0)+MAX(MIN(Assumptions!$D$67,C$34)-MAX(Assumptions!$C$67,C$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,C$34)-MAX(Assumptions!$C$68,C$33),0)+MAX(MIN(Assumptions!$D$69,C$34)-MAX(Assumptions!$C$69,C$33),0)</f>
         <v/>
       </c>
       <c r="D54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,D$34)-MAX(Assumptions!$C$66,D$33),0)+MAX(MIN(Assumptions!$D$67,D$34)-MAX(Assumptions!$C$67,D$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,D$34)-MAX(Assumptions!$C$68,D$33),0)+MAX(MIN(Assumptions!$D$69,D$34)-MAX(Assumptions!$C$69,D$33),0)</f>
         <v/>
       </c>
       <c r="E54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,E$34)-MAX(Assumptions!$C$66,E$33),0)+MAX(MIN(Assumptions!$D$67,E$34)-MAX(Assumptions!$C$67,E$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,E$34)-MAX(Assumptions!$C$68,E$33),0)+MAX(MIN(Assumptions!$D$69,E$34)-MAX(Assumptions!$C$69,E$33),0)</f>
         <v/>
       </c>
       <c r="F54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,F$34)-MAX(Assumptions!$C$66,F$33),0)+MAX(MIN(Assumptions!$D$67,F$34)-MAX(Assumptions!$C$67,F$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,F$34)-MAX(Assumptions!$C$68,F$33),0)+MAX(MIN(Assumptions!$D$69,F$34)-MAX(Assumptions!$C$69,F$33),0)</f>
         <v/>
       </c>
       <c r="G54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,G$34)-MAX(Assumptions!$C$66,G$33),0)+MAX(MIN(Assumptions!$D$67,G$34)-MAX(Assumptions!$C$67,G$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,G$34)-MAX(Assumptions!$C$68,G$33),0)+MAX(MIN(Assumptions!$D$69,G$34)-MAX(Assumptions!$C$69,G$33),0)</f>
         <v/>
       </c>
       <c r="H54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,H$34)-MAX(Assumptions!$C$66,H$33),0)+MAX(MIN(Assumptions!$D$67,H$34)-MAX(Assumptions!$C$67,H$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,H$34)-MAX(Assumptions!$C$68,H$33),0)+MAX(MIN(Assumptions!$D$69,H$34)-MAX(Assumptions!$C$69,H$33),0)</f>
         <v/>
       </c>
       <c r="I54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,I$34)-MAX(Assumptions!$C$66,I$33),0)+MAX(MIN(Assumptions!$D$67,I$34)-MAX(Assumptions!$C$67,I$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,I$34)-MAX(Assumptions!$C$68,I$33),0)+MAX(MIN(Assumptions!$D$69,I$34)-MAX(Assumptions!$C$69,I$33),0)</f>
         <v/>
       </c>
       <c r="J54" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,J$34)-MAX(Assumptions!$C$66,J$33),0)+MAX(MIN(Assumptions!$D$67,J$34)-MAX(Assumptions!$C$67,J$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,J$34)-MAX(Assumptions!$C$68,J$33),0)+MAX(MIN(Assumptions!$D$69,J$34)-MAX(Assumptions!$C$69,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -13076,39 +13096,39 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,B$34)-MAX(Assumptions!$C$68,B$33),0)+MAX(MIN(Assumptions!$D$69,B$34)-MAX(Assumptions!$C$69,B$33),0)+MAX(MIN(Assumptions!$D$70,B$34)-MAX(Assumptions!$C$70,B$33),0)+MAX(MIN(Assumptions!$D$71,B$34)-MAX(Assumptions!$C$71,B$33),0)+MAX(MIN(Assumptions!$D$72,B$34)-MAX(Assumptions!$C$72,B$33),0)+MAX(MIN(Assumptions!$D$73,B$34)-MAX(Assumptions!$C$73,B$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,B$34)-MAX(Assumptions!$C$70,B$33),0)+MAX(MIN(Assumptions!$D$71,B$34)-MAX(Assumptions!$C$71,B$33),0)+MAX(MIN(Assumptions!$D$72,B$34)-MAX(Assumptions!$C$72,B$33),0)+MAX(MIN(Assumptions!$D$73,B$34)-MAX(Assumptions!$C$73,B$33),0)+MAX(MIN(Assumptions!$D$74,B$34)-MAX(Assumptions!$C$74,B$33),0)+MAX(MIN(Assumptions!$D$75,B$34)-MAX(Assumptions!$C$75,B$33),0)</f>
         <v/>
       </c>
       <c r="C55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,C$34)-MAX(Assumptions!$C$68,C$33),0)+MAX(MIN(Assumptions!$D$69,C$34)-MAX(Assumptions!$C$69,C$33),0)+MAX(MIN(Assumptions!$D$70,C$34)-MAX(Assumptions!$C$70,C$33),0)+MAX(MIN(Assumptions!$D$71,C$34)-MAX(Assumptions!$C$71,C$33),0)+MAX(MIN(Assumptions!$D$72,C$34)-MAX(Assumptions!$C$72,C$33),0)+MAX(MIN(Assumptions!$D$73,C$34)-MAX(Assumptions!$C$73,C$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,C$34)-MAX(Assumptions!$C$70,C$33),0)+MAX(MIN(Assumptions!$D$71,C$34)-MAX(Assumptions!$C$71,C$33),0)+MAX(MIN(Assumptions!$D$72,C$34)-MAX(Assumptions!$C$72,C$33),0)+MAX(MIN(Assumptions!$D$73,C$34)-MAX(Assumptions!$C$73,C$33),0)+MAX(MIN(Assumptions!$D$74,C$34)-MAX(Assumptions!$C$74,C$33),0)+MAX(MIN(Assumptions!$D$75,C$34)-MAX(Assumptions!$C$75,C$33),0)</f>
         <v/>
       </c>
       <c r="D55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,D$34)-MAX(Assumptions!$C$68,D$33),0)+MAX(MIN(Assumptions!$D$69,D$34)-MAX(Assumptions!$C$69,D$33),0)+MAX(MIN(Assumptions!$D$70,D$34)-MAX(Assumptions!$C$70,D$33),0)+MAX(MIN(Assumptions!$D$71,D$34)-MAX(Assumptions!$C$71,D$33),0)+MAX(MIN(Assumptions!$D$72,D$34)-MAX(Assumptions!$C$72,D$33),0)+MAX(MIN(Assumptions!$D$73,D$34)-MAX(Assumptions!$C$73,D$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,D$34)-MAX(Assumptions!$C$70,D$33),0)+MAX(MIN(Assumptions!$D$71,D$34)-MAX(Assumptions!$C$71,D$33),0)+MAX(MIN(Assumptions!$D$72,D$34)-MAX(Assumptions!$C$72,D$33),0)+MAX(MIN(Assumptions!$D$73,D$34)-MAX(Assumptions!$C$73,D$33),0)+MAX(MIN(Assumptions!$D$74,D$34)-MAX(Assumptions!$C$74,D$33),0)+MAX(MIN(Assumptions!$D$75,D$34)-MAX(Assumptions!$C$75,D$33),0)</f>
         <v/>
       </c>
       <c r="E55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,E$34)-MAX(Assumptions!$C$68,E$33),0)+MAX(MIN(Assumptions!$D$69,E$34)-MAX(Assumptions!$C$69,E$33),0)+MAX(MIN(Assumptions!$D$70,E$34)-MAX(Assumptions!$C$70,E$33),0)+MAX(MIN(Assumptions!$D$71,E$34)-MAX(Assumptions!$C$71,E$33),0)+MAX(MIN(Assumptions!$D$72,E$34)-MAX(Assumptions!$C$72,E$33),0)+MAX(MIN(Assumptions!$D$73,E$34)-MAX(Assumptions!$C$73,E$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,E$34)-MAX(Assumptions!$C$70,E$33),0)+MAX(MIN(Assumptions!$D$71,E$34)-MAX(Assumptions!$C$71,E$33),0)+MAX(MIN(Assumptions!$D$72,E$34)-MAX(Assumptions!$C$72,E$33),0)+MAX(MIN(Assumptions!$D$73,E$34)-MAX(Assumptions!$C$73,E$33),0)+MAX(MIN(Assumptions!$D$74,E$34)-MAX(Assumptions!$C$74,E$33),0)+MAX(MIN(Assumptions!$D$75,E$34)-MAX(Assumptions!$C$75,E$33),0)</f>
         <v/>
       </c>
       <c r="F55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,F$34)-MAX(Assumptions!$C$68,F$33),0)+MAX(MIN(Assumptions!$D$69,F$34)-MAX(Assumptions!$C$69,F$33),0)+MAX(MIN(Assumptions!$D$70,F$34)-MAX(Assumptions!$C$70,F$33),0)+MAX(MIN(Assumptions!$D$71,F$34)-MAX(Assumptions!$C$71,F$33),0)+MAX(MIN(Assumptions!$D$72,F$34)-MAX(Assumptions!$C$72,F$33),0)+MAX(MIN(Assumptions!$D$73,F$34)-MAX(Assumptions!$C$73,F$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,F$34)-MAX(Assumptions!$C$70,F$33),0)+MAX(MIN(Assumptions!$D$71,F$34)-MAX(Assumptions!$C$71,F$33),0)+MAX(MIN(Assumptions!$D$72,F$34)-MAX(Assumptions!$C$72,F$33),0)+MAX(MIN(Assumptions!$D$73,F$34)-MAX(Assumptions!$C$73,F$33),0)+MAX(MIN(Assumptions!$D$74,F$34)-MAX(Assumptions!$C$74,F$33),0)+MAX(MIN(Assumptions!$D$75,F$34)-MAX(Assumptions!$C$75,F$33),0)</f>
         <v/>
       </c>
       <c r="G55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,G$34)-MAX(Assumptions!$C$68,G$33),0)+MAX(MIN(Assumptions!$D$69,G$34)-MAX(Assumptions!$C$69,G$33),0)+MAX(MIN(Assumptions!$D$70,G$34)-MAX(Assumptions!$C$70,G$33),0)+MAX(MIN(Assumptions!$D$71,G$34)-MAX(Assumptions!$C$71,G$33),0)+MAX(MIN(Assumptions!$D$72,G$34)-MAX(Assumptions!$C$72,G$33),0)+MAX(MIN(Assumptions!$D$73,G$34)-MAX(Assumptions!$C$73,G$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,G$34)-MAX(Assumptions!$C$70,G$33),0)+MAX(MIN(Assumptions!$D$71,G$34)-MAX(Assumptions!$C$71,G$33),0)+MAX(MIN(Assumptions!$D$72,G$34)-MAX(Assumptions!$C$72,G$33),0)+MAX(MIN(Assumptions!$D$73,G$34)-MAX(Assumptions!$C$73,G$33),0)+MAX(MIN(Assumptions!$D$74,G$34)-MAX(Assumptions!$C$74,G$33),0)+MAX(MIN(Assumptions!$D$75,G$34)-MAX(Assumptions!$C$75,G$33),0)</f>
         <v/>
       </c>
       <c r="H55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,H$34)-MAX(Assumptions!$C$68,H$33),0)+MAX(MIN(Assumptions!$D$69,H$34)-MAX(Assumptions!$C$69,H$33),0)+MAX(MIN(Assumptions!$D$70,H$34)-MAX(Assumptions!$C$70,H$33),0)+MAX(MIN(Assumptions!$D$71,H$34)-MAX(Assumptions!$C$71,H$33),0)+MAX(MIN(Assumptions!$D$72,H$34)-MAX(Assumptions!$C$72,H$33),0)+MAX(MIN(Assumptions!$D$73,H$34)-MAX(Assumptions!$C$73,H$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,H$34)-MAX(Assumptions!$C$70,H$33),0)+MAX(MIN(Assumptions!$D$71,H$34)-MAX(Assumptions!$C$71,H$33),0)+MAX(MIN(Assumptions!$D$72,H$34)-MAX(Assumptions!$C$72,H$33),0)+MAX(MIN(Assumptions!$D$73,H$34)-MAX(Assumptions!$C$73,H$33),0)+MAX(MIN(Assumptions!$D$74,H$34)-MAX(Assumptions!$C$74,H$33),0)+MAX(MIN(Assumptions!$D$75,H$34)-MAX(Assumptions!$C$75,H$33),0)</f>
         <v/>
       </c>
       <c r="I55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,I$34)-MAX(Assumptions!$C$68,I$33),0)+MAX(MIN(Assumptions!$D$69,I$34)-MAX(Assumptions!$C$69,I$33),0)+MAX(MIN(Assumptions!$D$70,I$34)-MAX(Assumptions!$C$70,I$33),0)+MAX(MIN(Assumptions!$D$71,I$34)-MAX(Assumptions!$C$71,I$33),0)+MAX(MIN(Assumptions!$D$72,I$34)-MAX(Assumptions!$C$72,I$33),0)+MAX(MIN(Assumptions!$D$73,I$34)-MAX(Assumptions!$C$73,I$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,I$34)-MAX(Assumptions!$C$70,I$33),0)+MAX(MIN(Assumptions!$D$71,I$34)-MAX(Assumptions!$C$71,I$33),0)+MAX(MIN(Assumptions!$D$72,I$34)-MAX(Assumptions!$C$72,I$33),0)+MAX(MIN(Assumptions!$D$73,I$34)-MAX(Assumptions!$C$73,I$33),0)+MAX(MIN(Assumptions!$D$74,I$34)-MAX(Assumptions!$C$74,I$33),0)+MAX(MIN(Assumptions!$D$75,I$34)-MAX(Assumptions!$C$75,I$33),0)</f>
         <v/>
       </c>
       <c r="J55" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,J$34)-MAX(Assumptions!$C$68,J$33),0)+MAX(MIN(Assumptions!$D$69,J$34)-MAX(Assumptions!$C$69,J$33),0)+MAX(MIN(Assumptions!$D$70,J$34)-MAX(Assumptions!$C$70,J$33),0)+MAX(MIN(Assumptions!$D$71,J$34)-MAX(Assumptions!$C$71,J$33),0)+MAX(MIN(Assumptions!$D$72,J$34)-MAX(Assumptions!$C$72,J$33),0)+MAX(MIN(Assumptions!$D$73,J$34)-MAX(Assumptions!$C$73,J$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,J$34)-MAX(Assumptions!$C$70,J$33),0)+MAX(MIN(Assumptions!$D$71,J$34)-MAX(Assumptions!$C$71,J$33),0)+MAX(MIN(Assumptions!$D$72,J$34)-MAX(Assumptions!$C$72,J$33),0)+MAX(MIN(Assumptions!$D$73,J$34)-MAX(Assumptions!$C$73,J$33),0)+MAX(MIN(Assumptions!$D$74,J$34)-MAX(Assumptions!$C$74,J$33),0)+MAX(MIN(Assumptions!$D$75,J$34)-MAX(Assumptions!$C$75,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -13119,39 +13139,39 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,B$34)-MAX(Assumptions!$C$74,B$33),0)+MAX(MIN(Assumptions!$D$75,B$34)-MAX(Assumptions!$C$75,B$33),0)+MAX(MIN(Assumptions!$D$76,B$34)-MAX(Assumptions!$C$76,B$33),0)+MAX(MIN(Assumptions!$D$77,B$34)-MAX(Assumptions!$C$77,B$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,B$34)-MAX(Assumptions!$C$76,B$33),0)+MAX(MIN(Assumptions!$D$77,B$34)-MAX(Assumptions!$C$77,B$33),0)+MAX(MIN(Assumptions!$D$78,B$34)-MAX(Assumptions!$C$78,B$33),0)+MAX(MIN(Assumptions!$D$79,B$34)-MAX(Assumptions!$C$79,B$33),0)</f>
         <v/>
       </c>
       <c r="C56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,C$34)-MAX(Assumptions!$C$74,C$33),0)+MAX(MIN(Assumptions!$D$75,C$34)-MAX(Assumptions!$C$75,C$33),0)+MAX(MIN(Assumptions!$D$76,C$34)-MAX(Assumptions!$C$76,C$33),0)+MAX(MIN(Assumptions!$D$77,C$34)-MAX(Assumptions!$C$77,C$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,C$34)-MAX(Assumptions!$C$76,C$33),0)+MAX(MIN(Assumptions!$D$77,C$34)-MAX(Assumptions!$C$77,C$33),0)+MAX(MIN(Assumptions!$D$78,C$34)-MAX(Assumptions!$C$78,C$33),0)+MAX(MIN(Assumptions!$D$79,C$34)-MAX(Assumptions!$C$79,C$33),0)</f>
         <v/>
       </c>
       <c r="D56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,D$34)-MAX(Assumptions!$C$74,D$33),0)+MAX(MIN(Assumptions!$D$75,D$34)-MAX(Assumptions!$C$75,D$33),0)+MAX(MIN(Assumptions!$D$76,D$34)-MAX(Assumptions!$C$76,D$33),0)+MAX(MIN(Assumptions!$D$77,D$34)-MAX(Assumptions!$C$77,D$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,D$34)-MAX(Assumptions!$C$76,D$33),0)+MAX(MIN(Assumptions!$D$77,D$34)-MAX(Assumptions!$C$77,D$33),0)+MAX(MIN(Assumptions!$D$78,D$34)-MAX(Assumptions!$C$78,D$33),0)+MAX(MIN(Assumptions!$D$79,D$34)-MAX(Assumptions!$C$79,D$33),0)</f>
         <v/>
       </c>
       <c r="E56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,E$34)-MAX(Assumptions!$C$74,E$33),0)+MAX(MIN(Assumptions!$D$75,E$34)-MAX(Assumptions!$C$75,E$33),0)+MAX(MIN(Assumptions!$D$76,E$34)-MAX(Assumptions!$C$76,E$33),0)+MAX(MIN(Assumptions!$D$77,E$34)-MAX(Assumptions!$C$77,E$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,E$34)-MAX(Assumptions!$C$76,E$33),0)+MAX(MIN(Assumptions!$D$77,E$34)-MAX(Assumptions!$C$77,E$33),0)+MAX(MIN(Assumptions!$D$78,E$34)-MAX(Assumptions!$C$78,E$33),0)+MAX(MIN(Assumptions!$D$79,E$34)-MAX(Assumptions!$C$79,E$33),0)</f>
         <v/>
       </c>
       <c r="F56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,F$34)-MAX(Assumptions!$C$74,F$33),0)+MAX(MIN(Assumptions!$D$75,F$34)-MAX(Assumptions!$C$75,F$33),0)+MAX(MIN(Assumptions!$D$76,F$34)-MAX(Assumptions!$C$76,F$33),0)+MAX(MIN(Assumptions!$D$77,F$34)-MAX(Assumptions!$C$77,F$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,F$34)-MAX(Assumptions!$C$76,F$33),0)+MAX(MIN(Assumptions!$D$77,F$34)-MAX(Assumptions!$C$77,F$33),0)+MAX(MIN(Assumptions!$D$78,F$34)-MAX(Assumptions!$C$78,F$33),0)+MAX(MIN(Assumptions!$D$79,F$34)-MAX(Assumptions!$C$79,F$33),0)</f>
         <v/>
       </c>
       <c r="G56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,G$34)-MAX(Assumptions!$C$74,G$33),0)+MAX(MIN(Assumptions!$D$75,G$34)-MAX(Assumptions!$C$75,G$33),0)+MAX(MIN(Assumptions!$D$76,G$34)-MAX(Assumptions!$C$76,G$33),0)+MAX(MIN(Assumptions!$D$77,G$34)-MAX(Assumptions!$C$77,G$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,G$34)-MAX(Assumptions!$C$76,G$33),0)+MAX(MIN(Assumptions!$D$77,G$34)-MAX(Assumptions!$C$77,G$33),0)+MAX(MIN(Assumptions!$D$78,G$34)-MAX(Assumptions!$C$78,G$33),0)+MAX(MIN(Assumptions!$D$79,G$34)-MAX(Assumptions!$C$79,G$33),0)</f>
         <v/>
       </c>
       <c r="H56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,H$34)-MAX(Assumptions!$C$74,H$33),0)+MAX(MIN(Assumptions!$D$75,H$34)-MAX(Assumptions!$C$75,H$33),0)+MAX(MIN(Assumptions!$D$76,H$34)-MAX(Assumptions!$C$76,H$33),0)+MAX(MIN(Assumptions!$D$77,H$34)-MAX(Assumptions!$C$77,H$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,H$34)-MAX(Assumptions!$C$76,H$33),0)+MAX(MIN(Assumptions!$D$77,H$34)-MAX(Assumptions!$C$77,H$33),0)+MAX(MIN(Assumptions!$D$78,H$34)-MAX(Assumptions!$C$78,H$33),0)+MAX(MIN(Assumptions!$D$79,H$34)-MAX(Assumptions!$C$79,H$33),0)</f>
         <v/>
       </c>
       <c r="I56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,I$34)-MAX(Assumptions!$C$74,I$33),0)+MAX(MIN(Assumptions!$D$75,I$34)-MAX(Assumptions!$C$75,I$33),0)+MAX(MIN(Assumptions!$D$76,I$34)-MAX(Assumptions!$C$76,I$33),0)+MAX(MIN(Assumptions!$D$77,I$34)-MAX(Assumptions!$C$77,I$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,I$34)-MAX(Assumptions!$C$76,I$33),0)+MAX(MIN(Assumptions!$D$77,I$34)-MAX(Assumptions!$C$77,I$33),0)+MAX(MIN(Assumptions!$D$78,I$34)-MAX(Assumptions!$C$78,I$33),0)+MAX(MIN(Assumptions!$D$79,I$34)-MAX(Assumptions!$C$79,I$33),0)</f>
         <v/>
       </c>
       <c r="J56" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,J$34)-MAX(Assumptions!$C$74,J$33),0)+MAX(MIN(Assumptions!$D$75,J$34)-MAX(Assumptions!$C$75,J$33),0)+MAX(MIN(Assumptions!$D$76,J$34)-MAX(Assumptions!$C$76,J$33),0)+MAX(MIN(Assumptions!$D$77,J$34)-MAX(Assumptions!$C$77,J$33),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,J$34)-MAX(Assumptions!$C$76,J$33),0)+MAX(MIN(Assumptions!$D$77,J$34)-MAX(Assumptions!$C$77,J$33),0)+MAX(MIN(Assumptions!$D$78,J$34)-MAX(Assumptions!$C$78,J$33),0)+MAX(MIN(Assumptions!$D$79,J$34)-MAX(Assumptions!$C$79,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -13263,39 +13283,39 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,B$34)-MAX(Assumptions!$C$66,B$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,B$34)-MAX(Assumptions!$C$67,B$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,B$34)-MAX(Assumptions!$C$68,B$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,B$34)-MAX(Assumptions!$C$69,B$33),0)</f>
         <v/>
       </c>
       <c r="C61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,C$34)-MAX(Assumptions!$C$66,C$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,C$34)-MAX(Assumptions!$C$67,C$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,C$34)-MAX(Assumptions!$C$68,C$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,C$34)-MAX(Assumptions!$C$69,C$33),0)</f>
         <v/>
       </c>
       <c r="D61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,D$34)-MAX(Assumptions!$C$66,D$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,D$34)-MAX(Assumptions!$C$67,D$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,D$34)-MAX(Assumptions!$C$68,D$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,D$34)-MAX(Assumptions!$C$69,D$33),0)</f>
         <v/>
       </c>
       <c r="E61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,E$34)-MAX(Assumptions!$C$66,E$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,E$34)-MAX(Assumptions!$C$67,E$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,E$34)-MAX(Assumptions!$C$68,E$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,E$34)-MAX(Assumptions!$C$69,E$33),0)</f>
         <v/>
       </c>
       <c r="F61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,F$34)-MAX(Assumptions!$C$66,F$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,F$34)-MAX(Assumptions!$C$67,F$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,F$34)-MAX(Assumptions!$C$68,F$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,F$34)-MAX(Assumptions!$C$69,F$33),0)</f>
         <v/>
       </c>
       <c r="G61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,G$34)-MAX(Assumptions!$C$66,G$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,G$34)-MAX(Assumptions!$C$67,G$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,G$34)-MAX(Assumptions!$C$68,G$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,G$34)-MAX(Assumptions!$C$69,G$33),0)</f>
         <v/>
       </c>
       <c r="H61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,H$34)-MAX(Assumptions!$C$66,H$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,H$34)-MAX(Assumptions!$C$67,H$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,H$34)-MAX(Assumptions!$C$68,H$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,H$34)-MAX(Assumptions!$C$69,H$33),0)</f>
         <v/>
       </c>
       <c r="I61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,I$34)-MAX(Assumptions!$C$66,I$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,I$34)-MAX(Assumptions!$C$67,I$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,I$34)-MAX(Assumptions!$C$68,I$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,I$34)-MAX(Assumptions!$C$69,I$33),0)</f>
         <v/>
       </c>
       <c r="J61" s="33">
-        <f>Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,J$34)-MAX(Assumptions!$C$66,J$33),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,J$34)-MAX(Assumptions!$C$67,J$33),0)</f>
+        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,J$34)-MAX(Assumptions!$C$68,J$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,J$34)-MAX(Assumptions!$C$69,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -13306,39 +13326,39 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,B$34)-MAX(Assumptions!$C$68,B$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,B$34)-MAX(Assumptions!$C$69,B$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,B$34)-MAX(Assumptions!$C$70,B$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,B$34)-MAX(Assumptions!$C$71,B$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,B$34)-MAX(Assumptions!$C$72,B$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,B$34)-MAX(Assumptions!$C$73,B$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,B$34)-MAX(Assumptions!$C$70,B$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,B$34)-MAX(Assumptions!$C$71,B$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,B$34)-MAX(Assumptions!$C$72,B$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,B$34)-MAX(Assumptions!$C$73,B$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,B$34)-MAX(Assumptions!$C$74,B$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,B$34)-MAX(Assumptions!$C$75,B$33),0)</f>
         <v/>
       </c>
       <c r="C62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,C$34)-MAX(Assumptions!$C$68,C$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,C$34)-MAX(Assumptions!$C$69,C$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,C$34)-MAX(Assumptions!$C$70,C$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,C$34)-MAX(Assumptions!$C$71,C$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,C$34)-MAX(Assumptions!$C$72,C$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,C$34)-MAX(Assumptions!$C$73,C$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,C$34)-MAX(Assumptions!$C$70,C$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,C$34)-MAX(Assumptions!$C$71,C$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,C$34)-MAX(Assumptions!$C$72,C$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,C$34)-MAX(Assumptions!$C$73,C$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,C$34)-MAX(Assumptions!$C$74,C$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,C$34)-MAX(Assumptions!$C$75,C$33),0)</f>
         <v/>
       </c>
       <c r="D62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,D$34)-MAX(Assumptions!$C$68,D$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,D$34)-MAX(Assumptions!$C$69,D$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,D$34)-MAX(Assumptions!$C$70,D$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,D$34)-MAX(Assumptions!$C$71,D$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,D$34)-MAX(Assumptions!$C$72,D$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,D$34)-MAX(Assumptions!$C$73,D$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,D$34)-MAX(Assumptions!$C$70,D$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,D$34)-MAX(Assumptions!$C$71,D$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,D$34)-MAX(Assumptions!$C$72,D$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,D$34)-MAX(Assumptions!$C$73,D$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,D$34)-MAX(Assumptions!$C$74,D$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,D$34)-MAX(Assumptions!$C$75,D$33),0)</f>
         <v/>
       </c>
       <c r="E62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,E$34)-MAX(Assumptions!$C$68,E$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,E$34)-MAX(Assumptions!$C$69,E$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,E$34)-MAX(Assumptions!$C$70,E$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,E$34)-MAX(Assumptions!$C$71,E$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,E$34)-MAX(Assumptions!$C$72,E$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,E$34)-MAX(Assumptions!$C$73,E$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,E$34)-MAX(Assumptions!$C$70,E$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,E$34)-MAX(Assumptions!$C$71,E$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,E$34)-MAX(Assumptions!$C$72,E$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,E$34)-MAX(Assumptions!$C$73,E$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,E$34)-MAX(Assumptions!$C$74,E$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,E$34)-MAX(Assumptions!$C$75,E$33),0)</f>
         <v/>
       </c>
       <c r="F62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,F$34)-MAX(Assumptions!$C$68,F$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,F$34)-MAX(Assumptions!$C$69,F$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,F$34)-MAX(Assumptions!$C$70,F$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,F$34)-MAX(Assumptions!$C$71,F$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,F$34)-MAX(Assumptions!$C$72,F$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,F$34)-MAX(Assumptions!$C$73,F$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,F$34)-MAX(Assumptions!$C$70,F$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,F$34)-MAX(Assumptions!$C$71,F$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,F$34)-MAX(Assumptions!$C$72,F$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,F$34)-MAX(Assumptions!$C$73,F$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,F$34)-MAX(Assumptions!$C$74,F$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,F$34)-MAX(Assumptions!$C$75,F$33),0)</f>
         <v/>
       </c>
       <c r="G62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,G$34)-MAX(Assumptions!$C$68,G$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,G$34)-MAX(Assumptions!$C$69,G$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,G$34)-MAX(Assumptions!$C$70,G$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,G$34)-MAX(Assumptions!$C$71,G$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,G$34)-MAX(Assumptions!$C$72,G$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,G$34)-MAX(Assumptions!$C$73,G$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,G$34)-MAX(Assumptions!$C$70,G$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,G$34)-MAX(Assumptions!$C$71,G$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,G$34)-MAX(Assumptions!$C$72,G$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,G$34)-MAX(Assumptions!$C$73,G$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,G$34)-MAX(Assumptions!$C$74,G$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,G$34)-MAX(Assumptions!$C$75,G$33),0)</f>
         <v/>
       </c>
       <c r="H62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,H$34)-MAX(Assumptions!$C$68,H$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,H$34)-MAX(Assumptions!$C$69,H$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,H$34)-MAX(Assumptions!$C$70,H$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,H$34)-MAX(Assumptions!$C$71,H$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,H$34)-MAX(Assumptions!$C$72,H$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,H$34)-MAX(Assumptions!$C$73,H$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,H$34)-MAX(Assumptions!$C$70,H$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,H$34)-MAX(Assumptions!$C$71,H$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,H$34)-MAX(Assumptions!$C$72,H$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,H$34)-MAX(Assumptions!$C$73,H$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,H$34)-MAX(Assumptions!$C$74,H$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,H$34)-MAX(Assumptions!$C$75,H$33),0)</f>
         <v/>
       </c>
       <c r="I62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,I$34)-MAX(Assumptions!$C$68,I$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,I$34)-MAX(Assumptions!$C$69,I$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,I$34)-MAX(Assumptions!$C$70,I$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,I$34)-MAX(Assumptions!$C$71,I$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,I$34)-MAX(Assumptions!$C$72,I$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,I$34)-MAX(Assumptions!$C$73,I$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,I$34)-MAX(Assumptions!$C$70,I$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,I$34)-MAX(Assumptions!$C$71,I$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,I$34)-MAX(Assumptions!$C$72,I$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,I$34)-MAX(Assumptions!$C$73,I$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,I$34)-MAX(Assumptions!$C$74,I$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,I$34)-MAX(Assumptions!$C$75,I$33),0)</f>
         <v/>
       </c>
       <c r="J62" s="33">
-        <f>Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,J$34)-MAX(Assumptions!$C$68,J$33),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,J$34)-MAX(Assumptions!$C$69,J$33),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,J$34)-MAX(Assumptions!$C$70,J$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,J$34)-MAX(Assumptions!$C$71,J$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,J$34)-MAX(Assumptions!$C$72,J$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,J$34)-MAX(Assumptions!$C$73,J$33),0)</f>
+        <f>Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,J$34)-MAX(Assumptions!$C$70,J$33),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,J$34)-MAX(Assumptions!$C$71,J$33),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,J$34)-MAX(Assumptions!$C$72,J$33),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,J$34)-MAX(Assumptions!$C$73,J$33),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,J$34)-MAX(Assumptions!$C$74,J$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,J$34)-MAX(Assumptions!$C$75,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -13349,39 +13369,39 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,B$34)-MAX(Assumptions!$C$74,B$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,B$34)-MAX(Assumptions!$C$75,B$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,B$34)-MAX(Assumptions!$C$76,B$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,B$34)-MAX(Assumptions!$C$77,B$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,B$34)-MAX(Assumptions!$C$76,B$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,B$34)-MAX(Assumptions!$C$77,B$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,B$34)-MAX(Assumptions!$C$78,B$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,B$34)-MAX(Assumptions!$C$79,B$33),0)</f>
         <v/>
       </c>
       <c r="C63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,C$34)-MAX(Assumptions!$C$74,C$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,C$34)-MAX(Assumptions!$C$75,C$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,C$34)-MAX(Assumptions!$C$76,C$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,C$34)-MAX(Assumptions!$C$77,C$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,C$34)-MAX(Assumptions!$C$76,C$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,C$34)-MAX(Assumptions!$C$77,C$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,C$34)-MAX(Assumptions!$C$78,C$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,C$34)-MAX(Assumptions!$C$79,C$33),0)</f>
         <v/>
       </c>
       <c r="D63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,D$34)-MAX(Assumptions!$C$74,D$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,D$34)-MAX(Assumptions!$C$75,D$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,D$34)-MAX(Assumptions!$C$76,D$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,D$34)-MAX(Assumptions!$C$77,D$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,D$34)-MAX(Assumptions!$C$76,D$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,D$34)-MAX(Assumptions!$C$77,D$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,D$34)-MAX(Assumptions!$C$78,D$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,D$34)-MAX(Assumptions!$C$79,D$33),0)</f>
         <v/>
       </c>
       <c r="E63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,E$34)-MAX(Assumptions!$C$74,E$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,E$34)-MAX(Assumptions!$C$75,E$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,E$34)-MAX(Assumptions!$C$76,E$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,E$34)-MAX(Assumptions!$C$77,E$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,E$34)-MAX(Assumptions!$C$76,E$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,E$34)-MAX(Assumptions!$C$77,E$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,E$34)-MAX(Assumptions!$C$78,E$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,E$34)-MAX(Assumptions!$C$79,E$33),0)</f>
         <v/>
       </c>
       <c r="F63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,F$34)-MAX(Assumptions!$C$74,F$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,F$34)-MAX(Assumptions!$C$75,F$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,F$34)-MAX(Assumptions!$C$76,F$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,F$34)-MAX(Assumptions!$C$77,F$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,F$34)-MAX(Assumptions!$C$76,F$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,F$34)-MAX(Assumptions!$C$77,F$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,F$34)-MAX(Assumptions!$C$78,F$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,F$34)-MAX(Assumptions!$C$79,F$33),0)</f>
         <v/>
       </c>
       <c r="G63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,G$34)-MAX(Assumptions!$C$74,G$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,G$34)-MAX(Assumptions!$C$75,G$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,G$34)-MAX(Assumptions!$C$76,G$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,G$34)-MAX(Assumptions!$C$77,G$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,G$34)-MAX(Assumptions!$C$76,G$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,G$34)-MAX(Assumptions!$C$77,G$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,G$34)-MAX(Assumptions!$C$78,G$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,G$34)-MAX(Assumptions!$C$79,G$33),0)</f>
         <v/>
       </c>
       <c r="H63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,H$34)-MAX(Assumptions!$C$74,H$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,H$34)-MAX(Assumptions!$C$75,H$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,H$34)-MAX(Assumptions!$C$76,H$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,H$34)-MAX(Assumptions!$C$77,H$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,H$34)-MAX(Assumptions!$C$76,H$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,H$34)-MAX(Assumptions!$C$77,H$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,H$34)-MAX(Assumptions!$C$78,H$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,H$34)-MAX(Assumptions!$C$79,H$33),0)</f>
         <v/>
       </c>
       <c r="I63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,I$34)-MAX(Assumptions!$C$74,I$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,I$34)-MAX(Assumptions!$C$75,I$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,I$34)-MAX(Assumptions!$C$76,I$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,I$34)-MAX(Assumptions!$C$77,I$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,I$34)-MAX(Assumptions!$C$76,I$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,I$34)-MAX(Assumptions!$C$77,I$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,I$34)-MAX(Assumptions!$C$78,I$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,I$34)-MAX(Assumptions!$C$79,I$33),0)</f>
         <v/>
       </c>
       <c r="J63" s="33">
-        <f>Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,J$34)-MAX(Assumptions!$C$74,J$33),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,J$34)-MAX(Assumptions!$C$75,J$33),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,J$34)-MAX(Assumptions!$C$76,J$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,J$34)-MAX(Assumptions!$C$77,J$33),0)</f>
+        <f>Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,J$34)-MAX(Assumptions!$C$76,J$33),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,J$34)-MAX(Assumptions!$C$77,J$33),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,J$34)-MAX(Assumptions!$C$78,J$33),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,J$34)-MAX(Assumptions!$C$79,J$33),0)</f>
         <v/>
       </c>
     </row>
@@ -14245,23 +14265,23 @@
         </is>
       </c>
       <c r="B95" s="47">
-        <f>Assumptions!$B$84</f>
+        <f>Assumptions!$B$86</f>
         <v/>
       </c>
       <c r="C95" s="47">
-        <f>Assumptions!$C$84</f>
+        <f>Assumptions!$C$86</f>
         <v/>
       </c>
       <c r="D95" s="47">
-        <f>Assumptions!$D$84</f>
+        <f>Assumptions!$D$86</f>
         <v/>
       </c>
       <c r="E95" s="47">
-        <f>Assumptions!$E$84</f>
+        <f>Assumptions!$E$86</f>
         <v/>
       </c>
       <c r="F95" s="47">
-        <f>Assumptions!$F$84</f>
+        <f>Assumptions!$F$86</f>
         <v/>
       </c>
     </row>
@@ -14272,23 +14292,23 @@
         </is>
       </c>
       <c r="B96" s="47">
-        <f>Assumptions!$B$85</f>
+        <f>Assumptions!$B$87</f>
         <v/>
       </c>
       <c r="C96" s="47">
-        <f>Assumptions!$C$85</f>
+        <f>Assumptions!$C$87</f>
         <v/>
       </c>
       <c r="D96" s="47">
-        <f>Assumptions!$D$85</f>
+        <f>Assumptions!$D$87</f>
         <v/>
       </c>
       <c r="E96" s="47">
-        <f>Assumptions!$E$85</f>
+        <f>Assumptions!$E$87</f>
         <v/>
       </c>
       <c r="F96" s="47">
-        <f>Assumptions!$F$85</f>
+        <f>Assumptions!$F$87</f>
         <v/>
       </c>
     </row>
@@ -14412,23 +14432,23 @@
         </is>
       </c>
       <c r="B102" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,B$96)-MAX(Assumptions!$C$66,B$95),0)+MAX(MIN(Assumptions!$D$67,B$96)-MAX(Assumptions!$C$67,B$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,B$96)-MAX(Assumptions!$C$68,B$95),0)+MAX(MIN(Assumptions!$D$69,B$96)-MAX(Assumptions!$C$69,B$95),0)</f>
         <v/>
       </c>
       <c r="C102" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,C$96)-MAX(Assumptions!$C$66,C$95),0)+MAX(MIN(Assumptions!$D$67,C$96)-MAX(Assumptions!$C$67,C$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,C$96)-MAX(Assumptions!$C$68,C$95),0)+MAX(MIN(Assumptions!$D$69,C$96)-MAX(Assumptions!$C$69,C$95),0)</f>
         <v/>
       </c>
       <c r="D102" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,D$96)-MAX(Assumptions!$C$66,D$95),0)+MAX(MIN(Assumptions!$D$67,D$96)-MAX(Assumptions!$C$67,D$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,D$96)-MAX(Assumptions!$C$68,D$95),0)+MAX(MIN(Assumptions!$D$69,D$96)-MAX(Assumptions!$C$69,D$95),0)</f>
         <v/>
       </c>
       <c r="E102" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,E$96)-MAX(Assumptions!$C$66,E$95),0)+MAX(MIN(Assumptions!$D$67,E$96)-MAX(Assumptions!$C$67,E$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,E$96)-MAX(Assumptions!$C$68,E$95),0)+MAX(MIN(Assumptions!$D$69,E$96)-MAX(Assumptions!$C$69,E$95),0)</f>
         <v/>
       </c>
       <c r="F102" s="33">
-        <f>MAX(MIN(Assumptions!$D$66,F$96)-MAX(Assumptions!$C$66,F$95),0)+MAX(MIN(Assumptions!$D$67,F$96)-MAX(Assumptions!$C$67,F$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$68,F$96)-MAX(Assumptions!$C$68,F$95),0)+MAX(MIN(Assumptions!$D$69,F$96)-MAX(Assumptions!$C$69,F$95),0)</f>
         <v/>
       </c>
     </row>
@@ -14439,23 +14459,23 @@
         </is>
       </c>
       <c r="B103" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,B$96)-MAX(Assumptions!$C$68,B$95),0)+MAX(MIN(Assumptions!$D$69,B$96)-MAX(Assumptions!$C$69,B$95),0)+MAX(MIN(Assumptions!$D$70,B$96)-MAX(Assumptions!$C$70,B$95),0)+MAX(MIN(Assumptions!$D$71,B$96)-MAX(Assumptions!$C$71,B$95),0)+MAX(MIN(Assumptions!$D$72,B$96)-MAX(Assumptions!$C$72,B$95),0)+MAX(MIN(Assumptions!$D$73,B$96)-MAX(Assumptions!$C$73,B$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,B$96)-MAX(Assumptions!$C$70,B$95),0)+MAX(MIN(Assumptions!$D$71,B$96)-MAX(Assumptions!$C$71,B$95),0)+MAX(MIN(Assumptions!$D$72,B$96)-MAX(Assumptions!$C$72,B$95),0)+MAX(MIN(Assumptions!$D$73,B$96)-MAX(Assumptions!$C$73,B$95),0)+MAX(MIN(Assumptions!$D$74,B$96)-MAX(Assumptions!$C$74,B$95),0)+MAX(MIN(Assumptions!$D$75,B$96)-MAX(Assumptions!$C$75,B$95),0)</f>
         <v/>
       </c>
       <c r="C103" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,C$96)-MAX(Assumptions!$C$68,C$95),0)+MAX(MIN(Assumptions!$D$69,C$96)-MAX(Assumptions!$C$69,C$95),0)+MAX(MIN(Assumptions!$D$70,C$96)-MAX(Assumptions!$C$70,C$95),0)+MAX(MIN(Assumptions!$D$71,C$96)-MAX(Assumptions!$C$71,C$95),0)+MAX(MIN(Assumptions!$D$72,C$96)-MAX(Assumptions!$C$72,C$95),0)+MAX(MIN(Assumptions!$D$73,C$96)-MAX(Assumptions!$C$73,C$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,C$96)-MAX(Assumptions!$C$70,C$95),0)+MAX(MIN(Assumptions!$D$71,C$96)-MAX(Assumptions!$C$71,C$95),0)+MAX(MIN(Assumptions!$D$72,C$96)-MAX(Assumptions!$C$72,C$95),0)+MAX(MIN(Assumptions!$D$73,C$96)-MAX(Assumptions!$C$73,C$95),0)+MAX(MIN(Assumptions!$D$74,C$96)-MAX(Assumptions!$C$74,C$95),0)+MAX(MIN(Assumptions!$D$75,C$96)-MAX(Assumptions!$C$75,C$95),0)</f>
         <v/>
       </c>
       <c r="D103" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,D$96)-MAX(Assumptions!$C$68,D$95),0)+MAX(MIN(Assumptions!$D$69,D$96)-MAX(Assumptions!$C$69,D$95),0)+MAX(MIN(Assumptions!$D$70,D$96)-MAX(Assumptions!$C$70,D$95),0)+MAX(MIN(Assumptions!$D$71,D$96)-MAX(Assumptions!$C$71,D$95),0)+MAX(MIN(Assumptions!$D$72,D$96)-MAX(Assumptions!$C$72,D$95),0)+MAX(MIN(Assumptions!$D$73,D$96)-MAX(Assumptions!$C$73,D$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,D$96)-MAX(Assumptions!$C$70,D$95),0)+MAX(MIN(Assumptions!$D$71,D$96)-MAX(Assumptions!$C$71,D$95),0)+MAX(MIN(Assumptions!$D$72,D$96)-MAX(Assumptions!$C$72,D$95),0)+MAX(MIN(Assumptions!$D$73,D$96)-MAX(Assumptions!$C$73,D$95),0)+MAX(MIN(Assumptions!$D$74,D$96)-MAX(Assumptions!$C$74,D$95),0)+MAX(MIN(Assumptions!$D$75,D$96)-MAX(Assumptions!$C$75,D$95),0)</f>
         <v/>
       </c>
       <c r="E103" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,E$96)-MAX(Assumptions!$C$68,E$95),0)+MAX(MIN(Assumptions!$D$69,E$96)-MAX(Assumptions!$C$69,E$95),0)+MAX(MIN(Assumptions!$D$70,E$96)-MAX(Assumptions!$C$70,E$95),0)+MAX(MIN(Assumptions!$D$71,E$96)-MAX(Assumptions!$C$71,E$95),0)+MAX(MIN(Assumptions!$D$72,E$96)-MAX(Assumptions!$C$72,E$95),0)+MAX(MIN(Assumptions!$D$73,E$96)-MAX(Assumptions!$C$73,E$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,E$96)-MAX(Assumptions!$C$70,E$95),0)+MAX(MIN(Assumptions!$D$71,E$96)-MAX(Assumptions!$C$71,E$95),0)+MAX(MIN(Assumptions!$D$72,E$96)-MAX(Assumptions!$C$72,E$95),0)+MAX(MIN(Assumptions!$D$73,E$96)-MAX(Assumptions!$C$73,E$95),0)+MAX(MIN(Assumptions!$D$74,E$96)-MAX(Assumptions!$C$74,E$95),0)+MAX(MIN(Assumptions!$D$75,E$96)-MAX(Assumptions!$C$75,E$95),0)</f>
         <v/>
       </c>
       <c r="F103" s="33">
-        <f>MAX(MIN(Assumptions!$D$68,F$96)-MAX(Assumptions!$C$68,F$95),0)+MAX(MIN(Assumptions!$D$69,F$96)-MAX(Assumptions!$C$69,F$95),0)+MAX(MIN(Assumptions!$D$70,F$96)-MAX(Assumptions!$C$70,F$95),0)+MAX(MIN(Assumptions!$D$71,F$96)-MAX(Assumptions!$C$71,F$95),0)+MAX(MIN(Assumptions!$D$72,F$96)-MAX(Assumptions!$C$72,F$95),0)+MAX(MIN(Assumptions!$D$73,F$96)-MAX(Assumptions!$C$73,F$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$70,F$96)-MAX(Assumptions!$C$70,F$95),0)+MAX(MIN(Assumptions!$D$71,F$96)-MAX(Assumptions!$C$71,F$95),0)+MAX(MIN(Assumptions!$D$72,F$96)-MAX(Assumptions!$C$72,F$95),0)+MAX(MIN(Assumptions!$D$73,F$96)-MAX(Assumptions!$C$73,F$95),0)+MAX(MIN(Assumptions!$D$74,F$96)-MAX(Assumptions!$C$74,F$95),0)+MAX(MIN(Assumptions!$D$75,F$96)-MAX(Assumptions!$C$75,F$95),0)</f>
         <v/>
       </c>
     </row>
@@ -14466,23 +14486,23 @@
         </is>
       </c>
       <c r="B104" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,B$96)-MAX(Assumptions!$C$74,B$95),0)+MAX(MIN(Assumptions!$D$75,B$96)-MAX(Assumptions!$C$75,B$95),0)+MAX(MIN(Assumptions!$D$76,B$96)-MAX(Assumptions!$C$76,B$95),0)+MAX(MIN(Assumptions!$D$77,B$96)-MAX(Assumptions!$C$77,B$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,B$96)-MAX(Assumptions!$C$76,B$95),0)+MAX(MIN(Assumptions!$D$77,B$96)-MAX(Assumptions!$C$77,B$95),0)+MAX(MIN(Assumptions!$D$78,B$96)-MAX(Assumptions!$C$78,B$95),0)+MAX(MIN(Assumptions!$D$79,B$96)-MAX(Assumptions!$C$79,B$95),0)</f>
         <v/>
       </c>
       <c r="C104" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,C$96)-MAX(Assumptions!$C$74,C$95),0)+MAX(MIN(Assumptions!$D$75,C$96)-MAX(Assumptions!$C$75,C$95),0)+MAX(MIN(Assumptions!$D$76,C$96)-MAX(Assumptions!$C$76,C$95),0)+MAX(MIN(Assumptions!$D$77,C$96)-MAX(Assumptions!$C$77,C$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,C$96)-MAX(Assumptions!$C$76,C$95),0)+MAX(MIN(Assumptions!$D$77,C$96)-MAX(Assumptions!$C$77,C$95),0)+MAX(MIN(Assumptions!$D$78,C$96)-MAX(Assumptions!$C$78,C$95),0)+MAX(MIN(Assumptions!$D$79,C$96)-MAX(Assumptions!$C$79,C$95),0)</f>
         <v/>
       </c>
       <c r="D104" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,D$96)-MAX(Assumptions!$C$74,D$95),0)+MAX(MIN(Assumptions!$D$75,D$96)-MAX(Assumptions!$C$75,D$95),0)+MAX(MIN(Assumptions!$D$76,D$96)-MAX(Assumptions!$C$76,D$95),0)+MAX(MIN(Assumptions!$D$77,D$96)-MAX(Assumptions!$C$77,D$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,D$96)-MAX(Assumptions!$C$76,D$95),0)+MAX(MIN(Assumptions!$D$77,D$96)-MAX(Assumptions!$C$77,D$95),0)+MAX(MIN(Assumptions!$D$78,D$96)-MAX(Assumptions!$C$78,D$95),0)+MAX(MIN(Assumptions!$D$79,D$96)-MAX(Assumptions!$C$79,D$95),0)</f>
         <v/>
       </c>
       <c r="E104" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,E$96)-MAX(Assumptions!$C$74,E$95),0)+MAX(MIN(Assumptions!$D$75,E$96)-MAX(Assumptions!$C$75,E$95),0)+MAX(MIN(Assumptions!$D$76,E$96)-MAX(Assumptions!$C$76,E$95),0)+MAX(MIN(Assumptions!$D$77,E$96)-MAX(Assumptions!$C$77,E$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,E$96)-MAX(Assumptions!$C$76,E$95),0)+MAX(MIN(Assumptions!$D$77,E$96)-MAX(Assumptions!$C$77,E$95),0)+MAX(MIN(Assumptions!$D$78,E$96)-MAX(Assumptions!$C$78,E$95),0)+MAX(MIN(Assumptions!$D$79,E$96)-MAX(Assumptions!$C$79,E$95),0)</f>
         <v/>
       </c>
       <c r="F104" s="33">
-        <f>MAX(MIN(Assumptions!$D$74,F$96)-MAX(Assumptions!$C$74,F$95),0)+MAX(MIN(Assumptions!$D$75,F$96)-MAX(Assumptions!$C$75,F$95),0)+MAX(MIN(Assumptions!$D$76,F$96)-MAX(Assumptions!$C$76,F$95),0)+MAX(MIN(Assumptions!$D$77,F$96)-MAX(Assumptions!$C$77,F$95),0)</f>
+        <f>MAX(MIN(Assumptions!$D$76,F$96)-MAX(Assumptions!$C$76,F$95),0)+MAX(MIN(Assumptions!$D$77,F$96)-MAX(Assumptions!$C$77,F$95),0)+MAX(MIN(Assumptions!$D$78,F$96)-MAX(Assumptions!$C$78,F$95),0)+MAX(MIN(Assumptions!$D$79,F$96)-MAX(Assumptions!$C$79,F$95),0)</f>
         <v/>
       </c>
     </row>
@@ -14579,23 +14599,23 @@
         </is>
       </c>
       <c r="B109" s="33">
-        <f>(Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,B$96)-MAX(Assumptions!$C$66,B$95),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,B$96)-MAX(Assumptions!$C$67,B$95),0))/1000</f>
+        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,B$96)-MAX(Assumptions!$C$68,B$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,B$96)-MAX(Assumptions!$C$69,B$95),0))/1000</f>
         <v/>
       </c>
       <c r="C109" s="33">
-        <f>(Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,C$96)-MAX(Assumptions!$C$66,C$95),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,C$96)-MAX(Assumptions!$C$67,C$95),0))/1000</f>
+        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,C$96)-MAX(Assumptions!$C$68,C$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,C$96)-MAX(Assumptions!$C$69,C$95),0))/1000</f>
         <v/>
       </c>
       <c r="D109" s="33">
-        <f>(Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,D$96)-MAX(Assumptions!$C$66,D$95),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,D$96)-MAX(Assumptions!$C$67,D$95),0))/1000</f>
+        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,D$96)-MAX(Assumptions!$C$68,D$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,D$96)-MAX(Assumptions!$C$69,D$95),0))/1000</f>
         <v/>
       </c>
       <c r="E109" s="33">
-        <f>(Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,E$96)-MAX(Assumptions!$C$66,E$95),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,E$96)-MAX(Assumptions!$C$67,E$95),0))/1000</f>
+        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,E$96)-MAX(Assumptions!$C$68,E$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,E$96)-MAX(Assumptions!$C$69,E$95),0))/1000</f>
         <v/>
       </c>
       <c r="F109" s="33">
-        <f>(Assumptions!$B$66*MAX(MIN(Assumptions!$D$66,F$96)-MAX(Assumptions!$C$66,F$95),0)+Assumptions!$B$67*MAX(MIN(Assumptions!$D$67,F$96)-MAX(Assumptions!$C$67,F$95),0))/1000</f>
+        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,F$96)-MAX(Assumptions!$C$68,F$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,F$96)-MAX(Assumptions!$C$69,F$95),0))/1000</f>
         <v/>
       </c>
     </row>
@@ -14606,23 +14626,23 @@
         </is>
       </c>
       <c r="B110" s="33">
-        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,B$96)-MAX(Assumptions!$C$68,B$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,B$96)-MAX(Assumptions!$C$69,B$95),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,B$96)-MAX(Assumptions!$C$70,B$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,B$96)-MAX(Assumptions!$C$71,B$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,B$96)-MAX(Assumptions!$C$72,B$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,B$96)-MAX(Assumptions!$C$73,B$95),0))/1000</f>
+        <f>(Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,B$96)-MAX(Assumptions!$C$70,B$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,B$96)-MAX(Assumptions!$C$71,B$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,B$96)-MAX(Assumptions!$C$72,B$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,B$96)-MAX(Assumptions!$C$73,B$95),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,B$96)-MAX(Assumptions!$C$74,B$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,B$96)-MAX(Assumptions!$C$75,B$95),0))/1000</f>
         <v/>
       </c>
       <c r="C110" s="33">
-        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,C$96)-MAX(Assumptions!$C$68,C$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,C$96)-MAX(Assumptions!$C$69,C$95),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,C$96)-MAX(Assumptions!$C$70,C$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,C$96)-MAX(Assumptions!$C$71,C$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,C$96)-MAX(Assumptions!$C$72,C$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,C$96)-MAX(Assumptions!$C$73,C$95),0))/1000</f>
+        <f>(Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,C$96)-MAX(Assumptions!$C$70,C$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,C$96)-MAX(Assumptions!$C$71,C$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,C$96)-MAX(Assumptions!$C$72,C$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,C$96)-MAX(Assumptions!$C$73,C$95),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,C$96)-MAX(Assumptions!$C$74,C$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,C$96)-MAX(Assumptions!$C$75,C$95),0))/1000</f>
         <v/>
       </c>
       <c r="D110" s="33">
-        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,D$96)-MAX(Assumptions!$C$68,D$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,D$96)-MAX(Assumptions!$C$69,D$95),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,D$96)-MAX(Assumptions!$C$70,D$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,D$96)-MAX(Assumptions!$C$71,D$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,D$96)-MAX(Assumptions!$C$72,D$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,D$96)-MAX(Assumptions!$C$73,D$95),0))/1000</f>
+        <f>(Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,D$96)-MAX(Assumptions!$C$70,D$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,D$96)-MAX(Assumptions!$C$71,D$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,D$96)-MAX(Assumptions!$C$72,D$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,D$96)-MAX(Assumptions!$C$73,D$95),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,D$96)-MAX(Assumptions!$C$74,D$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,D$96)-MAX(Assumptions!$C$75,D$95),0))/1000</f>
         <v/>
       </c>
       <c r="E110" s="33">
-        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,E$96)-MAX(Assumptions!$C$68,E$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,E$96)-MAX(Assumptions!$C$69,E$95),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,E$96)-MAX(Assumptions!$C$70,E$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,E$96)-MAX(Assumptions!$C$71,E$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,E$96)-MAX(Assumptions!$C$72,E$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,E$96)-MAX(Assumptions!$C$73,E$95),0))/1000</f>
+        <f>(Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,E$96)-MAX(Assumptions!$C$70,E$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,E$96)-MAX(Assumptions!$C$71,E$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,E$96)-MAX(Assumptions!$C$72,E$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,E$96)-MAX(Assumptions!$C$73,E$95),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,E$96)-MAX(Assumptions!$C$74,E$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,E$96)-MAX(Assumptions!$C$75,E$95),0))/1000</f>
         <v/>
       </c>
       <c r="F110" s="33">
-        <f>(Assumptions!$B$68*MAX(MIN(Assumptions!$D$68,F$96)-MAX(Assumptions!$C$68,F$95),0)+Assumptions!$B$69*MAX(MIN(Assumptions!$D$69,F$96)-MAX(Assumptions!$C$69,F$95),0)+Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,F$96)-MAX(Assumptions!$C$70,F$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,F$96)-MAX(Assumptions!$C$71,F$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,F$96)-MAX(Assumptions!$C$72,F$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,F$96)-MAX(Assumptions!$C$73,F$95),0))/1000</f>
+        <f>(Assumptions!$B$70*MAX(MIN(Assumptions!$D$70,F$96)-MAX(Assumptions!$C$70,F$95),0)+Assumptions!$B$71*MAX(MIN(Assumptions!$D$71,F$96)-MAX(Assumptions!$C$71,F$95),0)+Assumptions!$B$72*MAX(MIN(Assumptions!$D$72,F$96)-MAX(Assumptions!$C$72,F$95),0)+Assumptions!$B$73*MAX(MIN(Assumptions!$D$73,F$96)-MAX(Assumptions!$C$73,F$95),0)+Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,F$96)-MAX(Assumptions!$C$74,F$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,F$96)-MAX(Assumptions!$C$75,F$95),0))/1000</f>
         <v/>
       </c>
     </row>
@@ -14633,23 +14653,23 @@
         </is>
       </c>
       <c r="B111" s="33">
-        <f>(Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,B$96)-MAX(Assumptions!$C$74,B$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,B$96)-MAX(Assumptions!$C$75,B$95),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,B$96)-MAX(Assumptions!$C$76,B$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,B$96)-MAX(Assumptions!$C$77,B$95),0))/1000</f>
+        <f>(Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,B$96)-MAX(Assumptions!$C$76,B$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,B$96)-MAX(Assumptions!$C$77,B$95),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,B$96)-MAX(Assumptions!$C$78,B$95),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,B$96)-MAX(Assumptions!$C$79,B$95),0))/1000</f>
         <v/>
       </c>
       <c r="C111" s="33">
-        <f>(Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,C$96)-MAX(Assumptions!$C$74,C$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,C$96)-MAX(Assumptions!$C$75,C$95),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,C$96)-MAX(Assumptions!$C$76,C$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,C$96)-MAX(Assumptions!$C$77,C$95),0))/1000</f>
+        <f>(Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,C$96)-MAX(Assumptions!$C$76,C$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,C$96)-MAX(Assumptions!$C$77,C$95),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,C$96)-MAX(Assumptions!$C$78,C$95),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,C$96)-MAX(Assumptions!$C$79,C$95),0))/1000</f>
         <v/>
       </c>
       <c r="D111" s="33">
-        <f>(Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,D$96)-MAX(Assumptions!$C$74,D$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,D$96)-MAX(Assumptions!$C$75,D$95),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,D$96)-MAX(Assumptions!$C$76,D$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,D$96)-MAX(Assumptions!$C$77,D$95),0))/1000</f>
+        <f>(Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,D$96)-MAX(Assumptions!$C$76,D$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,D$96)-MAX(Assumptions!$C$77,D$95),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,D$96)-MAX(Assumptions!$C$78,D$95),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,D$96)-MAX(Assumptions!$C$79,D$95),0))/1000</f>
         <v/>
       </c>
       <c r="E111" s="33">
-        <f>(Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,E$96)-MAX(Assumptions!$C$74,E$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,E$96)-MAX(Assumptions!$C$75,E$95),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,E$96)-MAX(Assumptions!$C$76,E$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,E$96)-MAX(Assumptions!$C$77,E$95),0))/1000</f>
+        <f>(Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,E$96)-MAX(Assumptions!$C$76,E$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,E$96)-MAX(Assumptions!$C$77,E$95),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,E$96)-MAX(Assumptions!$C$78,E$95),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,E$96)-MAX(Assumptions!$C$79,E$95),0))/1000</f>
         <v/>
       </c>
       <c r="F111" s="33">
-        <f>(Assumptions!$B$74*MAX(MIN(Assumptions!$D$74,F$96)-MAX(Assumptions!$C$74,F$95),0)+Assumptions!$B$75*MAX(MIN(Assumptions!$D$75,F$96)-MAX(Assumptions!$C$75,F$95),0)+Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,F$96)-MAX(Assumptions!$C$76,F$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,F$96)-MAX(Assumptions!$C$77,F$95),0))/1000</f>
+        <f>(Assumptions!$B$76*MAX(MIN(Assumptions!$D$76,F$96)-MAX(Assumptions!$C$76,F$95),0)+Assumptions!$B$77*MAX(MIN(Assumptions!$D$77,F$96)-MAX(Assumptions!$C$77,F$95),0)+Assumptions!$B$78*MAX(MIN(Assumptions!$D$78,F$96)-MAX(Assumptions!$C$78,F$95),0)+Assumptions!$B$79*MAX(MIN(Assumptions!$D$79,F$96)-MAX(Assumptions!$C$79,F$95),0))/1000</f>
         <v/>
       </c>
     </row>
@@ -15287,7 +15307,7 @@
         </is>
       </c>
       <c r="B142" s="20">
-        <f>Assumptions!$C$117</f>
+        <f>Assumptions!$C$119</f>
         <v/>
       </c>
     </row>
@@ -15320,23 +15340,23 @@
         </is>
       </c>
       <c r="B146" s="50">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$99)*184/365</f>
+        <f>Assumptions!$C$99*(1+Assumptions!$C$101)*184/365</f>
         <v/>
       </c>
       <c r="C146" s="50">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)</f>
+        <f>Assumptions!$C$99*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
         <v/>
       </c>
       <c r="D146" s="50">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)</f>
+        <f>Assumptions!$C$99*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
         <v/>
       </c>
       <c r="E146" s="50">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
+        <f>Assumptions!$C$99*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)</f>
         <v/>
       </c>
       <c r="F146" s="50">
-        <f>Assumptions!$C$97*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
+        <f>Assumptions!$C$99*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)*(1+Assumptions!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -15347,23 +15367,23 @@
         </is>
       </c>
       <c r="B147" s="33">
-        <f>Assumptions!$C$98*(B134+B135)</f>
+        <f>Assumptions!$C$100*(B134+B135)</f>
         <v/>
       </c>
       <c r="C147" s="33">
-        <f>Assumptions!$C$98*C136</f>
+        <f>Assumptions!$C$100*C136</f>
         <v/>
       </c>
       <c r="D147" s="33">
-        <f>Assumptions!$C$98*D136</f>
+        <f>Assumptions!$C$100*D136</f>
         <v/>
       </c>
       <c r="E147" s="33">
-        <f>Assumptions!$C$98*E136</f>
+        <f>Assumptions!$C$100*E136</f>
         <v/>
       </c>
       <c r="F147" s="33">
-        <f>Assumptions!$C$98*F136</f>
+        <f>Assumptions!$C$100*F136</f>
         <v/>
       </c>
     </row>
@@ -15374,23 +15394,23 @@
         </is>
       </c>
       <c r="B148" s="42">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="C148" s="42">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="D148" s="42">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="E148" s="42">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
       <c r="F148" s="42">
-        <f>Assumptions!$C$104</f>
+        <f>Assumptions!$C$106</f>
         <v/>
       </c>
     </row>
@@ -15401,7 +15421,7 @@
         </is>
       </c>
       <c r="B149" s="38">
-        <f>Assumptions!$C$110+(B134+B135)*B148</f>
+        <f>Assumptions!$C$112+(B134+B135)*B148</f>
         <v/>
       </c>
       <c r="C149" s="38">
@@ -15428,7 +15448,7 @@
         </is>
       </c>
       <c r="B150" s="38">
-        <f>Assumptions!$C$117+(B134+B135)*B148-B146-B147</f>
+        <f>Assumptions!$C$119+(B134+B135)*B148-B146-B147</f>
         <v/>
       </c>
       <c r="C150" s="38">
@@ -15467,7 +15487,7 @@
         </is>
       </c>
       <c r="B153" s="19">
-        <f>Assumptions!$C$123</f>
+        <f>Assumptions!$C$125</f>
         <v/>
       </c>
     </row>
@@ -15500,23 +15520,23 @@
         </is>
       </c>
       <c r="B157" s="51">
-        <f>Assumptions!$B$131</f>
+        <f>Assumptions!$B$133</f>
         <v/>
       </c>
       <c r="C157" s="51">
-        <f>Assumptions!$C$131</f>
+        <f>Assumptions!$C$133</f>
         <v/>
       </c>
       <c r="D157" s="51">
-        <f>Assumptions!$D$131</f>
+        <f>Assumptions!$D$133</f>
         <v/>
       </c>
       <c r="E157" s="51">
-        <f>Assumptions!$E$131</f>
+        <f>Assumptions!$E$133</f>
         <v/>
       </c>
       <c r="F157" s="51">
-        <f>Assumptions!$F$131</f>
+        <f>Assumptions!$F$133</f>
         <v/>
       </c>
     </row>
@@ -15527,23 +15547,23 @@
         </is>
       </c>
       <c r="B158" s="19">
-        <f>Assumptions!$B$132</f>
+        <f>Assumptions!$B$134</f>
         <v/>
       </c>
       <c r="C158" s="19">
-        <f>Assumptions!$C$132</f>
+        <f>Assumptions!$C$134</f>
         <v/>
       </c>
       <c r="D158" s="19">
-        <f>Assumptions!$D$132</f>
+        <f>Assumptions!$D$134</f>
         <v/>
       </c>
       <c r="E158" s="19">
-        <f>Assumptions!$E$132</f>
+        <f>Assumptions!$E$134</f>
         <v/>
       </c>
       <c r="F158" s="19">
-        <f>Assumptions!$F$132</f>
+        <f>Assumptions!$F$134</f>
         <v/>
       </c>
     </row>
@@ -15554,23 +15574,23 @@
         </is>
       </c>
       <c r="B159" s="52">
-        <f>Assumptions!$B$133</f>
+        <f>Assumptions!$B$135</f>
         <v/>
       </c>
       <c r="C159" s="52">
-        <f>Assumptions!$C$133</f>
+        <f>Assumptions!$C$135</f>
         <v/>
       </c>
       <c r="D159" s="52">
-        <f>Assumptions!$D$133</f>
+        <f>Assumptions!$D$135</f>
         <v/>
       </c>
       <c r="E159" s="52">
-        <f>Assumptions!$E$133</f>
+        <f>Assumptions!$E$135</f>
         <v/>
       </c>
       <c r="F159" s="52">
-        <f>Assumptions!$F$133</f>
+        <f>Assumptions!$F$135</f>
         <v/>
       </c>
     </row>
@@ -15581,23 +15601,23 @@
         </is>
       </c>
       <c r="B160" s="33">
-        <f>Assumptions!$C$125*(1+Assumptions!$C$99)</f>
+        <f>Assumptions!$C$127*(1+Assumptions!$C$101)</f>
         <v/>
       </c>
       <c r="C160" s="33">
-        <f>Assumptions!$C$125*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)</f>
+        <f>Assumptions!$C$127*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
         <v/>
       </c>
       <c r="D160" s="33">
-        <f>Assumptions!$C$125*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)</f>
+        <f>Assumptions!$C$127*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
         <v/>
       </c>
       <c r="E160" s="33">
-        <f>Assumptions!$C$125*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
+        <f>Assumptions!$C$127*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)</f>
         <v/>
       </c>
       <c r="F160" s="33">
-        <f>Assumptions!$C$125*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
+        <f>Assumptions!$C$127*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)*(1+Assumptions!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -15608,7 +15628,7 @@
         </is>
       </c>
       <c r="B161" s="33">
-        <f>Assumptions!$C$111+(B159*2-Assumptions!$C$124)*184*B160/1000</f>
+        <f>Assumptions!$C$113+(B159*2-Assumptions!$C$126)*184*B160/1000</f>
         <v/>
       </c>
       <c r="C161" s="33">
@@ -15635,23 +15655,23 @@
         </is>
       </c>
       <c r="B162" s="8">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$128</f>
         <v/>
       </c>
       <c r="C162" s="8">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$128</f>
         <v/>
       </c>
       <c r="D162" s="8">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$128</f>
         <v/>
       </c>
       <c r="E162" s="8">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$128</f>
         <v/>
       </c>
       <c r="F162" s="8">
-        <f>Assumptions!$C$126</f>
+        <f>Assumptions!$C$128</f>
         <v/>
       </c>
     </row>
@@ -15662,7 +15682,7 @@
         </is>
       </c>
       <c r="B163" s="33">
-        <f>Assumptions!$C$118+(B161-Assumptions!$C$111)*B162</f>
+        <f>Assumptions!$C$120+(B161-Assumptions!$C$113)*B162</f>
         <v/>
       </c>
       <c r="C163" s="33">
@@ -15689,23 +15709,23 @@
         </is>
       </c>
       <c r="B164" s="33">
-        <f>-Assumptions!$C$127*(1+Assumptions!$C$99)</f>
+        <f>-Assumptions!$C$129*(1+Assumptions!$C$101)</f>
         <v/>
       </c>
       <c r="C164" s="33">
-        <f>-Assumptions!$C$127*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)</f>
+        <f>-Assumptions!$C$129*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
         <v/>
       </c>
       <c r="D164" s="33">
-        <f>-Assumptions!$C$127*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)</f>
+        <f>-Assumptions!$C$129*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
         <v/>
       </c>
       <c r="E164" s="33">
-        <f>-Assumptions!$C$127*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
+        <f>-Assumptions!$C$129*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)</f>
         <v/>
       </c>
       <c r="F164" s="33">
-        <f>-Assumptions!$C$127*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
+        <f>-Assumptions!$C$129*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)*(1+Assumptions!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -15775,23 +15795,23 @@
         </is>
       </c>
       <c r="B168" s="20">
-        <f>Assumptions!$B$136</f>
+        <f>Assumptions!$B$138</f>
         <v/>
       </c>
       <c r="C168" s="20">
-        <f>Assumptions!$C$136</f>
+        <f>Assumptions!$C$138</f>
         <v/>
       </c>
       <c r="D168" s="20">
-        <f>Assumptions!$D$136</f>
+        <f>Assumptions!$D$138</f>
         <v/>
       </c>
       <c r="E168" s="20">
-        <f>Assumptions!$E$136</f>
+        <f>Assumptions!$E$138</f>
         <v/>
       </c>
       <c r="F168" s="20">
-        <f>Assumptions!$F$136</f>
+        <f>Assumptions!$F$138</f>
         <v/>
       </c>
     </row>
@@ -15802,23 +15822,23 @@
         </is>
       </c>
       <c r="B169" s="33">
-        <f>Assumptions!$C$114+(B168-Assumptions!$C$107)*Assumptions!$B$137</f>
+        <f>Assumptions!$C$116+(B168-Assumptions!$C$109)*Assumptions!$B$139</f>
         <v/>
       </c>
       <c r="C169" s="33">
-        <f>C168*Assumptions!$C$137</f>
+        <f>C168*Assumptions!$C$139</f>
         <v/>
       </c>
       <c r="D169" s="33">
-        <f>D168*Assumptions!$D$137</f>
+        <f>D168*Assumptions!$D$139</f>
         <v/>
       </c>
       <c r="E169" s="33">
-        <f>E168*Assumptions!$E$137</f>
+        <f>E168*Assumptions!$E$139</f>
         <v/>
       </c>
       <c r="F169" s="33">
-        <f>F168*Assumptions!$F$137</f>
+        <f>F168*Assumptions!$F$139</f>
         <v/>
       </c>
     </row>
@@ -15829,23 +15849,23 @@
         </is>
       </c>
       <c r="B170" s="20">
-        <f>Assumptions!$B$138</f>
+        <f>Assumptions!$B$140</f>
         <v/>
       </c>
       <c r="C170" s="20">
-        <f>Assumptions!$C$138</f>
+        <f>Assumptions!$C$140</f>
         <v/>
       </c>
       <c r="D170" s="20">
-        <f>Assumptions!$D$138</f>
+        <f>Assumptions!$D$140</f>
         <v/>
       </c>
       <c r="E170" s="20">
-        <f>Assumptions!$E$138</f>
+        <f>Assumptions!$E$140</f>
         <v/>
       </c>
       <c r="F170" s="20">
-        <f>Assumptions!$F$138</f>
+        <f>Assumptions!$F$140</f>
         <v/>
       </c>
     </row>
@@ -15856,23 +15876,23 @@
         </is>
       </c>
       <c r="B171" s="33">
-        <f>Assumptions!$C$115+(B170-Assumptions!$C$108)*Assumptions!$B$139</f>
+        <f>Assumptions!$C$117+(B170-Assumptions!$C$110)*Assumptions!$B$141</f>
         <v/>
       </c>
       <c r="C171" s="33">
-        <f>C170*Assumptions!$C$139</f>
+        <f>C170*Assumptions!$C$141</f>
         <v/>
       </c>
       <c r="D171" s="33">
-        <f>D170*Assumptions!$D$139</f>
+        <f>D170*Assumptions!$D$141</f>
         <v/>
       </c>
       <c r="E171" s="33">
-        <f>E170*Assumptions!$E$139</f>
+        <f>E170*Assumptions!$E$141</f>
         <v/>
       </c>
       <c r="F171" s="33">
-        <f>F170*Assumptions!$F$139</f>
+        <f>F170*Assumptions!$F$141</f>
         <v/>
       </c>
     </row>
@@ -15883,23 +15903,23 @@
         </is>
       </c>
       <c r="B172" s="20">
-        <f>Assumptions!$B$140</f>
+        <f>Assumptions!$B$142</f>
         <v/>
       </c>
       <c r="C172" s="20">
-        <f>Assumptions!$C$140</f>
+        <f>Assumptions!$C$142</f>
         <v/>
       </c>
       <c r="D172" s="20">
-        <f>Assumptions!$D$140</f>
+        <f>Assumptions!$D$142</f>
         <v/>
       </c>
       <c r="E172" s="20">
-        <f>Assumptions!$E$140</f>
+        <f>Assumptions!$E$142</f>
         <v/>
       </c>
       <c r="F172" s="20">
-        <f>Assumptions!$F$140</f>
+        <f>Assumptions!$F$142</f>
         <v/>
       </c>
     </row>
@@ -15910,23 +15930,23 @@
         </is>
       </c>
       <c r="B173" s="33">
-        <f>Assumptions!$C$116+(B172-Assumptions!$C$109)*Assumptions!$B$141</f>
+        <f>Assumptions!$C$118+(B172-Assumptions!$C$111)*Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="C173" s="33">
-        <f>C172*Assumptions!$C$141</f>
+        <f>C172*Assumptions!$C$143</f>
         <v/>
       </c>
       <c r="D173" s="33">
-        <f>D172*Assumptions!$D$141</f>
+        <f>D172*Assumptions!$D$143</f>
         <v/>
       </c>
       <c r="E173" s="33">
-        <f>E172*Assumptions!$E$141</f>
+        <f>E172*Assumptions!$E$143</f>
         <v/>
       </c>
       <c r="F173" s="33">
-        <f>F172*Assumptions!$F$141</f>
+        <f>F172*Assumptions!$F$143</f>
         <v/>
       </c>
     </row>
@@ -15937,23 +15957,23 @@
         </is>
       </c>
       <c r="B174" s="20">
-        <f>Assumptions!$B$142</f>
+        <f>Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="C174" s="20">
-        <f>Assumptions!$C$142</f>
+        <f>Assumptions!$C$144</f>
         <v/>
       </c>
       <c r="D174" s="20">
-        <f>Assumptions!$D$142</f>
+        <f>Assumptions!$D$144</f>
         <v/>
       </c>
       <c r="E174" s="20">
-        <f>Assumptions!$E$142</f>
+        <f>Assumptions!$E$144</f>
         <v/>
       </c>
       <c r="F174" s="20">
-        <f>Assumptions!$F$142</f>
+        <f>Assumptions!$F$144</f>
         <v/>
       </c>
     </row>
@@ -15964,23 +15984,23 @@
         </is>
       </c>
       <c r="B175" s="33">
-        <f>Assumptions!$C$119+(B174-Assumptions!$C$112)*Assumptions!$B$143</f>
+        <f>Assumptions!$C$121+(B174-Assumptions!$C$114)*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="C175" s="33">
-        <f>C174*Assumptions!$C$143</f>
+        <f>C174*Assumptions!$C$145</f>
         <v/>
       </c>
       <c r="D175" s="33">
-        <f>D174*Assumptions!$D$143</f>
+        <f>D174*Assumptions!$D$145</f>
         <v/>
       </c>
       <c r="E175" s="33">
-        <f>E174*Assumptions!$E$143</f>
+        <f>E174*Assumptions!$E$145</f>
         <v/>
       </c>
       <c r="F175" s="33">
-        <f>F174*Assumptions!$F$143</f>
+        <f>F174*Assumptions!$F$145</f>
         <v/>
       </c>
     </row>
@@ -15991,23 +16011,23 @@
         </is>
       </c>
       <c r="B176" s="20">
-        <f>Assumptions!$B$144</f>
+        <f>Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="C176" s="20">
-        <f>Assumptions!$C$144</f>
+        <f>Assumptions!$C$146</f>
         <v/>
       </c>
       <c r="D176" s="20">
-        <f>Assumptions!$D$144</f>
+        <f>Assumptions!$D$146</f>
         <v/>
       </c>
       <c r="E176" s="20">
-        <f>Assumptions!$E$144</f>
+        <f>Assumptions!$E$146</f>
         <v/>
       </c>
       <c r="F176" s="20">
-        <f>Assumptions!$F$144</f>
+        <f>Assumptions!$F$146</f>
         <v/>
       </c>
     </row>
@@ -16018,23 +16038,23 @@
         </is>
       </c>
       <c r="B177" s="33">
-        <f>Assumptions!$C$120+(B176-Assumptions!$C$113)*Assumptions!$B$145</f>
+        <f>Assumptions!$C$122+(B176-Assumptions!$C$115)*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="C177" s="33">
-        <f>C176*Assumptions!$C$145</f>
+        <f>C176*Assumptions!$C$147</f>
         <v/>
       </c>
       <c r="D177" s="33">
-        <f>D176*Assumptions!$D$145</f>
+        <f>D176*Assumptions!$D$147</f>
         <v/>
       </c>
       <c r="E177" s="33">
-        <f>E176*Assumptions!$E$145</f>
+        <f>E176*Assumptions!$E$147</f>
         <v/>
       </c>
       <c r="F177" s="33">
-        <f>F176*Assumptions!$F$145</f>
+        <f>F176*Assumptions!$F$147</f>
         <v/>
       </c>
     </row>
@@ -16045,23 +16065,23 @@
         </is>
       </c>
       <c r="B178" s="33">
-        <f>-Assumptions!$C$128*(1+Assumptions!$C$99)</f>
+        <f>-Assumptions!$C$130*(1+Assumptions!$C$101)</f>
         <v/>
       </c>
       <c r="C178" s="33">
-        <f>-Assumptions!$C$128*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)</f>
+        <f>-Assumptions!$C$130*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
         <v/>
       </c>
       <c r="D178" s="33">
-        <f>-Assumptions!$C$128*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)</f>
+        <f>-Assumptions!$C$130*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
         <v/>
       </c>
       <c r="E178" s="33">
-        <f>-Assumptions!$C$128*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)</f>
+        <f>-Assumptions!$C$130*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)</f>
         <v/>
       </c>
       <c r="F178" s="33">
-        <f>-Assumptions!$C$128*(1+Assumptions!$C$99)*(1+Assumptions!$C$100)*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)</f>
+        <f>-Assumptions!$C$130*(1+Assumptions!$C$101)*(1+Assumptions!$C$102)*(1+Assumptions!$C$103)*(1+Assumptions!$C$104)*(1+Assumptions!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -16989,7 +17009,7 @@
         </is>
       </c>
       <c r="C8" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
     </row>
@@ -17000,7 +17020,7 @@
         </is>
       </c>
       <c r="C9" s="20">
-        <f>-Assumptions!$C$178</f>
+        <f>-Assumptions!$C$180</f>
         <v/>
       </c>
     </row>
@@ -17011,7 +17031,7 @@
         </is>
       </c>
       <c r="C10" s="20">
-        <f>-Assumptions!$C$180</f>
+        <f>-Assumptions!$C$182</f>
         <v/>
       </c>
     </row>
@@ -17022,7 +17042,7 @@
         </is>
       </c>
       <c r="C11" s="20">
-        <f>-Assumptions!$C$88</f>
+        <f>-Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -17033,7 +17053,7 @@
         </is>
       </c>
       <c r="C12" s="20">
-        <f>-Assumptions!$C$181</f>
+        <f>-Assumptions!$C$183</f>
         <v/>
       </c>
     </row>
@@ -17044,7 +17064,7 @@
         </is>
       </c>
       <c r="C13" s="20">
-        <f>-Assumptions!$C$179</f>
+        <f>-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -17132,7 +17152,7 @@
         </is>
       </c>
       <c r="C21" s="8">
-        <f>Assumptions!$C$198</f>
+        <f>Assumptions!$C$200</f>
         <v/>
       </c>
     </row>
@@ -17172,11 +17192,11 @@
         </is>
       </c>
       <c r="C24" s="33">
-        <f>C23+Assumptions!$C$186-Assumptions!$C$178-Assumptions!$C$180-Assumptions!$C$88-Assumptions!$C$181-Assumptions!$C$179</f>
+        <f>C23+Assumptions!$C$188-Assumptions!$C$180-Assumptions!$C$182-Assumptions!$C$90-Assumptions!$C$183-Assumptions!$C$181</f>
         <v/>
       </c>
       <c r="D24" s="33">
-        <f>D23+Assumptions!$C$186-Assumptions!$C$178-Assumptions!$C$180-Assumptions!$C$88-Assumptions!$C$181-Assumptions!$C$179</f>
+        <f>D23+Assumptions!$C$188-Assumptions!$C$180-Assumptions!$C$182-Assumptions!$C$90-Assumptions!$C$183-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -17265,7 +17285,7 @@
         </is>
       </c>
       <c r="C32" s="20">
-        <f>Assumptions!$C$178+Assumptions!$C$180+Assumptions!$C$88</f>
+        <f>Assumptions!$C$180+Assumptions!$C$182+Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -17331,7 +17351,7 @@
         </is>
       </c>
       <c r="C38" s="44">
-        <f>C31/(Assumptions!$C$187+Assumptions!$C$181)</f>
+        <f>C31/(Assumptions!$C$189+Assumptions!$C$183)</f>
         <v/>
       </c>
     </row>
@@ -17342,7 +17362,7 @@
         </is>
       </c>
       <c r="C39" s="8">
-        <f>Assumptions!$C$191/C31</f>
+        <f>Assumptions!$C$193/C31</f>
         <v/>
       </c>
     </row>
@@ -17353,7 +17373,7 @@
         </is>
       </c>
       <c r="C40" s="33">
-        <f>C33+Assumptions!$C$181+Assumptions!$C$183</f>
+        <f>C33+Assumptions!$C$183+Assumptions!$C$185</f>
         <v/>
       </c>
     </row>
@@ -17428,7 +17448,7 @@
         </is>
       </c>
       <c r="C47" s="33">
-        <f>C46+Assumptions!$C$186-Assumptions!$C$178-Assumptions!$C$180-Assumptions!$C$88-Assumptions!$C$181-Assumptions!$C$179</f>
+        <f>C46+Assumptions!$C$188-Assumptions!$C$180-Assumptions!$C$182-Assumptions!$C$90-Assumptions!$C$183-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -17534,11 +17554,11 @@
         </is>
       </c>
       <c r="C56" s="33">
-        <f>C55+Assumptions!$C$186-Assumptions!$C$178-Assumptions!$C$180-Assumptions!$C$88-Assumptions!$C$181-Assumptions!$C$179</f>
+        <f>C55+Assumptions!$C$188-Assumptions!$C$180-Assumptions!$C$182-Assumptions!$C$90-Assumptions!$C$183-Assumptions!$C$181</f>
         <v/>
       </c>
       <c r="D56" s="33">
-        <f>D55+Assumptions!$C$186-Assumptions!$C$178-Assumptions!$C$180-Assumptions!$C$88-Assumptions!$C$181-Assumptions!$C$179</f>
+        <f>D55+Assumptions!$C$188-Assumptions!$C$180-Assumptions!$C$182-Assumptions!$C$90-Assumptions!$C$183-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -17607,7 +17627,7 @@
         </is>
       </c>
       <c r="C62" s="20">
-        <f>Assumptions!$C$187</f>
+        <f>Assumptions!$C$189</f>
         <v/>
       </c>
     </row>
@@ -17662,7 +17682,7 @@
         </is>
       </c>
       <c r="C67" s="8">
-        <f>Assumptions!$C$193</f>
+        <f>Assumptions!$C$195</f>
         <v/>
       </c>
     </row>
@@ -17673,7 +17693,7 @@
         </is>
       </c>
       <c r="C68" s="8">
-        <f>Assumptions!$C$197</f>
+        <f>Assumptions!$C$199</f>
         <v/>
       </c>
     </row>
@@ -18684,23 +18704,23 @@
         </is>
       </c>
       <c r="B13" s="20">
-        <f>-Assumptions!$B$148</f>
+        <f>-Assumptions!$B$150</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>-Assumptions!$C$148</f>
+        <f>-Assumptions!$C$150</f>
         <v/>
       </c>
       <c r="D13" s="20">
-        <f>-Assumptions!$D$148</f>
+        <f>-Assumptions!$D$150</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>-Assumptions!$E$148</f>
+        <f>-Assumptions!$E$150</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>-Assumptions!$F$148</f>
+        <f>-Assumptions!$F$150</f>
         <v/>
       </c>
     </row>
@@ -19013,23 +19033,23 @@
         </is>
       </c>
       <c r="B26" s="33">
-        <f>-B8*(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-B8*(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="C26" s="33">
-        <f>-C8*(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-C8*(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="D26" s="33">
-        <f>-D8*(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-D8*(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="E26" s="33">
-        <f>-E8*(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-E8*(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="F26" s="33">
-        <f>-F8*(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-F8*(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
     </row>
@@ -19040,23 +19060,23 @@
         </is>
       </c>
       <c r="B27" s="33">
-        <f>-B8*(Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-B8*(Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="C27" s="33">
-        <f>-C8*(Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-C8*(Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="D27" s="33">
-        <f>-D8*(Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-D8*(Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="E27" s="33">
-        <f>-E8*(Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-E8*(Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>-F8*(Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-F8*(Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
     </row>
@@ -19067,23 +19087,23 @@
         </is>
       </c>
       <c r="B28" s="33">
-        <f>-B8*(Assumptions!$C$175)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-B8*(Assumptions!$C$177)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="C28" s="33">
-        <f>-C8*(Assumptions!$C$175)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-C8*(Assumptions!$C$177)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="D28" s="33">
-        <f>-D8*(Assumptions!$C$175)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-D8*(Assumptions!$C$177)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="E28" s="33">
-        <f>-E8*(Assumptions!$C$175)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-E8*(Assumptions!$C$177)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
       <c r="F28" s="33">
-        <f>-F8*(Assumptions!$C$175)/(Assumptions!$C$169+Assumptions!$C$170+Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175)</f>
+        <f>-F8*(Assumptions!$C$177)/(Assumptions!$C$171+Assumptions!$C$172+Assumptions!$C$173+Assumptions!$C$174+Assumptions!$C$175+Assumptions!$C$176+Assumptions!$C$177)</f>
         <v/>
       </c>
     </row>
@@ -19175,23 +19195,23 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>B29*Assumptions!$C$166</f>
+        <f>B29*Assumptions!$C$168</f>
         <v/>
       </c>
       <c r="C32" s="33">
-        <f>C29*Assumptions!$C$166</f>
+        <f>C29*Assumptions!$C$168</f>
         <v/>
       </c>
       <c r="D32" s="33">
-        <f>D29*Assumptions!$C$166</f>
+        <f>D29*Assumptions!$C$168</f>
         <v/>
       </c>
       <c r="E32" s="33">
-        <f>E29*Assumptions!$C$166</f>
+        <f>E29*Assumptions!$C$168</f>
         <v/>
       </c>
       <c r="F32" s="33">
-        <f>F29*Assumptions!$C$166</f>
+        <f>F29*Assumptions!$C$168</f>
         <v/>
       </c>
     </row>
@@ -19202,23 +19222,23 @@
         </is>
       </c>
       <c r="B33" s="33">
-        <f>B30*Assumptions!$C$167</f>
+        <f>B30*Assumptions!$C$169</f>
         <v/>
       </c>
       <c r="C33" s="33">
-        <f>C30*Assumptions!$C$167</f>
+        <f>C30*Assumptions!$C$169</f>
         <v/>
       </c>
       <c r="D33" s="33">
-        <f>D30*Assumptions!$C$167</f>
+        <f>D30*Assumptions!$C$169</f>
         <v/>
       </c>
       <c r="E33" s="33">
-        <f>E30*Assumptions!$C$167</f>
+        <f>E30*Assumptions!$C$169</f>
         <v/>
       </c>
       <c r="F33" s="33">
-        <f>F30*Assumptions!$C$167</f>
+        <f>F30*Assumptions!$C$169</f>
         <v/>
       </c>
     </row>
@@ -19229,23 +19249,23 @@
         </is>
       </c>
       <c r="B34" s="33">
-        <f>B31*Assumptions!$C$168</f>
+        <f>B31*Assumptions!$C$170</f>
         <v/>
       </c>
       <c r="C34" s="33">
-        <f>C31*Assumptions!$C$168</f>
+        <f>C31*Assumptions!$C$170</f>
         <v/>
       </c>
       <c r="D34" s="33">
-        <f>D31*Assumptions!$C$168</f>
+        <f>D31*Assumptions!$C$170</f>
         <v/>
       </c>
       <c r="E34" s="33">
-        <f>E31*Assumptions!$C$168</f>
+        <f>E31*Assumptions!$C$170</f>
         <v/>
       </c>
       <c r="F34" s="33">
-        <f>F31*Assumptions!$C$168</f>
+        <f>F31*Assumptions!$C$170</f>
         <v/>
       </c>
     </row>
@@ -19322,7 +19342,7 @@
         </is>
       </c>
       <c r="C39" s="8">
-        <f>Assumptions!$C$193</f>
+        <f>Assumptions!$C$195</f>
         <v/>
       </c>
     </row>
@@ -19432,7 +19452,7 @@
         </is>
       </c>
       <c r="C49" s="20">
-        <f>Assumptions!$C$186</f>
+        <f>Assumptions!$C$188</f>
         <v/>
       </c>
     </row>
@@ -19454,7 +19474,7 @@
         </is>
       </c>
       <c r="C51" s="20">
-        <f>-Assumptions!$C$178</f>
+        <f>-Assumptions!$C$180</f>
         <v/>
       </c>
     </row>
@@ -19465,7 +19485,7 @@
         </is>
       </c>
       <c r="C52" s="20">
-        <f>-Assumptions!$C$180</f>
+        <f>-Assumptions!$C$182</f>
         <v/>
       </c>
     </row>
@@ -19476,7 +19496,7 @@
         </is>
       </c>
       <c r="C53" s="20">
-        <f>-Assumptions!$C$88</f>
+        <f>-Assumptions!$C$90</f>
         <v/>
       </c>
     </row>
@@ -19487,7 +19507,7 @@
         </is>
       </c>
       <c r="C54" s="20">
-        <f>-Assumptions!$C$181</f>
+        <f>-Assumptions!$C$183</f>
         <v/>
       </c>
     </row>
@@ -19498,7 +19518,7 @@
         </is>
       </c>
       <c r="C55" s="20">
-        <f>-Assumptions!$C$179</f>
+        <f>-Assumptions!$C$181</f>
         <v/>
       </c>
     </row>
@@ -19520,7 +19540,7 @@
         </is>
       </c>
       <c r="C57" s="20">
-        <f>Assumptions!$C$184</f>
+        <f>Assumptions!$C$186</f>
         <v/>
       </c>
     </row>
@@ -19531,7 +19551,7 @@
         </is>
       </c>
       <c r="C58" s="33">
-        <f>Assumptions!$C$183-C57</f>
+        <f>Assumptions!$C$185-C57</f>
         <v/>
       </c>
     </row>
@@ -19542,7 +19562,7 @@
         </is>
       </c>
       <c r="C59" s="56">
-        <f>Assumptions!$C$185*C58/Assumptions!$C$183</f>
+        <f>Assumptions!$C$187*C58/Assumptions!$C$185</f>
         <v/>
       </c>
     </row>
@@ -19669,7 +19689,7 @@
       </c>
       <c r="B70" s="16" t="n"/>
       <c r="C70" s="57">
-        <f>C67+C68*C69</f>
+        <f>C67+C68*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
       <c r="D70" s="16" t="n"/>
@@ -19693,7 +19713,7 @@
         </is>
       </c>
       <c r="C73" s="21">
-        <f>Assumptions!$C$24</f>
+        <f>Assumptions!$C$26</f>
         <v/>
       </c>
     </row>
@@ -19704,7 +19724,7 @@
         </is>
       </c>
       <c r="C74" s="21">
-        <f>Assumptions!$C$25</f>
+        <f>Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -19726,7 +19746,7 @@
         </is>
       </c>
       <c r="C76" s="21">
-        <f>Assumptions!$C$26</f>
+        <f>Assumptions!$C$28</f>
         <v/>
       </c>
     </row>
@@ -19737,7 +19757,7 @@
         </is>
       </c>
       <c r="C77" s="21">
-        <f>Assumptions!$C$27</f>
+        <f>Assumptions!$C$29</f>
         <v/>
       </c>
     </row>
@@ -19759,7 +19779,7 @@
         </is>
       </c>
       <c r="C79" s="21">
-        <f>Assumptions!$C$28</f>
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
@@ -19770,7 +19790,7 @@
         </is>
       </c>
       <c r="C80" s="21">
-        <f>Assumptions!$C$29</f>
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -19803,7 +19823,7 @@
         </is>
       </c>
       <c r="C83" s="20">
-        <f>Assumptions!$C$30</f>
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
@@ -19814,7 +19834,7 @@
         </is>
       </c>
       <c r="C84" s="20">
-        <f>Assumptions!$C$31</f>
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -19825,7 +19845,7 @@
         </is>
       </c>
       <c r="C85" s="20">
-        <f>Assumptions!$C$32</f>
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -19847,7 +19867,7 @@
         </is>
       </c>
       <c r="C87" s="20">
-        <f>Assumptions!$C$33</f>
+        <f>Assumptions!$C$35</f>
         <v/>
       </c>
     </row>
@@ -19858,7 +19878,7 @@
         </is>
       </c>
       <c r="C88" s="20">
-        <f>Assumptions!$C$34</f>
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -19869,7 +19889,7 @@
         </is>
       </c>
       <c r="C89" s="20">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -19937,7 +19957,7 @@
         </is>
       </c>
       <c r="C95" s="8">
-        <f>Assumptions!$C$21</f>
+        <f>Assumptions!$C$23</f>
         <v/>
       </c>
     </row>
@@ -19993,7 +20013,7 @@
         </is>
       </c>
       <c r="C100" s="20">
-        <f>Assumptions!$C$181</f>
+        <f>Assumptions!$C$183</f>
         <v/>
       </c>
     </row>
@@ -20048,7 +20068,7 @@
         </is>
       </c>
       <c r="C105" s="56">
-        <f>C73+Assumptions!$C$182</f>
+        <f>C73+Assumptions!$C$184</f>
         <v/>
       </c>
     </row>
@@ -20072,7 +20092,7 @@
         </is>
       </c>
       <c r="C107" s="21">
-        <f>Assumptions!$C$20</f>
+        <f>Assumptions!$C$22</f>
         <v/>
       </c>
     </row>
@@ -20083,7 +20103,7 @@
         </is>
       </c>
       <c r="C108" s="56">
-        <f>C107+C68*C69</f>
+        <f>C107+C68*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -20116,7 +20136,7 @@
         </is>
       </c>
       <c r="C111" s="56">
-        <f>C107+Assumptions!$C$182</f>
+        <f>C107+Assumptions!$C$184</f>
         <v/>
       </c>
     </row>
@@ -20170,7 +20190,7 @@
         </is>
       </c>
       <c r="C116" s="56">
-        <f>C67+C115*C69</f>
+        <f>C67+C115*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -20181,7 +20201,7 @@
         </is>
       </c>
       <c r="C117" s="56">
-        <f>C107+C115*C69</f>
+        <f>C107+C115*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -20248,7 +20268,7 @@
         </is>
       </c>
       <c r="C124" s="56">
-        <f>C67+C122*C69</f>
+        <f>C67+C122*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -20259,7 +20279,7 @@
         </is>
       </c>
       <c r="C125" s="56">
-        <f>C67+C123*C69</f>
+        <f>C67+C123*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -20281,7 +20301,7 @@
         </is>
       </c>
       <c r="C127" s="56">
-        <f>C67+C126*C69</f>
+        <f>C67+C126*Assumptions!$C$20+Assumptions!$C$21</f>
         <v/>
       </c>
     </row>
@@ -21313,23 +21333,23 @@
         <v>18959</v>
       </c>
       <c r="E22" s="20">
-        <f>Assumptions!$C$24*Assumptions!$C$188</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="F22" s="20">
-        <f>Assumptions!$C$24*Assumptions!$C$188</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="G22" s="20">
-        <f>Assumptions!$C$24*Assumptions!$C$188</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>Assumptions!$C$24*Assumptions!$C$188</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190</f>
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>Assumptions!$C$24*Assumptions!$C$188</f>
+        <f>Assumptions!$C$26*Assumptions!$C$190</f>
         <v/>
       </c>
     </row>
@@ -21499,23 +21519,23 @@
         <v>-24306</v>
       </c>
       <c r="E27" s="33">
-        <f>-E26*Assumptions!$C$185</f>
+        <f>-E26*Assumptions!$C$187</f>
         <v/>
       </c>
       <c r="F27" s="33">
-        <f>-F26*Assumptions!$C$185</f>
+        <f>-F26*Assumptions!$C$187</f>
         <v/>
       </c>
       <c r="G27" s="33">
-        <f>-G26*Assumptions!$C$185</f>
+        <f>-G26*Assumptions!$C$187</f>
         <v/>
       </c>
       <c r="H27" s="33">
-        <f>-H26*Assumptions!$C$185</f>
+        <f>-H26*Assumptions!$C$187</f>
         <v/>
       </c>
       <c r="I27" s="33">
-        <f>-I26*Assumptions!$C$185</f>
+        <f>-I26*Assumptions!$C$187</f>
         <v/>
       </c>
     </row>
@@ -21574,23 +21594,23 @@
         <v>-61333</v>
       </c>
       <c r="E29" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="F29" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="G29" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="H29" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
       <c r="I29" s="33">
-        <f>-Assumptions!$C$181*(Assumptions!$C$24+Assumptions!$C$182)</f>
+        <f>-Assumptions!$C$183*(Assumptions!$C$26+Assumptions!$C$184)</f>
         <v/>
       </c>
     </row>
